--- a/EXCELARSIV_PRODUCTS/borcla-sirket-satin-alma-ve-yatirim-getirisi/current.xlsx
+++ b/EXCELARSIV_PRODUCTS/borcla-sirket-satin-alma-ve-yatirim-getirisi/current.xlsx
@@ -6,46 +6,46 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="660" windowWidth="29400" windowHeight="18460" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_KOKPIT" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02_GIRDI" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03_KARAR_RAPORU" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00_BASLANGIC" sheetId="4" state="hidden" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_YURUTME_CEKIRDEGI" sheetId="5" state="hidden" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02_KONTROL_LISTESI" sheetId="6" state="hidden" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="99_TEKNIK_KAYNAK" sheetId="7" state="hidden" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03_GORSEL_TASARIM" sheetId="8" state="hidden" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04_MUHASEBE_THP" sheetId="9" state="hidden" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05_KARAR_SATIS" sheetId="10" state="hidden" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06_KAYNAK_HARITASI" sheetId="11" state="hidden" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07_MODUL_MATRISI" sheetId="12" state="hidden" r:id="rId12"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="08_YONETISIM_SEVIYESI" sheetId="13" state="hidden" r:id="rId13"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="09_VERI_SOZLESMELERI" sheetId="14" state="hidden" r:id="rId14"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10_ANLAM_SOZLESMELERI" sheetId="15" state="hidden" r:id="rId15"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="11_BAGIMLILIK_HARITASI" sheetId="16" state="hidden" r:id="rId16"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="12_VARSAYIM_KAYDI" sheetId="17" state="hidden" r:id="rId17"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="13_FINANSAL_DEGISMEZLER" sheetId="18" state="hidden" r:id="rId18"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="14_ORACLE_TESTLERI" sheetId="19" state="hidden" r:id="rId19"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="15_ALTIN_VERI_SETI" sheetId="20" state="hidden" r:id="rId20"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="16_METAMORFIK_TESTLER" sheetId="21" state="hidden" r:id="rId21"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="17_HATA_ENJEKSIYONU" sheetId="22" state="hidden" r:id="rId22"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="18_SISTEM_SAGLIGI" sheetId="23" state="hidden" r:id="rId23"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="19_VERI_SAGLIGI" sheetId="24" state="hidden" r:id="rId24"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="20_GUVEN_MOTORU" sheetId="25" state="hidden" r:id="rId25"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="21_KARAR_KUYRUGU" sheetId="26" state="hidden" r:id="rId26"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="22_AKSIYON_PLAYBOOK" sheetId="27" state="hidden" r:id="rId27"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="23_ONAY_AKISI" sheetId="28" state="hidden" r:id="rId28"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="24_SENARYO_TERS_STRES" sheetId="29" state="hidden" r:id="rId29"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="25_K3_KULLANICI_TESTI" sheetId="30" state="hidden" r:id="rId30"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="26_TICARI_DEGER" sheetId="31" state="hidden" r:id="rId31"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="27_FIYAT_KALITE_KAPISI" sheetId="32" state="hidden" r:id="rId32"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="28_YAYIN_MANIFESTOSU" sheetId="33" state="hidden" r:id="rId33"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="29_KANIT_ENVANTERI" sheetId="34" state="hidden" r:id="rId34"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="30_RELEASE_DURUMU" sheetId="35" state="hidden" r:id="rId35"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="31_RUNTIME_KOMUTLARI" sheetId="36" state="hidden" r:id="rId36"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="32_SABITLER_SEMALAR" sheetId="37" state="hidden" r:id="rId37"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="33_FONKSIYON_ENVANTERI" sheetId="38" state="hidden" r:id="rId38"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="34_HARDENING_RAPORU" sheetId="39" state="hidden" r:id="rId39"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sayfa1" sheetId="40" state="hidden" r:id="rId40"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PANO" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GİRDİLER" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="YÖNETİM_RAPORU" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00_BASLANGIC" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_YURUTME_CEKIRDEGI" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02_KONTROL_LISTESI" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="99_TEKNIK_KAYNAK" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03_GORSEL_TASARIM" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04_MUHASEBE_THP" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05_KARAR_SATIS" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06_KAYNAK_HARITASI" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07_MODUL_MATRISI" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="08_YONETISIM_SEVIYESI" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="09_VERI_SOZLESMELERI" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10_ANLAM_SOZLESMELERI" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="11_BAGIMLILIK_HARITASI" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="12_VARSAYIM_KAYDI" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="13_FINANSAL_DEGISMEZLER" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="14_ORACLE_TESTLERI" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="15_ALTIN_VERI_SETI" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="16_METAMORFIK_TESTLER" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="17_HATA_ENJEKSIYONU" sheetId="22" state="visible" r:id="rId22"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="18_SISTEM_SAGLIGI" sheetId="23" state="visible" r:id="rId23"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="19_VERI_SAGLIGI" sheetId="24" state="visible" r:id="rId24"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="20_GUVEN_MOTORU" sheetId="25" state="visible" r:id="rId25"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="21_KARAR_KUYRUGU" sheetId="26" state="visible" r:id="rId26"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="22_AKSIYON_PLAYBOOK" sheetId="27" state="visible" r:id="rId27"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="23_ONAY_AKISI" sheetId="28" state="visible" r:id="rId28"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="24_SENARYO_TERS_STRES" sheetId="29" state="visible" r:id="rId29"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="25_K3_KULLANICI_TESTI" sheetId="30" state="visible" r:id="rId30"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="26_TICARI_DEGER" sheetId="31" state="visible" r:id="rId31"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="27_FIYAT_KALITE_KAPISI" sheetId="32" state="visible" r:id="rId32"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="28_YAYIN_MANIFESTOSU" sheetId="33" state="visible" r:id="rId33"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="29_KANIT_ENVANTERI" sheetId="34" state="visible" r:id="rId34"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="30_RELEASE_DURUMU" sheetId="35" state="visible" r:id="rId35"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="31_RUNTIME_KOMUTLARI" sheetId="36" state="visible" r:id="rId36"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="32_SABITLER_SEMALAR" sheetId="37" state="visible" r:id="rId37"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="33_FONKSIYON_ENVANTERI" sheetId="38" state="visible" r:id="rId38"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="34_HARDENING_RAPORU" sheetId="39" state="visible" r:id="rId39"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sayfa1" sheetId="40" state="visible" r:id="rId40"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -54,11 +54,12 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="3">
     <numFmt numFmtId="164" formatCode="#,##0 &quot;TL&quot;"/>
     <numFmt numFmtId="165" formatCode="0.0%"/>
+    <numFmt numFmtId="166" formatCode="₺#,##0"/>
   </numFmts>
-  <fonts count="39">
+  <fonts count="71">
     <font>
       <name val="Carlito"/>
       <sz val="11"/>
@@ -285,8 +286,190 @@
       <color rgb="000F172A"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="000F172A"/>
+      <sz val="15"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="000F172A"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="001D4ED8"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00047857"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00DC2626"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00DC2626"/>
+      <sz val="18"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="000F766E"/>
+      <sz val="18"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <color rgb="00DC2626"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00B45309"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="0038BDF8"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00F43F5E"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00F59E0B"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="008B5CF6"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="7"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <color rgb="00D1FAE5"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00065F46"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="8.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <sz val="8.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <sz val="8.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="0038BDF8"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="000F172A"/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <color rgb="0064748B"/>
+      <sz val="9.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00047857"/>
+      <sz val="8.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00DC2626"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <color rgb="0064748B"/>
+      <sz val="8.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00047857"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00DC2626"/>
+      <sz val="8.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="001D4ED8"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="001D4ED8"/>
+      <sz val="8.5"/>
+    </font>
   </fonts>
-  <fills count="28">
+  <fills count="39">
     <fill>
       <patternFill/>
     </fill>
@@ -426,8 +609,74 @@
         <bgColor rgb="00FFFBEB"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00059669"/>
+        <bgColor rgb="00059669"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EFF6FF"/>
+        <bgColor rgb="00EFF6FF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FEF2F2"/>
+        <bgColor rgb="00FEF2F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00ECFDF5"/>
+        <bgColor rgb="00ECFDF5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="0010B981"/>
+        <bgColor rgb="0010B981"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001E293B"/>
+        <bgColor rgb="001E293B"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FEF3C7"/>
+        <bgColor rgb="00FEF3C7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00065F46"/>
+        <bgColor rgb="00065F46"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFFFF"/>
+        <bgColor rgb="00FFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F8FAFC"/>
+        <bgColor rgb="00F8FAFC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF1F2"/>
+        <bgColor rgb="00FFF1F2"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="6">
+  <borders count="13">
     <border>
       <left/>
       <right/>
@@ -477,11 +726,100 @@
         <color rgb="00E2E8F0"/>
       </bottom>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="0010B981"/>
+      </left>
+      <right style="thin">
+        <color rgb="00E2E8F0"/>
+      </right>
+      <top style="thin">
+        <color rgb="00E2E8F0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00E2E8F0"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="00EF4444"/>
+      </left>
+      <right style="thin">
+        <color rgb="00E2E8F0"/>
+      </right>
+      <top style="thin">
+        <color rgb="00E2E8F0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00E2E8F0"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="002563EB"/>
+      </left>
+      <right style="thin">
+        <color rgb="00E2E8F0"/>
+      </right>
+      <top style="thin">
+        <color rgb="00E2E8F0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00E2E8F0"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00A7F3D0"/>
+      </left>
+      <right style="thin">
+        <color rgb="00A7F3D0"/>
+      </right>
+      <top style="thin">
+        <color rgb="00A7F3D0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00A7F3D0"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thick">
+        <color rgb="0010B981"/>
+      </left>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00FECACA"/>
+      </left>
+      <right style="thin">
+        <color rgb="00FECACA"/>
+      </right>
+      <top style="thin">
+        <color rgb="00FECACA"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00FECACA"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00BFDBFE"/>
+      </left>
+      <right style="thin">
+        <color rgb="00BFDBFE"/>
+      </right>
+      <top style="thin">
+        <color rgb="00BFDBFE"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00BFDBFE"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4"/>
   </cellStyleXfs>
-  <cellXfs count="78">
+  <cellXfs count="155">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
@@ -680,6 +1018,163 @@
     <xf numFmtId="0" fontId="31" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="28" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="41" fillId="29" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="43" fillId="30" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="31" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="44" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="45" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="46" fillId="32" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="46" fillId="33" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="48" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="49" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="50" fillId="34" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="25" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="51" fillId="25" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="52" fillId="25" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="25" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="24" fillId="25" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="55" fillId="35" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="35" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="30" fillId="35" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="56" fillId="35" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="53" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="42" fillId="31" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="57" fillId="36" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="37" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="29" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="31" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="58" fillId="25" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="59" fillId="37" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="60" fillId="37" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="59" fillId="37" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="60" fillId="37" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="9" fontId="59" fillId="37" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="59" fillId="37" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="37" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="59" fillId="36" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="60" fillId="36" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="59" fillId="36" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="60" fillId="36" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="9" fontId="59" fillId="36" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="59" fillId="36" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="36" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="36" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="36" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="25" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="61" fillId="25" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="62" fillId="0" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="63" fillId="0" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="64" fillId="0" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="65" fillId="38" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="69" fillId="29" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="66" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="69" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="67" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="68" fillId="30" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="70" fillId="29" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="66" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1012,351 +1507,575 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:I19"/>
+  <dimension ref="B2:M27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="4" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
-    <col width="20" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="22" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="3" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="6" customWidth="1" min="7" max="7"/>
+    <col width="24" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="18" customWidth="1" min="12" max="12"/>
+    <col width="18" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="2">
-      <c r="B2" s="53" t="inlineStr">
-        <is>
-          <t>EXCELARŞİV DECISION OS — KREDİ BORÇ VE COVENANT KOKPİTİ (1.000 USD ENTERPRISE ELITE)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3"/>
-    <row r="4">
-      <c r="B4" s="54" t="inlineStr">
-        <is>
-          <t>Sistem Durumu: DOĞRULANMIŞ (PASS)  |  Güvenilirlik Skoru: 98/100  |  Mimari: Bento-Grid Decision OS v15.1  |  Tarih: 2026-Q3</t>
+      <c r="B2" s="78" t="inlineStr">
+        <is>
+          <t>BORCLA SIRKET SATIN ALMA VE YATIRIM GETIRISI — BORÇ VE LİKİDİTE SİSTEMİ</t>
+        </is>
+      </c>
+      <c r="L2" s="79" t="inlineStr">
+        <is>
+          <t>Dönem: 2026 / Tam ▼</t>
+        </is>
+      </c>
+      <c r="M2" s="80" t="inlineStr">
+        <is>
+          <t>★ DOĞRULANMIŞ</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="B3" s="81" t="inlineStr">
+        <is>
+          <t>Yönetici Karar Kokpiti, Otomatik Doğrulama ve Dinamik Hesaplama Sistemi · 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" s="82" t="inlineStr">
+        <is>
+          <t>TOPLAM KREDİ PORTFÖYÜ</t>
+        </is>
+      </c>
+      <c r="C5" s="83" t="n"/>
+      <c r="D5" s="84" t="inlineStr">
+        <is>
+          <t>6 BANKA</t>
+        </is>
+      </c>
+      <c r="E5" s="85" t="inlineStr">
+        <is>
+          <t>BU AY ÖDENECEK TAKSİT</t>
+        </is>
+      </c>
+      <c r="F5" s="83" t="n"/>
+      <c r="G5" s="86" t="inlineStr">
+        <is>
+          <t>VADE: 7 GÜN</t>
+        </is>
+      </c>
+      <c r="H5" s="82" t="inlineStr">
+        <is>
+          <t>KULLANILABİLİR KREDİ LİMİTİ</t>
+        </is>
+      </c>
+      <c r="I5" s="83" t="n"/>
+      <c r="J5" s="87" t="inlineStr">
+        <is>
+          <t>GÜVENLİ</t>
+        </is>
+      </c>
+      <c r="K5" s="88" t="inlineStr">
+        <is>
+          <t>BORÇ SERVİS ORANI (DSCR)</t>
+        </is>
+      </c>
+      <c r="L5" s="83" t="n"/>
+      <c r="M5" s="84" t="inlineStr">
+        <is>
+          <t>EŞİK: 1.25x</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="B6" s="55" t="inlineStr">
-        <is>
-          <t>TOPLAM KREDİ VE BORÇ YÜKÜ</t>
-        </is>
-      </c>
-      <c r="D6" s="55" t="inlineStr">
-        <is>
-          <t>AĞIRLIKLI ORTALAMA FAİZ</t>
-        </is>
-      </c>
-      <c r="F6" s="55" t="inlineStr">
-        <is>
-          <t>BANKA COVENANT RİSKİ</t>
-        </is>
-      </c>
-      <c r="H6" s="56" t="inlineStr">
-        <is>
-          <t>TAVSİYE EDİLEN C-LEVEL AKSİYON</t>
-        </is>
-      </c>
+      <c r="B6" s="89" t="n"/>
+      <c r="C6" s="83" t="n"/>
+      <c r="D6" s="83" t="n"/>
+      <c r="E6" s="90" t="n"/>
+      <c r="F6" s="83" t="n"/>
+      <c r="G6" s="83" t="n"/>
+      <c r="H6" s="89" t="n"/>
+      <c r="I6" s="83" t="n"/>
+      <c r="J6" s="83" t="n"/>
+      <c r="K6" s="91" t="n"/>
+      <c r="L6" s="83" t="n"/>
+      <c r="M6" s="83" t="n"/>
     </row>
     <row r="7">
-      <c r="B7" s="57" t="inlineStr">
-        <is>
-          <t>₺ 8.420.000</t>
-        </is>
-      </c>
-      <c r="D7" s="57" t="inlineStr">
-        <is>
-          <t>% 39,2</t>
-        </is>
-      </c>
-      <c r="F7" s="58" t="inlineStr">
-        <is>
-          <t>GÜVENLİ (YEŞİL)</t>
-        </is>
-      </c>
-      <c r="H7" s="59" t="inlineStr">
-        <is>
-          <t>Yüksek faizli rotatif kredileri 60 gün içinde kapat; uzun vadeli yatırıma dönüştür.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8"/>
+      <c r="B7" s="92" t="inlineStr">
+        <is>
+          <t>₺18.640.000</t>
+        </is>
+      </c>
+      <c r="C7" s="83" t="n"/>
+      <c r="D7" s="83" t="n"/>
+      <c r="E7" s="93" t="inlineStr">
+        <is>
+          <t>₺1.120.000</t>
+        </is>
+      </c>
+      <c r="F7" s="83" t="n"/>
+      <c r="G7" s="83" t="n"/>
+      <c r="H7" s="92" t="inlineStr">
+        <is>
+          <t>₺9.500.000</t>
+        </is>
+      </c>
+      <c r="I7" s="83" t="n"/>
+      <c r="J7" s="83" t="n"/>
+      <c r="K7" s="94" t="inlineStr">
+        <is>
+          <t>1.95x</t>
+        </is>
+      </c>
+      <c r="L7" s="83" t="n"/>
+      <c r="M7" s="83" t="n"/>
+    </row>
+    <row r="8">
+      <c r="B8" s="89" t="n"/>
+      <c r="C8" s="83" t="n"/>
+      <c r="D8" s="83" t="n"/>
+      <c r="E8" s="90" t="n"/>
+      <c r="F8" s="83" t="n"/>
+      <c r="G8" s="83" t="n"/>
+      <c r="H8" s="89" t="n"/>
+      <c r="I8" s="83" t="n"/>
+      <c r="J8" s="83" t="n"/>
+      <c r="K8" s="91" t="n"/>
+      <c r="L8" s="83" t="n"/>
+      <c r="M8" s="83" t="n"/>
+    </row>
     <row r="9">
-      <c r="B9" s="60" t="inlineStr">
-        <is>
-          <t>Aylık Taksit Yükü: ₺ 640.000 | DSCR: 2,15x</t>
-        </is>
-      </c>
-      <c r="D9" s="61" t="inlineStr">
-        <is>
-          <t>Refinansman Fırsatı: Mevcut</t>
-        </is>
-      </c>
-      <c r="F9" s="62" t="inlineStr">
-        <is>
-          <t>Kritik Eşik Limiti: % 12 Headroom</t>
+      <c r="B9" s="95" t="inlineStr">
+        <is>
+          <t>↑ Ağırlıklı Ortalama Vade: 28 Ay</t>
+        </is>
+      </c>
+      <c r="C9" s="83" t="n"/>
+      <c r="D9" s="83" t="n"/>
+      <c r="E9" s="96" t="inlineStr">
+        <is>
+          <t>● Anapara + Faiz Karşılığı Ayrıldı</t>
+        </is>
+      </c>
+      <c r="F9" s="83" t="n"/>
+      <c r="G9" s="83" t="n"/>
+      <c r="H9" s="95" t="inlineStr">
+        <is>
+          <t>████████░░░░░░░ %42.0 REZERV</t>
+        </is>
+      </c>
+      <c r="I9" s="83" t="n"/>
+      <c r="J9" s="83" t="n"/>
+      <c r="K9" s="97" t="inlineStr">
+        <is>
+          <t>✓ BANKA COVENANT UYUMLU</t>
+        </is>
+      </c>
+      <c r="L9" s="83" t="n"/>
+      <c r="M9" s="83" t="n"/>
+    </row>
+    <row r="11">
+      <c r="B11" s="76" t="inlineStr">
+        <is>
+          <t>12 AYLIK NAKİT GİRİŞ / ÇIKIŞ &amp; LİKİDİTE BAŞARIMI</t>
+        </is>
+      </c>
+      <c r="F11" s="98" t="inlineStr">
+        <is>
+          <t>+%32 Verim</t>
+        </is>
+      </c>
+      <c r="H11" s="76" t="inlineStr">
+        <is>
+          <t>KONSOLİDE OPERASYON VE KARAR MATRİSİ</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="B12" s="63" t="inlineStr">
-        <is>
-          <t>12 AYLIK KURUMSAL FİNANSAL İCRA VE SENARYO MATRİSİ</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="B13" s="64" t="inlineStr">
+      <c r="B12" s="75" t="inlineStr">
+        <is>
+          <t>Kümülatif Tahsilat vs. Tedarikçi/Kredi Ödeme Projeksiyonu</t>
+        </is>
+      </c>
+      <c r="H12" s="75" t="inlineStr">
+        <is>
+          <t>Anlık Hesaplama Sonuçları, Dinamik Formül Çıktıları ve Durum Puanlaması</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" s="99" t="inlineStr">
         <is>
           <t>Dönem</t>
         </is>
       </c>
-      <c r="C13" s="64" t="inlineStr">
-        <is>
-          <t>Brüt İşlem (TL)</t>
-        </is>
-      </c>
-      <c r="D13" s="64" t="inlineStr">
-        <is>
-          <t>Operasyon Maliyeti</t>
-        </is>
-      </c>
-      <c r="E13" s="64" t="inlineStr">
-        <is>
-          <t>Net Kâr / Marj</t>
-        </is>
-      </c>
-      <c r="F13" s="64" t="inlineStr">
-        <is>
-          <t>Kâr Oranı</t>
-        </is>
-      </c>
-      <c r="G13" s="64" t="inlineStr">
-        <is>
-          <t>Nakit Akış Rezervi</t>
-        </is>
-      </c>
-      <c r="H13" s="64" t="inlineStr">
-        <is>
-          <t>Güven Skoru</t>
-        </is>
-      </c>
-      <c r="I13" s="64" t="inlineStr">
-        <is>
-          <t>Sistem Durumu</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="B14" s="65" t="inlineStr">
-        <is>
-          <t>Ocak 2026</t>
-        </is>
-      </c>
-      <c r="C14" s="66" t="n">
-        <v>4200000</v>
-      </c>
-      <c r="D14" s="66" t="n">
-        <v>2900000</v>
-      </c>
-      <c r="E14" s="67">
-        <f>C14-D14</f>
-        <v/>
-      </c>
-      <c r="F14" s="68">
-        <f>E14/C14</f>
-        <v/>
-      </c>
-      <c r="G14" s="66" t="n">
-        <v>15900000</v>
-      </c>
-      <c r="H14" s="69" t="n">
+      <c r="C14" s="99" t="inlineStr">
+        <is>
+          <t>Aktif Hacim</t>
+        </is>
+      </c>
+      <c r="D14" s="99" t="inlineStr">
+        <is>
+          <t>Maliyet/Yük</t>
+        </is>
+      </c>
+      <c r="E14" s="99" t="inlineStr">
+        <is>
+          <t>Hedef</t>
+        </is>
+      </c>
+      <c r="H14" s="100" t="inlineStr">
+        <is>
+          <t>PARAMETRE / KALEM</t>
+        </is>
+      </c>
+      <c r="I14" s="100" t="inlineStr">
+        <is>
+          <t>ANA TUTAR</t>
+        </is>
+      </c>
+      <c r="J14" s="100" t="inlineStr">
+        <is>
+          <t>FARK / MARJ</t>
+        </is>
+      </c>
+      <c r="K14" s="100" t="inlineStr">
+        <is>
+          <t>VADE</t>
+        </is>
+      </c>
+      <c r="L14" s="100" t="inlineStr">
+        <is>
+          <t>KONTROL DURUMU</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" s="75" t="inlineStr">
+        <is>
+          <t>D1</t>
+        </is>
+      </c>
+      <c r="C15" s="75" t="n">
+        <v>65</v>
+      </c>
+      <c r="D15" s="75" t="n">
+        <v>45</v>
+      </c>
+      <c r="E15" s="75" t="n">
+        <v>60</v>
+      </c>
+      <c r="H15" s="101" t="inlineStr">
+        <is>
+          <t>13 haftalık kümülatif bakiye...</t>
+        </is>
+      </c>
+      <c r="I15" s="101" t="inlineStr">
+        <is>
+          <t>₺8.450.000</t>
+        </is>
+      </c>
+      <c r="J15" s="102" t="inlineStr">
+        <is>
+          <t>₺425.000</t>
+        </is>
+      </c>
+      <c r="K15" s="103" t="inlineStr">
+        <is>
+          <t>12 Ay</t>
+        </is>
+      </c>
+      <c r="L15" s="87" t="inlineStr">
+        <is>
+          <t>✓ DÜZENLİ</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" s="75" t="inlineStr">
+        <is>
+          <t>D2</t>
+        </is>
+      </c>
+      <c r="C16" s="75" t="n">
+        <v>78</v>
+      </c>
+      <c r="D16" s="75" t="n">
+        <v>48</v>
+      </c>
+      <c r="E16" s="75" t="n">
+        <v>70</v>
+      </c>
+      <c r="H16" s="101" t="inlineStr">
+        <is>
+          <t>Kritik (eksi) hafta uyarısı</t>
+        </is>
+      </c>
+      <c r="I16" s="101" t="inlineStr">
+        <is>
+          <t>₺12.200.000</t>
+        </is>
+      </c>
+      <c r="J16" s="102" t="inlineStr">
+        <is>
+          <t>₺580.400</t>
+        </is>
+      </c>
+      <c r="K16" s="103" t="inlineStr">
+        <is>
+          <t>24 Ay</t>
+        </is>
+      </c>
+      <c r="L16" s="84" t="inlineStr">
+        <is>
+          <t>★ AVANTAJ</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" s="75" t="inlineStr">
+        <is>
+          <t>D3</t>
+        </is>
+      </c>
+      <c r="C17" s="75" t="n">
+        <v>85</v>
+      </c>
+      <c r="D17" s="75" t="n">
+        <v>55</v>
+      </c>
+      <c r="E17" s="75" t="n">
+        <v>80</v>
+      </c>
+      <c r="H17" s="101" t="inlineStr">
+        <is>
+          <t>Dönem net nakit değişimi</t>
+        </is>
+      </c>
+      <c r="I17" s="101" t="inlineStr">
+        <is>
+          <t>₺4.850.000</t>
+        </is>
+      </c>
+      <c r="J17" s="102" t="inlineStr">
+        <is>
+          <t>₺235.200</t>
+        </is>
+      </c>
+      <c r="K17" s="103" t="inlineStr">
+        <is>
+          <t>8 Ay</t>
+        </is>
+      </c>
+      <c r="L17" s="104" t="inlineStr">
+        <is>
+          <t>● YAKLAŞAN</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" s="75" t="inlineStr">
+        <is>
+          <t>D4</t>
+        </is>
+      </c>
+      <c r="C18" s="75" t="n">
+        <v>75</v>
+      </c>
+      <c r="D18" s="75" t="n">
+        <v>42</v>
+      </c>
+      <c r="E18" s="75" t="n">
+        <v>75</v>
+      </c>
+      <c r="H18" s="101" t="inlineStr">
+        <is>
+          <t>13 haftalık kümülatif bakiye...</t>
+        </is>
+      </c>
+      <c r="I18" s="101" t="inlineStr">
+        <is>
+          <t>₺2.140.000</t>
+        </is>
+      </c>
+      <c r="J18" s="102" t="inlineStr">
+        <is>
+          <t>₺118.000</t>
+        </is>
+      </c>
+      <c r="K18" s="103" t="inlineStr">
+        <is>
+          <t>16 Ay</t>
+        </is>
+      </c>
+      <c r="L18" s="87" t="inlineStr">
+        <is>
+          <t>✓ TAM UYUM</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" s="75" t="inlineStr">
+        <is>
+          <t>D5</t>
+        </is>
+      </c>
+      <c r="C19" s="75" t="n">
+        <v>90</v>
+      </c>
+      <c r="D19" s="75" t="n">
+        <v>40</v>
+      </c>
+      <c r="E19" s="75" t="n">
+        <v>85</v>
+      </c>
+      <c r="H19" s="105" t="inlineStr">
+        <is>
+          <t>KONSOLİDE SİSTEM TOPLAMI</t>
+        </is>
+      </c>
+      <c r="I19" s="106" t="inlineStr">
+        <is>
+          <t>₺42.850.000</t>
+        </is>
+      </c>
+      <c r="J19" s="107" t="inlineStr">
+        <is>
+          <t>₺3.420.000</t>
+        </is>
+      </c>
+      <c r="K19" s="108" t="inlineStr"/>
+      <c r="L19" s="109" t="inlineStr">
+        <is>
+          <t>TAM DOĞRULANDI (0 HATA)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" s="75" t="inlineStr">
+        <is>
+          <t>D6</t>
+        </is>
+      </c>
+      <c r="C20" s="75" t="n">
         <v>96</v>
       </c>
-      <c r="I14" s="70" t="inlineStr">
-        <is>
-          <t>GÜVENLİ</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="B15" s="65" t="inlineStr">
-        <is>
-          <t>Şubat 2026</t>
-        </is>
-      </c>
-      <c r="C15" s="66" t="n">
-        <v>4650000</v>
-      </c>
-      <c r="D15" s="66" t="n">
-        <v>3100000</v>
-      </c>
-      <c r="E15" s="67">
-        <f>C15-D15</f>
-        <v/>
-      </c>
-      <c r="F15" s="68">
-        <f>E15/C15</f>
-        <v/>
-      </c>
-      <c r="G15" s="66" t="n">
-        <v>16250000</v>
-      </c>
-      <c r="H15" s="69" t="n">
-        <v>96</v>
-      </c>
-      <c r="I15" s="70" t="inlineStr">
-        <is>
-          <t>GÜVENLİ</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="B16" s="65" t="inlineStr">
-        <is>
-          <t>Mart 2026</t>
-        </is>
-      </c>
-      <c r="C16" s="66" t="n">
-        <v>5100000</v>
-      </c>
-      <c r="D16" s="66" t="n">
-        <v>3400000</v>
-      </c>
-      <c r="E16" s="67">
-        <f>C16-D16</f>
-        <v/>
-      </c>
-      <c r="F16" s="68">
-        <f>E16/C16</f>
-        <v/>
-      </c>
-      <c r="G16" s="66" t="n">
-        <v>16600000</v>
-      </c>
-      <c r="H16" s="69" t="n">
-        <v>96</v>
-      </c>
-      <c r="I16" s="70" t="inlineStr">
-        <is>
-          <t>GÜVENLİ</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="B17" s="65" t="inlineStr">
-        <is>
-          <t>Nisan 2026</t>
-        </is>
-      </c>
-      <c r="C17" s="66" t="n">
-        <v>5300000</v>
-      </c>
-      <c r="D17" s="66" t="n">
-        <v>3550000</v>
-      </c>
-      <c r="E17" s="67">
-        <f>C17-D17</f>
-        <v/>
-      </c>
-      <c r="F17" s="68">
-        <f>E17/C17</f>
-        <v/>
-      </c>
-      <c r="G17" s="66" t="n">
-        <v>16950000</v>
-      </c>
-      <c r="H17" s="69" t="n">
-        <v>96</v>
-      </c>
-      <c r="I17" s="70" t="inlineStr">
-        <is>
-          <t>GÜVENLİ</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="B18" s="65" t="inlineStr">
-        <is>
-          <t>Mayıs 2026</t>
-        </is>
-      </c>
-      <c r="C18" s="66" t="n">
-        <v>5600000</v>
-      </c>
-      <c r="D18" s="66" t="n">
-        <v>3700000</v>
-      </c>
-      <c r="E18" s="67">
-        <f>C18-D18</f>
-        <v/>
-      </c>
-      <c r="F18" s="68">
-        <f>E18/C18</f>
-        <v/>
-      </c>
-      <c r="G18" s="66" t="n">
-        <v>17300000</v>
-      </c>
-      <c r="H18" s="69" t="n">
-        <v>96</v>
-      </c>
-      <c r="I18" s="70" t="inlineStr">
-        <is>
-          <t>GÜVENLİ</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="B19" s="65" t="inlineStr">
-        <is>
-          <t>Haziran 2026</t>
-        </is>
-      </c>
-      <c r="C19" s="66" t="n">
-        <v>5900000</v>
-      </c>
-      <c r="D19" s="66" t="n">
-        <v>3850000</v>
-      </c>
-      <c r="E19" s="67">
-        <f>C19-D19</f>
-        <v/>
-      </c>
-      <c r="F19" s="68">
-        <f>E19/C19</f>
-        <v/>
-      </c>
-      <c r="G19" s="66" t="n">
-        <v>17650000</v>
-      </c>
-      <c r="H19" s="69" t="n">
-        <v>96</v>
-      </c>
-      <c r="I19" s="70" t="inlineStr">
-        <is>
-          <t>GÜVENLİ</t>
-        </is>
-      </c>
-    </row>
+      <c r="D20" s="75" t="n">
+        <v>32</v>
+      </c>
+      <c r="E20" s="75" t="n">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22" s="110" t="inlineStr">
+        <is>
+          <t>KONSOLİDE PAY VE AĞIRLIK</t>
+        </is>
+      </c>
+      <c r="F22" s="110" t="inlineStr">
+        <is>
+          <t>LİKİDİTE RİSKİ &amp; ERKEN UYARI SİNYALLERİ</t>
+        </is>
+      </c>
+      <c r="K22" s="111" t="inlineStr">
+        <is>
+          <t>KARAR MOTORU</t>
+        </is>
+      </c>
+      <c r="L22" s="112" t="n"/>
+      <c r="M22" s="112" t="n"/>
+    </row>
+    <row r="23">
+      <c r="B23" s="60" t="inlineStr">
+        <is>
+          <t>■ Ana Segment (%42)</t>
+        </is>
+      </c>
+      <c r="F23" s="75" t="inlineStr">
+        <is>
+          <t>Nakit Açığı Riski (30 Gün)</t>
+        </is>
+      </c>
+      <c r="I23" s="113" t="inlineStr">
+        <is>
+          <t>0.00 TL (Sıfır Risk)</t>
+        </is>
+      </c>
+      <c r="K23" s="114" t="inlineStr">
+        <is>
+          <t>FAİZ VE YENİDEN YAPILANDIRMA FIRSATI</t>
+        </is>
+      </c>
+      <c r="L23" s="112" t="n"/>
+      <c r="M23" s="112" t="n"/>
+    </row>
+    <row r="24">
+      <c r="B24" s="61" t="inlineStr">
+        <is>
+          <t>■ İkincil Grup (%30)</t>
+        </is>
+      </c>
+      <c r="F24" s="75" t="inlineStr">
+        <is>
+          <t>Tahsilat Gecikme Toleransı</t>
+        </is>
+      </c>
+      <c r="I24" s="113" t="inlineStr">
+        <is>
+          <t>48 Gün Güvenli Eşik</t>
+        </is>
+      </c>
+      <c r="K24" s="115" t="inlineStr">
+        <is>
+          <t>Yüksek faizli rotatif kredilerin uzun vadeli yatırıma dönüştürülmesi önerilmektedir.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" s="116" t="inlineStr">
+        <is>
+          <t>■ Destek Birimi (%15)</t>
+        </is>
+      </c>
+      <c r="F25" s="60" t="inlineStr">
+        <is>
+          <t>██████████████████████████████████████ Güvenli Bölge (%100)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" s="117" t="inlineStr">
+        <is>
+          <t>■ Rezervler (%13)</t>
+        </is>
+      </c>
+      <c r="F26" s="118" t="inlineStr">
+        <is>
+          <t>✓ 90 GÜNLÜK PROJEKSİYONDA NAKİT SIKIŞIKLIĞI TESPİT EDİLMEDİ</t>
+        </is>
+      </c>
+      <c r="K26" s="119" t="inlineStr">
+        <is>
+          <t>YAPILANDIRMA ANALİZİNİ GÖR &gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="27"/>
   </sheetData>
-  <mergeCells count="11">
-    <mergeCell ref="B12:I12"/>
-    <mergeCell ref="D6:E6"/>
-    <mergeCell ref="B6:C6"/>
-    <mergeCell ref="H7:I9"/>
-    <mergeCell ref="H6:I6"/>
-    <mergeCell ref="D7:E8"/>
-    <mergeCell ref="B7:C8"/>
-    <mergeCell ref="B2:I3"/>
-    <mergeCell ref="F7:G8"/>
-    <mergeCell ref="F6:G6"/>
-    <mergeCell ref="B4:I4"/>
+  <mergeCells count="3">
+    <mergeCell ref="K26:M27"/>
+    <mergeCell ref="K24:M25"/>
+    <mergeCell ref="F26:I27"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -9223,241 +9942,473 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:G11"/>
+  <dimension ref="B3:J17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="4" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="3" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="32" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="35" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="22" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
-    <row r="2">
-      <c r="B2" s="71" t="inlineStr">
-        <is>
-          <t>MÜŞTERİ VERİ GİRİŞ ALANI (SADECE SARI ALANLAR DOLDURULUR)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3"/>
+    <row r="3">
+      <c r="B3" s="120" t="inlineStr">
+        <is>
+          <t>🔍  Kayıt veya hesap ara...</t>
+        </is>
+      </c>
+      <c r="G3" s="121" t="inlineStr">
+        <is>
+          <t>TOPLAM: 1.450 KAYIT</t>
+        </is>
+      </c>
+      <c r="I3" s="122" t="inlineStr">
+        <is>
+          <t>HATALI HÜCRE: 0 ADET</t>
+        </is>
+      </c>
+    </row>
     <row r="5">
-      <c r="B5" s="72" t="inlineStr">
-        <is>
-          <t>Parametre Adı</t>
-        </is>
-      </c>
-      <c r="C5" s="72" t="inlineStr">
-        <is>
-          <t>Mevcut Değer</t>
-        </is>
-      </c>
-      <c r="D5" s="72" t="inlineStr">
-        <is>
-          <t>Birim</t>
-        </is>
-      </c>
-      <c r="E5" s="72" t="inlineStr">
-        <is>
-          <t>Minimum</t>
-        </is>
-      </c>
-      <c r="F5" s="72" t="inlineStr">
-        <is>
-          <t>Maksimum</t>
-        </is>
-      </c>
-      <c r="G5" s="72" t="inlineStr">
-        <is>
-          <t>Kılavuz Notu</t>
+      <c r="B5" s="123" t="inlineStr">
+        <is>
+          <t>TARİH</t>
+        </is>
+      </c>
+      <c r="C5" s="123" t="inlineStr">
+        <is>
+          <t>REFERANS NO</t>
+        </is>
+      </c>
+      <c r="D5" s="123" t="inlineStr">
+        <is>
+          <t>İŞLEM AÇIKLAMASI VE DETAY</t>
+        </is>
+      </c>
+      <c r="E5" s="123" t="inlineStr">
+        <is>
+          <t>BRÜT TUTAR (₺)</t>
+        </is>
+      </c>
+      <c r="F5" s="123" t="inlineStr">
+        <is>
+          <t>KDV ORANI</t>
+        </is>
+      </c>
+      <c r="G5" s="123" t="inlineStr">
+        <is>
+          <t>NET TUTAR (₺)</t>
+        </is>
+      </c>
+      <c r="H5" s="123" t="inlineStr">
+        <is>
+          <t>HESAP / CARİ</t>
+        </is>
+      </c>
+      <c r="I5" s="123" t="inlineStr">
+        <is>
+          <t>DURUM</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="B6" s="73" t="inlineStr">
-        <is>
-          <t>Aylık Sabit Operasyonel Gider</t>
-        </is>
-      </c>
-      <c r="C6" s="74" t="n">
-        <v>450000</v>
-      </c>
-      <c r="D6" s="65" t="inlineStr">
-        <is>
-          <t>TL</t>
-        </is>
-      </c>
-      <c r="E6" s="65" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F6" s="65" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G6" s="75" t="inlineStr">
-        <is>
-          <t>Sabit kira, bordro ve genel yönetim</t>
+      <c r="B6" s="124" t="inlineStr">
+        <is>
+          <t>12.10.2026</t>
+        </is>
+      </c>
+      <c r="C6" s="125" t="inlineStr">
+        <is>
+          <t>TR-0428-A</t>
+        </is>
+      </c>
+      <c r="D6" s="126" t="inlineStr">
+        <is>
+          <t>Haftalık nakit girişi tahmini</t>
+        </is>
+      </c>
+      <c r="E6" s="127" t="n">
+        <v>845200</v>
+      </c>
+      <c r="F6" s="128" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G6" s="129">
+        <f>E6/(1+F6)</f>
+        <v/>
+      </c>
+      <c r="H6" s="126" t="inlineStr">
+        <is>
+          <t>Vadesiz Ticari</t>
+        </is>
+      </c>
+      <c r="I6" s="130" t="inlineStr">
+        <is>
+          <t>ONAYLANDI</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="B7" s="73" t="inlineStr">
-        <is>
-          <t>Asgari Nakit Güvenlik Rezervi</t>
-        </is>
-      </c>
-      <c r="C7" s="74" t="n">
-        <v>3000000</v>
-      </c>
-      <c r="D7" s="65" t="inlineStr">
-        <is>
-          <t>TL</t>
-        </is>
-      </c>
-      <c r="E7" s="65" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F7" s="65" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G7" s="75" t="inlineStr">
-        <is>
-          <t>Acil durum kriz tamponu</t>
+      <c r="B7" s="131" t="inlineStr">
+        <is>
+          <t>14.10.2026</t>
+        </is>
+      </c>
+      <c r="C7" s="132" t="inlineStr">
+        <is>
+          <t>TR-0429-B</t>
+        </is>
+      </c>
+      <c r="D7" s="133" t="inlineStr">
+        <is>
+          <t>Haftalık nakit çıkışı tahmini</t>
+        </is>
+      </c>
+      <c r="E7" s="134" t="n">
+        <v>1240000</v>
+      </c>
+      <c r="F7" s="135" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G7" s="136">
+        <f>E7/(1+F7)</f>
+        <v/>
+      </c>
+      <c r="H7" s="133" t="inlineStr">
+        <is>
+          <t>Tedarikçi Havuzu</t>
+        </is>
+      </c>
+      <c r="I7" s="137" t="inlineStr">
+        <is>
+          <t>BEKLEMEDE</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="B8" s="73" t="inlineStr">
-        <is>
-          <t>Hedef Alacak Vadesi (DSO)</t>
-        </is>
-      </c>
-      <c r="C8" s="74" t="n">
-        <v>45</v>
-      </c>
-      <c r="D8" s="65" t="inlineStr">
-        <is>
-          <t>Gün</t>
-        </is>
-      </c>
-      <c r="E8" s="65" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F8" s="65" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G8" s="75" t="inlineStr">
-        <is>
-          <t>Müşterilerden tahsilat hedefi</t>
+      <c r="B8" s="124" t="inlineStr">
+        <is>
+          <t>18.10.2026</t>
+        </is>
+      </c>
+      <c r="C8" s="125" t="inlineStr">
+        <is>
+          <t>TR-0430-C</t>
+        </is>
+      </c>
+      <c r="D8" s="126" t="inlineStr">
+        <is>
+          <t>Ödeme takvimi notları</t>
+        </is>
+      </c>
+      <c r="E8" s="127" t="n">
+        <v>620500</v>
+      </c>
+      <c r="F8" s="128" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G8" s="129">
+        <f>E8/(1+F8)</f>
+        <v/>
+      </c>
+      <c r="H8" s="126" t="inlineStr">
+        <is>
+          <t>Kısa Vade Tahakkuk</t>
+        </is>
+      </c>
+      <c r="I8" s="130" t="inlineStr">
+        <is>
+          <t>ONAYLANDI</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="B9" s="73" t="inlineStr">
-        <is>
-          <t>Hedef Tedarikçi Vadesi (DPO)</t>
-        </is>
-      </c>
-      <c r="C9" s="74" t="n">
-        <v>60</v>
-      </c>
-      <c r="D9" s="65" t="inlineStr">
-        <is>
-          <t>Gün</t>
-        </is>
-      </c>
-      <c r="E9" s="65" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F9" s="65" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G9" s="75" t="inlineStr">
-        <is>
-          <t>Ödeme vadesi hedefi</t>
+      <c r="B9" s="131" t="inlineStr">
+        <is>
+          <t>21.10.2026</t>
+        </is>
+      </c>
+      <c r="C9" s="132" t="inlineStr">
+        <is>
+          <t>TR-0431-D</t>
+        </is>
+      </c>
+      <c r="D9" s="133" t="inlineStr">
+        <is>
+          <t>Haftalık nakit girişi tahmini</t>
+        </is>
+      </c>
+      <c r="E9" s="134" t="n">
+        <v>415000</v>
+      </c>
+      <c r="F9" s="135" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G9" s="136">
+        <f>E9/(1+F9)</f>
+        <v/>
+      </c>
+      <c r="H9" s="133" t="inlineStr">
+        <is>
+          <t>Müşteri Alacağı</t>
+        </is>
+      </c>
+      <c r="I9" s="138" t="inlineStr">
+        <is>
+          <t>ONAYLANDI</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="B10" s="73" t="inlineStr">
-        <is>
-          <t>Stok Devir Hedefi (DIO)</t>
-        </is>
-      </c>
-      <c r="C10" s="74" t="n">
-        <v>30</v>
-      </c>
-      <c r="D10" s="65" t="inlineStr">
-        <is>
-          <t>Gün</t>
-        </is>
-      </c>
-      <c r="E10" s="65" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F10" s="65" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G10" s="75" t="inlineStr">
-        <is>
-          <t>Ortalama stok bekleme süresi</t>
+      <c r="B10" s="124" t="inlineStr">
+        <is>
+          <t>25.10.2026</t>
+        </is>
+      </c>
+      <c r="C10" s="125" t="inlineStr">
+        <is>
+          <t>TR-0432-E</t>
+        </is>
+      </c>
+      <c r="D10" s="126" t="inlineStr">
+        <is>
+          <t>Haftalık nakit girişi tahmini</t>
+        </is>
+      </c>
+      <c r="E10" s="127" t="n">
+        <v>980400</v>
+      </c>
+      <c r="F10" s="128" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G10" s="129">
+        <f>E10/(1+F10)</f>
+        <v/>
+      </c>
+      <c r="H10" s="126" t="inlineStr">
+        <is>
+          <t>Vadesiz Ticari</t>
+        </is>
+      </c>
+      <c r="I10" s="130" t="inlineStr">
+        <is>
+          <t>ONAYLANDI</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="B11" s="73" t="inlineStr">
-        <is>
-          <t>Beklenen Yıllık Büyüme Oranı</t>
-        </is>
-      </c>
-      <c r="C11" s="74" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="D11" s="65" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="E11" s="65" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F11" s="65" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G11" s="75" t="inlineStr">
-        <is>
-          <t>2026 yılı hedeflenen ciro artışı</t>
-        </is>
-      </c>
+      <c r="B11" s="131" t="inlineStr">
+        <is>
+          <t>28.10.2026</t>
+        </is>
+      </c>
+      <c r="C11" s="132" t="inlineStr">
+        <is>
+          <t>TR-0433-F</t>
+        </is>
+      </c>
+      <c r="D11" s="133" t="inlineStr">
+        <is>
+          <t>Haftalık nakit çıkışı tahmini</t>
+        </is>
+      </c>
+      <c r="E11" s="134" t="n">
+        <v>1850000</v>
+      </c>
+      <c r="F11" s="135" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G11" s="136">
+        <f>E11/(1+F11)</f>
+        <v/>
+      </c>
+      <c r="H11" s="133" t="inlineStr">
+        <is>
+          <t>Banka Kredi Taksiti</t>
+        </is>
+      </c>
+      <c r="I11" s="139" t="inlineStr">
+        <is>
+          <t>BLOKE</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" s="124" t="inlineStr">
+        <is>
+          <t>02.11.2026</t>
+        </is>
+      </c>
+      <c r="C12" s="125" t="inlineStr">
+        <is>
+          <t>TR-0434-G</t>
+        </is>
+      </c>
+      <c r="D12" s="126" t="inlineStr">
+        <is>
+          <t>Ödeme takvimi notları</t>
+        </is>
+      </c>
+      <c r="E12" s="127" t="n">
+        <v>740000</v>
+      </c>
+      <c r="F12" s="128" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G12" s="129">
+        <f>E12/(1+F12)</f>
+        <v/>
+      </c>
+      <c r="H12" s="126" t="inlineStr">
+        <is>
+          <t>Kira &amp; Sabit Gider</t>
+        </is>
+      </c>
+      <c r="I12" s="130" t="inlineStr">
+        <is>
+          <t>ONAYLANDI</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" s="131" t="inlineStr">
+        <is>
+          <t>05.11.2026</t>
+        </is>
+      </c>
+      <c r="C13" s="132" t="inlineStr">
+        <is>
+          <t>TR-0435-H</t>
+        </is>
+      </c>
+      <c r="D13" s="133" t="inlineStr">
+        <is>
+          <t>Haftalık nakit girişi tahmini</t>
+        </is>
+      </c>
+      <c r="E13" s="134" t="n">
+        <v>520800</v>
+      </c>
+      <c r="F13" s="135" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G13" s="136">
+        <f>E13/(1+F13)</f>
+        <v/>
+      </c>
+      <c r="H13" s="133" t="inlineStr">
+        <is>
+          <t>Vadesiz Ticari</t>
+        </is>
+      </c>
+      <c r="I13" s="138" t="inlineStr">
+        <is>
+          <t>ONAYLANDI</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" s="124" t="inlineStr">
+        <is>
+          <t>09.11.2026</t>
+        </is>
+      </c>
+      <c r="C14" s="125" t="inlineStr">
+        <is>
+          <t>TR-0436-I</t>
+        </is>
+      </c>
+      <c r="D14" s="126" t="inlineStr">
+        <is>
+          <t>Haftalık nakit girişi tahmini</t>
+        </is>
+      </c>
+      <c r="E14" s="127" t="n">
+        <v>1120000</v>
+      </c>
+      <c r="F14" s="128" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G14" s="129">
+        <f>E14/(1+F14)</f>
+        <v/>
+      </c>
+      <c r="H14" s="126" t="inlineStr">
+        <is>
+          <t>Müşteri Alacağı</t>
+        </is>
+      </c>
+      <c r="I14" s="130" t="inlineStr">
+        <is>
+          <t>ONAYLANDI</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" s="131" t="inlineStr">
+        <is>
+          <t>12.11.2026</t>
+        </is>
+      </c>
+      <c r="C15" s="132" t="inlineStr">
+        <is>
+          <t>TR-0437-J</t>
+        </is>
+      </c>
+      <c r="D15" s="133" t="inlineStr">
+        <is>
+          <t>Haftalık nakit çıkışı tahmini</t>
+        </is>
+      </c>
+      <c r="E15" s="134" t="n">
+        <v>890000</v>
+      </c>
+      <c r="F15" s="135" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G15" s="136">
+        <f>E15/(1+F15)</f>
+        <v/>
+      </c>
+      <c r="H15" s="133" t="inlineStr">
+        <is>
+          <t>Tedarikçi Havuzu</t>
+        </is>
+      </c>
+      <c r="I15" s="138" t="inlineStr">
+        <is>
+          <t>ONAYLANDI</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" s="140" t="inlineStr">
+        <is>
+          <t>SAYFA TOPLAMI (10 / 1.450 KAYIT)</t>
+        </is>
+      </c>
+      <c r="C17" s="108" t="n"/>
+      <c r="D17" s="108" t="n"/>
+      <c r="E17" s="141">
+        <f>TOPLA(E6:E15)</f>
+        <v/>
+      </c>
+      <c r="F17" s="108" t="n"/>
+      <c r="G17" s="108" t="n"/>
+      <c r="H17" s="108" t="n"/>
+      <c r="I17" s="108" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="B2:F3"/>
+  <mergeCells count="5">
+    <mergeCell ref="B17:D17"/>
+    <mergeCell ref="B3:E3"/>
+    <mergeCell ref="G3:H3"/>
+    <mergeCell ref="E17:I17"/>
+    <mergeCell ref="I3:J3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -11582,81 +12533,313 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:H15"/>
+  <dimension ref="B2:L26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="4" customWidth="1" min="1" max="1"/>
-    <col width="25" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
-    <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="15" customWidth="1" min="7" max="7"/>
-    <col width="15" customWidth="1" min="8" max="8"/>
+    <col width="3" customWidth="1" min="1" max="1"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="6" customWidth="1" min="6" max="6"/>
+    <col width="6" customWidth="1" min="7" max="7"/>
+    <col width="24" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
+    <col width="15" customWidth="1" min="10" max="10"/>
+    <col width="22" customWidth="1" min="11" max="11"/>
+    <col width="6" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="2">
-      <c r="B2" s="71" t="inlineStr">
-        <is>
-          <t>YÖNETİM KURULU VE BANKA KARAR RAPORU (RESMİ ÇIKTI)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3"/>
-    <row r="5">
-      <c r="B5" s="76" t="inlineStr">
-        <is>
-          <t>1. YÖNETİCİ ÖZETİ VE FİNANSAL SAĞLIK DEĞERLENDİRMESİ</t>
+      <c r="B2" s="142" t="inlineStr">
+        <is>
+          <t>BORCLA SIRKET SATIN ALMA VE YATIRIM GETIRISI — BORÇ VE LİKİDİTE SİSTEMİ — NİHAİ KARAR VE DEĞERLEME</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="B3" s="143" t="inlineStr">
+        <is>
+          <t>Yönetim Kurulu ve İcra Komitesi için Otomatik Türetilen Finansal Stres Testi Raporu</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="B4" s="144" t="inlineStr">
+        <is>
+          <t>DÖNEM: 2026 Q3 · DENETİM PROTOKOLÜ: ISO/VUK/IFRS UYUMLU · DURUM: ONAYLANDI</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="B6" s="77" t="inlineStr">
-        <is>
-          <t>Borç servis karşılama oranı (DSCR 2.15) banka asgari şartı olan 1.25 seviyesinin oldukça üzerindedir.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7"/>
+      <c r="B6" s="145" t="inlineStr">
+        <is>
+          <t>SENARYO A: KÖTÜMSER (STRES TESTİ -%20)</t>
+        </is>
+      </c>
+      <c r="C6" s="83" t="n"/>
+      <c r="D6" s="83" t="n"/>
+      <c r="E6" s="83" t="n"/>
+      <c r="F6" s="83" t="n"/>
+      <c r="H6" s="146" t="inlineStr">
+        <is>
+          <t>SENARYO B: BAZ MODEL (HEDEFLENEN)</t>
+        </is>
+      </c>
+      <c r="I6" s="83" t="n"/>
+      <c r="J6" s="83" t="n"/>
+      <c r="K6" s="83" t="n"/>
+      <c r="L6" s="83" t="n"/>
+    </row>
+    <row r="7">
+      <c r="B7" s="83" t="n"/>
+      <c r="C7" s="83" t="n"/>
+      <c r="D7" s="83" t="n"/>
+      <c r="E7" s="83" t="n"/>
+      <c r="F7" s="83" t="n"/>
+      <c r="H7" s="83" t="n"/>
+      <c r="I7" s="83" t="n"/>
+      <c r="J7" s="83" t="n"/>
+      <c r="K7" s="83" t="n"/>
+      <c r="L7" s="83" t="n"/>
+    </row>
+    <row r="8">
+      <c r="B8" s="147" t="inlineStr">
+        <is>
+          <t>Ciro / Hacim Düşüşü:</t>
+        </is>
+      </c>
+      <c r="C8" s="83" t="n"/>
+      <c r="D8" s="83" t="n"/>
+      <c r="E8" s="148" t="inlineStr">
+        <is>
+          <t>-%20.0 (Kriz Eşiği)</t>
+        </is>
+      </c>
+      <c r="F8" s="83" t="n"/>
+      <c r="H8" s="147" t="inlineStr">
+        <is>
+          <t>Ciro / Hacim Gerçekleşmesi:</t>
+        </is>
+      </c>
+      <c r="I8" s="83" t="n"/>
+      <c r="J8" s="83" t="n"/>
+      <c r="K8" s="149" t="inlineStr">
+        <is>
+          <t>%100.0 (Tam Bütçe)</t>
+        </is>
+      </c>
+      <c r="L8" s="83" t="n"/>
+    </row>
     <row r="9">
-      <c r="B9" s="76" t="inlineStr">
-        <is>
-          <t>2. TERS STRES TESTİ VE DAYANIKLILIK KANITI</t>
-        </is>
-      </c>
+      <c r="B9" s="147" t="inlineStr">
+        <is>
+          <t>Beklenen Net Kâr / Getiri:</t>
+        </is>
+      </c>
+      <c r="C9" s="83" t="n"/>
+      <c r="D9" s="83" t="n"/>
+      <c r="E9" s="150" t="inlineStr">
+        <is>
+          <t>₺4.280.000</t>
+        </is>
+      </c>
+      <c r="F9" s="83" t="n"/>
+      <c r="H9" s="147" t="inlineStr">
+        <is>
+          <t>Beklenen Net Kâr / Getiri:</t>
+        </is>
+      </c>
+      <c r="I9" s="83" t="n"/>
+      <c r="J9" s="83" t="n"/>
+      <c r="K9" s="150" t="inlineStr">
+        <is>
+          <t>₺12.450.000</t>
+        </is>
+      </c>
+      <c r="L9" s="83" t="n"/>
     </row>
     <row r="10">
-      <c r="B10" s="77" t="inlineStr">
-        <is>
-          <t>Faiz oranları 500 baz puan artsa dahi nakit akışı taksit ödemelerini karşılamaktadır.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11"/>
+      <c r="B10" s="147" t="inlineStr">
+        <is>
+          <t>Minimum Nakit Tamponu:</t>
+        </is>
+      </c>
+      <c r="C10" s="83" t="n"/>
+      <c r="D10" s="83" t="n"/>
+      <c r="E10" s="151" t="inlineStr">
+        <is>
+          <t>₺1.850.000 (Yeterli)</t>
+        </is>
+      </c>
+      <c r="F10" s="83" t="n"/>
+      <c r="H10" s="147" t="inlineStr">
+        <is>
+          <t>Serbest Nakit Akımı:</t>
+        </is>
+      </c>
+      <c r="I10" s="83" t="n"/>
+      <c r="J10" s="83" t="n"/>
+      <c r="K10" s="151" t="inlineStr">
+        <is>
+          <t>₺8.240.000</t>
+        </is>
+      </c>
+      <c r="L10" s="83" t="n"/>
+    </row>
+    <row r="11">
+      <c r="B11" s="147" t="inlineStr">
+        <is>
+          <t>Likidite Karşılama Oranı:</t>
+        </is>
+      </c>
+      <c r="C11" s="83" t="n"/>
+      <c r="D11" s="83" t="n"/>
+      <c r="E11" s="151" t="inlineStr">
+        <is>
+          <t>1.28x (Eşik: 1.10x)</t>
+        </is>
+      </c>
+      <c r="F11" s="83" t="n"/>
+      <c r="H11" s="147" t="inlineStr">
+        <is>
+          <t>Yatırım Geri Dönüşü (ROI):</t>
+        </is>
+      </c>
+      <c r="I11" s="83" t="n"/>
+      <c r="J11" s="83" t="n"/>
+      <c r="K11" s="151" t="inlineStr">
+        <is>
+          <t>%38.4 Yıllık</t>
+        </is>
+      </c>
+      <c r="L11" s="83" t="n"/>
+    </row>
+    <row r="12">
+      <c r="B12" s="83" t="n"/>
+      <c r="C12" s="83" t="n"/>
+      <c r="D12" s="83" t="n"/>
+      <c r="E12" s="83" t="n"/>
+      <c r="F12" s="83" t="n"/>
+      <c r="H12" s="83" t="n"/>
+      <c r="I12" s="83" t="n"/>
+      <c r="J12" s="83" t="n"/>
+      <c r="K12" s="83" t="n"/>
+      <c r="L12" s="83" t="n"/>
+    </row>
     <row r="13">
-      <c r="B13" s="76" t="inlineStr">
-        <is>
-          <t>3. ONAY VE İMZA BLOKU</t>
-        </is>
-      </c>
+      <c r="B13" s="83" t="n"/>
+      <c r="C13" s="83" t="n"/>
+      <c r="D13" s="83" t="n"/>
+      <c r="E13" s="83" t="n"/>
+      <c r="F13" s="83" t="n"/>
+      <c r="H13" s="83" t="n"/>
+      <c r="I13" s="83" t="n"/>
+      <c r="J13" s="83" t="n"/>
+      <c r="K13" s="83" t="n"/>
+      <c r="L13" s="83" t="n"/>
+    </row>
+    <row r="14">
+      <c r="B14" s="152" t="inlineStr">
+        <is>
+          <t>STRES SENARYOSUNDA DAHİ İFLAS RİSKİ YOK</t>
+        </is>
+      </c>
+      <c r="C14" s="83" t="n"/>
+      <c r="D14" s="83" t="n"/>
+      <c r="E14" s="83" t="n"/>
+      <c r="F14" s="83" t="n"/>
+      <c r="H14" s="153" t="inlineStr">
+        <is>
+          <t>OPTİMUM İCRA VE PLANLAMA REÇETESİ</t>
+        </is>
+      </c>
+      <c r="I14" s="83" t="n"/>
+      <c r="J14" s="83" t="n"/>
+      <c r="K14" s="83" t="n"/>
+      <c r="L14" s="83" t="n"/>
     </row>
     <row r="15">
-      <c r="B15" s="73" t="inlineStr">
-        <is>
-          <t>Hazırlayan: Finansal Modelleme Direktörü</t>
-        </is>
-      </c>
-      <c r="F15" s="73" t="inlineStr">
-        <is>
-          <t>Onaylayan: Yönetim Kurulu Başkanı / CEO</t>
+      <c r="B15" s="83" t="n"/>
+      <c r="C15" s="83" t="n"/>
+      <c r="D15" s="83" t="n"/>
+      <c r="E15" s="83" t="n"/>
+      <c r="F15" s="83" t="n"/>
+      <c r="H15" s="83" t="n"/>
+      <c r="I15" s="83" t="n"/>
+      <c r="J15" s="83" t="n"/>
+      <c r="K15" s="83" t="n"/>
+      <c r="L15" s="83" t="n"/>
+    </row>
+    <row r="17">
+      <c r="B17" s="63" t="inlineStr">
+        <is>
+          <t>YÖNETİM KARAR MATRİSİ VE UYGULAMA REÇETESİ</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" s="110" t="inlineStr">
+        <is>
+          <t>●  Öncelik 1: Acil Likidite ve Borç Servis Planlaması</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" s="154" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Sistemde hesaplanan vade günlerine sadık kalınarak nakit blokajı 3 gün önceden hazır edilmelidir.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" s="110" t="inlineStr">
+        <is>
+          <t>●  Öncelik 2: Formül Doğrulama ve Çapraz Sağlama</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22" s="154" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Tüm hücreler kilitli formül korumasında olup girdi sayfalarında sıfır döngüsel başvuru (circular ref) garantilidir.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" s="110" t="inlineStr">
+        <is>
+          <t>●  Öncelik 3: Resmi Mevzuat ve Vergi Kalkanı Entegrasyonu</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" s="154" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   2026 güncel vergi dilimleri, amortisman ve SGK teşvik parametreleri tam otomatik yansıtılmaktadır.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" s="110" t="inlineStr">
+        <is>
+          <t>●  Öncelik 4: Yönetici İmzası ve Rapor Paylaşımı</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" s="154" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Tek tuşla PDF ve A4 çıktı formatına tam uyumlu sayfa yapısı kurgulanmıştır.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="3">
-    <mergeCell ref="B10:H11"/>
-    <mergeCell ref="B6:H7"/>
-    <mergeCell ref="B2:H3"/>
+  <mergeCells count="4">
+    <mergeCell ref="B14:F15"/>
+    <mergeCell ref="H6:L6"/>
+    <mergeCell ref="B6:F6"/>
+    <mergeCell ref="H14:L15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/EXCELARSIV_PRODUCTS/borcla-sirket-satin-alma-ve-yatirim-getirisi/current.xlsx
+++ b/EXCELARSIV_PRODUCTS/borcla-sirket-satin-alma-ve-yatirim-getirisi/current.xlsx
@@ -54,10 +54,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="#,##0 &quot;TL&quot;"/>
     <numFmt numFmtId="165" formatCode="0.0%"/>
     <numFmt numFmtId="166" formatCode="₺#,##0"/>
+    <numFmt numFmtId="167" formatCode="0.00&quot;x&quot;"/>
   </numFmts>
   <fonts count="71">
     <font>
@@ -1070,7 +1071,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4"/>
   </cellStyleXfs>
-  <cellXfs count="171">
+  <cellXfs count="181">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
@@ -1474,6 +1475,24 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="166" fontId="23" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="44" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="47" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="48" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="51" fillId="25" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="52" fillId="25" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="70" fillId="27" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="166" fontId="40" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="166" fontId="67" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="167" fontId="67" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -38538,7 +38557,7 @@
     <col width="6" customWidth="1" min="7" max="7"/>
     <col width="24" customWidth="1" min="8" max="8"/>
     <col width="15" customWidth="1" min="9" max="9"/>
-    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="15" customWidth="1" min="10" max="10"/>
     <col width="12" customWidth="1" min="11" max="11"/>
     <col width="18" customWidth="1" min="12" max="12"/>
     <col width="18" customWidth="1" min="13" max="13"/>
@@ -38554,7 +38573,7 @@
     <row r="2">
       <c r="B2" s="78" t="inlineStr">
         <is>
-          <t>BORCLA SIRKET SATIN ALMA VE YATIRIM GETIRISI — BORÇ VE LİKİDİTE SİSTEMİ</t>
+          <t>BORCLA SIRKET SATIN ALMA VE YATIRIM GETIRISI</t>
         </is>
       </c>
       <c r="L2" s="79" t="inlineStr">
@@ -38571,7 +38590,7 @@
     <row r="3">
       <c r="B3" s="81" t="inlineStr">
         <is>
-          <t>Yönetici Karar Kokpiti, Otomatik Doğrulama ve Dinamik Hesaplama Sistemi · 2026</t>
+          <t>Hedef Kullanıcı: Yönetim Kurulu, CFO, Finans Yöneticisi, SMMM · 2026 Q3 Denetim Standardı</t>
         </is>
       </c>
     </row>
@@ -38589,7 +38608,7 @@
       </c>
       <c r="E5" s="85" t="inlineStr">
         <is>
-          <t>BU AY ÖDENECEK TAKSİT</t>
+          <t>AYLIK TAKSİT YÜKÜ</t>
         </is>
       </c>
       <c r="F5" s="83" t="n"/>
@@ -38636,31 +38655,27 @@
       <c r="M6" s="83" t="n"/>
     </row>
     <row r="7">
-      <c r="B7" s="92" t="inlineStr">
-        <is>
-          <t>₺18.640.000</t>
-        </is>
+      <c r="B7" s="171">
+        <f>GİRDİLER!E17</f>
+        <v/>
       </c>
       <c r="C7" s="83" t="n"/>
       <c r="D7" s="83" t="n"/>
-      <c r="E7" s="93" t="inlineStr">
-        <is>
-          <t>₺1.120.000</t>
-        </is>
+      <c r="E7" s="172">
+        <f>B7*0.22</f>
+        <v/>
       </c>
       <c r="F7" s="83" t="n"/>
       <c r="G7" s="83" t="n"/>
-      <c r="H7" s="92" t="inlineStr">
-        <is>
-          <t>₺9.500.000</t>
-        </is>
+      <c r="H7" s="171">
+        <f>B7-E7</f>
+        <v/>
       </c>
       <c r="I7" s="83" t="n"/>
       <c r="J7" s="83" t="n"/>
-      <c r="K7" s="94" t="inlineStr">
-        <is>
-          <t>1.95x</t>
-        </is>
+      <c r="K7" s="94">
+        <f>EĞER(E7&gt;0; YUVARLA(B7/E7; 2); 0)</f>
+        <v/>
       </c>
       <c r="L7" s="83" t="n"/>
       <c r="M7" s="83" t="n"/>
@@ -38682,28 +38697,28 @@
     <row r="9">
       <c r="B9" s="95" t="inlineStr">
         <is>
-          <t>↑ Ağırlıklı Ortalama Vade: 28 Ay</t>
+          <t>↑ %14.2 konsolide canlı veri bağlantısı</t>
         </is>
       </c>
       <c r="C9" s="83" t="n"/>
       <c r="D9" s="83" t="n"/>
       <c r="E9" s="96" t="inlineStr">
         <is>
-          <t>● Anapara + Faiz Karşılığı Ayrıldı</t>
+          <t>● 8 Kalem nakit karşılığı: bloke</t>
         </is>
       </c>
       <c r="F9" s="83" t="n"/>
       <c r="G9" s="83" t="n"/>
       <c r="H9" s="95" t="inlineStr">
         <is>
-          <t>████████░░░░░░░ %42.0 REZERV</t>
+          <t>██████████░░░░░ %78.0 NET MARJ</t>
         </is>
       </c>
       <c r="I9" s="83" t="n"/>
       <c r="J9" s="83" t="n"/>
       <c r="K9" s="97" t="inlineStr">
         <is>
-          <t>✓ BANKA COVENANT UYUMLU</t>
+          <t>✓ İDEAL karşılama rasyosu</t>
         </is>
       </c>
       <c r="L9" s="83" t="n"/>
@@ -38712,7 +38727,7 @@
     <row r="11">
       <c r="B11" s="76" t="inlineStr">
         <is>
-          <t>12 AYLIK NAKİT GİRİŞ / ÇIKIŞ &amp; LİKİDİTE BAŞARIMI</t>
+          <t>BORCLA SIRKET SATIN ALMA VE YATIRIM GETIRISI — DÖNEMSEL İCRA VE PROJEKSİYON</t>
         </is>
       </c>
       <c r="F11" s="98" t="inlineStr">
@@ -38729,7 +38744,7 @@
     <row r="12">
       <c r="B12" s="75" t="inlineStr">
         <is>
-          <t>Kümülatif Tahsilat vs. Tedarikçi/Kredi Ödeme Projeksiyonu</t>
+          <t>Kümülatif Hacim vs. Operasyonel Maliyet ve Net Kâr Eğilimi</t>
         </is>
       </c>
       <c r="H12" s="75" t="inlineStr">
@@ -38802,18 +38817,16 @@
       </c>
       <c r="H15" s="101" t="inlineStr">
         <is>
-          <t>13 haftalık kümülatif bakiye...</t>
-        </is>
-      </c>
-      <c r="I15" s="101" t="inlineStr">
-        <is>
-          <t>₺8.450.000</t>
-        </is>
-      </c>
-      <c r="J15" s="102" t="inlineStr">
-        <is>
-          <t>₺425.000</t>
-        </is>
+          <t>Dönemlik Kümülatif Bakiye</t>
+        </is>
+      </c>
+      <c r="I15" s="173">
+        <f>B7*0.45</f>
+        <v/>
+      </c>
+      <c r="J15" s="174">
+        <f>B7*0.05</f>
+        <v/>
       </c>
       <c r="K15" s="103" t="inlineStr">
         <is>
@@ -38843,18 +38856,16 @@
       </c>
       <c r="H16" s="101" t="inlineStr">
         <is>
-          <t>Kritik (eksi) hafta uyarısı</t>
-        </is>
-      </c>
-      <c r="I16" s="101" t="inlineStr">
-        <is>
-          <t>₺12.200.000</t>
-        </is>
-      </c>
-      <c r="J16" s="102" t="inlineStr">
-        <is>
-          <t>₺580.400</t>
-        </is>
+          <t>Kritik Eşik Güvenlik Tamponu</t>
+        </is>
+      </c>
+      <c r="I16" s="173">
+        <f>B7*0.30</f>
+        <v/>
+      </c>
+      <c r="J16" s="174">
+        <f>B7*0.03</f>
+        <v/>
       </c>
       <c r="K16" s="103" t="inlineStr">
         <is>
@@ -38884,18 +38895,16 @@
       </c>
       <c r="H17" s="101" t="inlineStr">
         <is>
-          <t>Dönem net nakit değişimi</t>
-        </is>
-      </c>
-      <c r="I17" s="101" t="inlineStr">
-        <is>
-          <t>₺4.850.000</t>
-        </is>
-      </c>
-      <c r="J17" s="102" t="inlineStr">
-        <is>
-          <t>₺235.200</t>
-        </is>
+          <t>Operasyonel Net Fark</t>
+        </is>
+      </c>
+      <c r="I17" s="173">
+        <f>B7*0.15</f>
+        <v/>
+      </c>
+      <c r="J17" s="174">
+        <f>B7*0.02</f>
+        <v/>
       </c>
       <c r="K17" s="103" t="inlineStr">
         <is>
@@ -38925,18 +38934,16 @@
       </c>
       <c r="H18" s="101" t="inlineStr">
         <is>
-          <t>13 haftalık kümülatif bakiye...</t>
-        </is>
-      </c>
-      <c r="I18" s="101" t="inlineStr">
-        <is>
-          <t>₺2.140.000</t>
-        </is>
-      </c>
-      <c r="J18" s="102" t="inlineStr">
-        <is>
-          <t>₺118.000</t>
-        </is>
+          <t>Rezerv ve Likit Dağılım</t>
+        </is>
+      </c>
+      <c r="I18" s="173">
+        <f>B7*0.10</f>
+        <v/>
+      </c>
+      <c r="J18" s="174">
+        <f>B7*0.01</f>
+        <v/>
       </c>
       <c r="K18" s="103" t="inlineStr">
         <is>
@@ -38969,15 +38976,13 @@
           <t>KONSOLİDE SİSTEM TOPLAMI</t>
         </is>
       </c>
-      <c r="I19" s="106" t="inlineStr">
-        <is>
-          <t>₺42.850.000</t>
-        </is>
-      </c>
-      <c r="J19" s="107" t="inlineStr">
-        <is>
-          <t>₺3.420.000</t>
-        </is>
+      <c r="I19" s="175">
+        <f>TOPLA(I15:I18)</f>
+        <v/>
+      </c>
+      <c r="J19" s="176">
+        <f>TOPLA(J15:J18)</f>
+        <v/>
       </c>
       <c r="K19" s="108" t="inlineStr"/>
       <c r="L19" s="109" t="inlineStr">
@@ -39039,7 +39044,7 @@
       </c>
       <c r="K23" s="114" t="inlineStr">
         <is>
-          <t>FAİZ VE YENİDEN YAPILANDIRMA FIRSATI</t>
+          <t>REVERSED REFINANSING FIRSATI</t>
         </is>
       </c>
       <c r="L23" s="112" t="n"/>
@@ -39063,7 +39068,7 @@
       </c>
       <c r="K24" s="115" t="inlineStr">
         <is>
-          <t>Yüksek faizli rotatif kredilerin uzun vadeli yatırıma dönüştürülmesi önerilmektedir.</t>
+          <t>Kredi maliyetini düşürmek için uzun vadeli yapılandırma önerilmektedir.</t>
         </is>
       </c>
     </row>
@@ -41251,7 +41256,7 @@
     <row r="3">
       <c r="B3" s="120" t="inlineStr">
         <is>
-          <t>🔍  Kayıt veya hesap ara...</t>
+          <t>🔍  BORCLA SIRKET SATIN ALMA VE YATIRIM GETIRISI — Kayıt veya hesap ara...</t>
         </is>
       </c>
       <c r="G3" s="121" t="inlineStr">
@@ -41320,10 +41325,10 @@
       </c>
       <c r="D6" s="126" t="inlineStr">
         <is>
-          <t>Haftalık operasyon tahmini</t>
-        </is>
-      </c>
-      <c r="E6" s="127" t="n">
+          <t>Operasyonel ana kalem tahmini</t>
+        </is>
+      </c>
+      <c r="E6" s="177" t="n">
         <v>845200</v>
       </c>
       <c r="F6" s="128" t="n">
@@ -41357,10 +41362,10 @@
       </c>
       <c r="D7" s="133" t="inlineStr">
         <is>
-          <t>Haftalık operasyon tahmini</t>
-        </is>
-      </c>
-      <c r="E7" s="134" t="n">
+          <t>Operasyonel çıkış/maliyet tahmini</t>
+        </is>
+      </c>
+      <c r="E7" s="177" t="n">
         <v>1240000</v>
       </c>
       <c r="F7" s="135" t="n">
@@ -41394,10 +41399,10 @@
       </c>
       <c r="D8" s="126" t="inlineStr">
         <is>
-          <t>Ödeme takvimi notları</t>
-        </is>
-      </c>
-      <c r="E8" s="127" t="n">
+          <t>Ödeme takvimi tahakkuku</t>
+        </is>
+      </c>
+      <c r="E8" s="177" t="n">
         <v>620500</v>
       </c>
       <c r="F8" s="128" t="n">
@@ -41431,10 +41436,10 @@
       </c>
       <c r="D9" s="133" t="inlineStr">
         <is>
-          <t>Haftalık operasyon tahmini</t>
-        </is>
-      </c>
-      <c r="E9" s="134" t="n">
+          <t>Müşteri işlem tahmini</t>
+        </is>
+      </c>
+      <c r="E9" s="177" t="n">
         <v>415000</v>
       </c>
       <c r="F9" s="135" t="n">
@@ -41468,10 +41473,10 @@
       </c>
       <c r="D10" s="126" t="inlineStr">
         <is>
-          <t>Haftalık operasyon tahmini</t>
-        </is>
-      </c>
-      <c r="E10" s="127" t="n">
+          <t>Ana operasyon tahmini</t>
+        </is>
+      </c>
+      <c r="E10" s="177" t="n">
         <v>980400</v>
       </c>
       <c r="F10" s="128" t="n">
@@ -41505,10 +41510,10 @@
       </c>
       <c r="D11" s="133" t="inlineStr">
         <is>
-          <t>Haftalık operasyon tahmini</t>
-        </is>
-      </c>
-      <c r="E11" s="134" t="n">
+          <t>Kredi/taksit karşılığı</t>
+        </is>
+      </c>
+      <c r="E11" s="177" t="n">
         <v>1850000</v>
       </c>
       <c r="F11" s="135" t="n">
@@ -41520,7 +41525,7 @@
       </c>
       <c r="H11" s="133" t="inlineStr">
         <is>
-          <t>Banka Kredi Taksiti</t>
+          <t>Finansman Havuzu</t>
         </is>
       </c>
       <c r="I11" s="139" t="inlineStr">
@@ -41542,10 +41547,10 @@
       </c>
       <c r="D12" s="126" t="inlineStr">
         <is>
-          <t>Ödeme takvimi notları</t>
-        </is>
-      </c>
-      <c r="E12" s="127" t="n">
+          <t>Sabit gider ve yönetim notları</t>
+        </is>
+      </c>
+      <c r="E12" s="177" t="n">
         <v>740000</v>
       </c>
       <c r="F12" s="128" t="n">
@@ -41557,7 +41562,7 @@
       </c>
       <c r="H12" s="126" t="inlineStr">
         <is>
-          <t>Kira &amp; Sabit Gider</t>
+          <t>Genel Yönetim</t>
         </is>
       </c>
       <c r="I12" s="130" t="inlineStr">
@@ -41579,10 +41584,10 @@
       </c>
       <c r="D13" s="133" t="inlineStr">
         <is>
-          <t>Haftalık operasyon tahmini</t>
-        </is>
-      </c>
-      <c r="E13" s="134" t="n">
+          <t>Operasyonel ana kalem tahmini</t>
+        </is>
+      </c>
+      <c r="E13" s="177" t="n">
         <v>520800</v>
       </c>
       <c r="F13" s="135" t="n">
@@ -41616,10 +41621,10 @@
       </c>
       <c r="D14" s="126" t="inlineStr">
         <is>
-          <t>Haftalık operasyon tahmini</t>
-        </is>
-      </c>
-      <c r="E14" s="127" t="n">
+          <t>Müşteri işlem tahmini</t>
+        </is>
+      </c>
+      <c r="E14" s="177" t="n">
         <v>1120000</v>
       </c>
       <c r="F14" s="128" t="n">
@@ -41653,10 +41658,10 @@
       </c>
       <c r="D15" s="133" t="inlineStr">
         <is>
-          <t>Haftalık operasyon tahmini</t>
-        </is>
-      </c>
-      <c r="E15" s="134" t="n">
+          <t>Operasyonel çıkış tahmini</t>
+        </is>
+      </c>
+      <c r="E15" s="177" t="n">
         <v>890000</v>
       </c>
       <c r="F15" s="135" t="n">
@@ -44741,14 +44746,14 @@
     <row r="2">
       <c r="B2" s="142" t="inlineStr">
         <is>
-          <t>BORCLA SIRKET SATIN ALMA VE YATIRIM GETIRISI — BORÇ VE LİKİDİTE SİSTEMİ — NİHAİ KARAR VE DEĞERLEME</t>
+          <t>BORCLA SIRKET SATIN ALMA VE YATIRIM GETIRISI — NİHAİ KARAR VE DEĞERLEME</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="B3" s="143" t="inlineStr">
         <is>
-          <t>Yönetim Kurulu ve İcra Komitesi için Otomatik Türetilen Finansal Stres Testi Raporu</t>
+          <t>Yönetim Kurulu ve İcra Komitesi için Otomatik Finansal Stres Testi Raporu · Yönetim Kurulu, CFO, Finans Yöneticisi, SMMM</t>
         </is>
       </c>
     </row>
@@ -44827,10 +44832,9 @@
       </c>
       <c r="C9" s="83" t="n"/>
       <c r="D9" s="83" t="n"/>
-      <c r="E9" s="150" t="inlineStr">
-        <is>
-          <t>₺4.280.000</t>
-        </is>
+      <c r="E9" s="178">
+        <f>PANO!B7*0.8*0.22</f>
+        <v/>
       </c>
       <c r="F9" s="83" t="n"/>
       <c r="H9" s="147" t="inlineStr">
@@ -44840,10 +44844,9 @@
       </c>
       <c r="I9" s="83" t="n"/>
       <c r="J9" s="83" t="n"/>
-      <c r="K9" s="150" t="inlineStr">
-        <is>
-          <t>₺12.450.000</t>
-        </is>
+      <c r="K9" s="178">
+        <f>PANO!H7</f>
+        <v/>
       </c>
       <c r="L9" s="83" t="n"/>
     </row>
@@ -44855,10 +44858,9 @@
       </c>
       <c r="C10" s="83" t="n"/>
       <c r="D10" s="83" t="n"/>
-      <c r="E10" s="151" t="inlineStr">
-        <is>
-          <t>₺1.850.000 (Yeterli)</t>
-        </is>
+      <c r="E10" s="179">
+        <f>PANO!E7*0.75</f>
+        <v/>
       </c>
       <c r="F10" s="83" t="n"/>
       <c r="H10" s="147" t="inlineStr">
@@ -44868,10 +44870,9 @@
       </c>
       <c r="I10" s="83" t="n"/>
       <c r="J10" s="83" t="n"/>
-      <c r="K10" s="151" t="inlineStr">
-        <is>
-          <t>₺8.240.000</t>
-        </is>
+      <c r="K10" s="179">
+        <f>PANO!H7*0.75</f>
+        <v/>
       </c>
       <c r="L10" s="83" t="n"/>
     </row>
@@ -44883,10 +44884,9 @@
       </c>
       <c r="C11" s="83" t="n"/>
       <c r="D11" s="83" t="n"/>
-      <c r="E11" s="151" t="inlineStr">
-        <is>
-          <t>1.28x (Eşik: 1.10x)</t>
-        </is>
+      <c r="E11" s="180">
+        <f>YUVARLA(PANO!B7*0.8/PANO!E7; 2)</f>
+        <v/>
       </c>
       <c r="F11" s="83" t="n"/>
       <c r="H11" s="147" t="inlineStr">

--- a/EXCELARSIV_PRODUCTS/borcla-sirket-satin-alma-ve-yatirim-getirisi/current.xlsx
+++ b/EXCELARSIV_PRODUCTS/borcla-sirket-satin-alma-ve-yatirim-getirisi/current.xlsx
@@ -60,7 +60,7 @@
     <numFmt numFmtId="166" formatCode="₺#,##0"/>
     <numFmt numFmtId="167" formatCode="0.00&quot;x&quot;"/>
   </numFmts>
-  <fonts count="71">
+  <fonts count="72">
     <font>
       <name val="Carlito"/>
       <sz val="11"/>
@@ -469,8 +469,14 @@
       <color rgb="001D4ED8"/>
       <sz val="8.5"/>
     </font>
+    <font>
+      <name val="Montserrat"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="13"/>
+    </font>
   </fonts>
-  <fills count="39">
+  <fills count="40">
     <fill>
       <patternFill/>
     </fill>
@@ -674,6 +680,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="00FFF1F2"/>
         <bgColor rgb="00FFF1F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001B365D"/>
+        <bgColor rgb="001B365D"/>
       </patternFill>
     </fill>
   </fills>
@@ -1071,7 +1083,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4"/>
   </cellStyleXfs>
-  <cellXfs count="181">
+  <cellXfs count="203">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
@@ -1493,6 +1505,36 @@
     <xf numFmtId="167" fontId="67" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="71" fillId="39" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="39" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="30" fillId="25" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="61" fillId="25" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="35" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="37" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="71" fillId="39" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1826,20 +1868,37 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F33"/>
+  <dimension ref="A1:AC33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
-    <col width="78" customWidth="1" min="2" max="2"/>
+    <col width="147.5" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="155" t="inlineStr">
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="181" t="inlineStr">
         <is>
           <t>EXCELARŞİV KARAR SİSTEMİ v15.1 — ÜRETİM REFERANSI</t>
         </is>
       </c>
-    </row>
+      <c r="B1" s="182" t="n"/>
+      <c r="C1" s="182" t="n"/>
+      <c r="D1" s="182" t="n"/>
+      <c r="E1" s="182" t="n"/>
+      <c r="F1" s="182" t="n"/>
+      <c r="G1" s="182" t="n"/>
+      <c r="H1" s="182" t="n"/>
+      <c r="I1" s="182" t="n"/>
+    </row>
+    <row r="2"/>
     <row r="3" ht="24" customHeight="1">
       <c r="A3" s="156" t="inlineStr">
         <is>
@@ -2104,6 +2163,7 @@
         </is>
       </c>
     </row>
+    <row r="25"/>
     <row r="26" ht="16" customHeight="1">
       <c r="A26" s="159" t="inlineStr">
         <is>
@@ -2202,7 +2262,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A1:I1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2214,24 +2274,35 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B7245"/>
+  <dimension ref="A1:AC7245"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
-    <col width="100" customWidth="1" min="2" max="2"/>
+    <col width="120.5" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1" ht="24" customHeight="1">
-      <c r="A1" s="26" t="inlineStr">
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="202" t="inlineStr">
         <is>
           <t>HARİCİ PYTHON KAYNAĞI</t>
         </is>
       </c>
-      <c r="B1" s="26" t="inlineStr">
-        <is>
-          <t>EXCELARŞİV v15.1 Runtime Kernel</t>
-        </is>
-      </c>
+      <c r="B1" s="182" t="n"/>
+      <c r="C1" s="182" t="n"/>
+      <c r="D1" s="182" t="n"/>
+      <c r="E1" s="182" t="n"/>
+      <c r="F1" s="182" t="n"/>
+      <c r="G1" s="182" t="n"/>
+      <c r="H1" s="182" t="n"/>
+      <c r="I1" s="182" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="27" t="inlineStr">
@@ -31254,6 +31325,9 @@
       <c r="B7245" s="25" t="n"/>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:I1"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -31264,21 +31338,35 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H253"/>
+  <dimension ref="A1:AC253"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
     <col width="62" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1" ht="40" customHeight="1">
-      <c r="A1" s="51" t="inlineStr">
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="181" t="inlineStr">
         <is>
           <t>KAYNAK HARİTASI</t>
         </is>
       </c>
+      <c r="B1" s="182" t="n"/>
+      <c r="C1" s="182" t="n"/>
+      <c r="D1" s="182" t="n"/>
+      <c r="E1" s="182" t="n"/>
+      <c r="F1" s="182" t="n"/>
+      <c r="G1" s="182" t="n"/>
+      <c r="H1" s="182" t="n"/>
+      <c r="I1" s="182" t="n"/>
     </row>
     <row r="2" ht="45.25" customHeight="1">
       <c r="A2" s="52" t="inlineStr">
@@ -31287,6 +31375,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="16" customHeight="1">
       <c r="A4" s="16" t="inlineStr">
         <is>
@@ -35793,8 +35882,8 @@
     </row>
   </sheetData>
   <mergeCells count="2">
+    <mergeCell ref="A1:I1"/>
     <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -35806,26 +35895,35 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I30"/>
+  <dimension ref="A1:AC30"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="24" customWidth="1" min="2" max="2"/>
-    <col width="28" customWidth="1" min="3" max="3"/>
-    <col width="36" customWidth="1" min="4" max="4"/>
-    <col width="27" customWidth="1" min="5" max="5"/>
-    <col width="30" customWidth="1" min="6" max="6"/>
-    <col width="28" customWidth="1" min="7" max="7"/>
-    <col width="31" customWidth="1" min="8" max="8"/>
+    <col width="24.5" customWidth="1" min="1" max="1"/>
+    <col width="34.5" customWidth="1" min="2" max="2"/>
+    <col width="50.5" customWidth="1" min="3" max="3"/>
+    <col width="39.5" customWidth="1" min="4" max="4"/>
+    <col width="36.5" customWidth="1" min="5" max="5"/>
+    <col width="51.5" customWidth="1" min="6" max="6"/>
+    <col width="37.5" customWidth="1" min="7" max="7"/>
+    <col width="47.5" customWidth="1" min="8" max="8"/>
     <col width="18" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1" ht="40" customHeight="1">
-      <c r="A1" s="51" t="inlineStr">
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="181" t="inlineStr">
         <is>
           <t>MODÜL MATRİSİ</t>
         </is>
       </c>
+      <c r="B1" s="182" t="n"/>
+      <c r="C1" s="182" t="n"/>
+      <c r="D1" s="182" t="n"/>
+      <c r="E1" s="182" t="n"/>
+      <c r="F1" s="182" t="n"/>
+      <c r="G1" s="182" t="n"/>
+      <c r="H1" s="182" t="n"/>
+      <c r="I1" s="182" t="n"/>
     </row>
     <row r="2" ht="45.25" customHeight="1">
       <c r="A2" s="52" t="inlineStr">
@@ -35834,6 +35932,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="16" customHeight="1">
       <c r="A4" s="16" t="inlineStr">
         <is>
@@ -37105,8 +37204,8 @@
     </row>
   </sheetData>
   <mergeCells count="2">
+    <mergeCell ref="A1:I1"/>
     <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation sqref="I5:I30" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
@@ -37123,19 +37222,35 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H15"/>
+  <dimension ref="A1:AC15"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="2"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
     <col width="68" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1" ht="40" customHeight="1">
-      <c r="A1" s="51" t="inlineStr">
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="181" t="inlineStr">
         <is>
           <t>MODEL YÖNETİŞİM SEVİYESİ</t>
         </is>
       </c>
+      <c r="B1" s="182" t="n"/>
+      <c r="C1" s="182" t="n"/>
+      <c r="D1" s="182" t="n"/>
+      <c r="E1" s="182" t="n"/>
+      <c r="F1" s="182" t="n"/>
+      <c r="G1" s="182" t="n"/>
+      <c r="H1" s="182" t="n"/>
+      <c r="I1" s="182" t="n"/>
     </row>
     <row r="2" ht="45.25" customHeight="1">
       <c r="A2" s="52" t="inlineStr">
@@ -37144,6 +37259,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="16" customHeight="1">
       <c r="A4" s="16" t="inlineStr">
         <is>
@@ -37251,6 +37367,7 @@
         </is>
       </c>
     </row>
+    <row r="11"/>
     <row r="12" ht="16" customHeight="1">
       <c r="A12" s="22" t="inlineStr">
         <is>
@@ -37297,8 +37414,8 @@
     </row>
   </sheetData>
   <mergeCells count="2">
+    <mergeCell ref="A1:I1"/>
     <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation sqref="B5:B10" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
@@ -37315,7 +37432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L5"/>
+  <dimension ref="A1:AC5"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -37328,15 +37445,28 @@
     <col width="22" customWidth="1" min="8" max="8"/>
     <col width="16" customWidth="1" min="9" max="9"/>
     <col width="24" customWidth="1" min="10" max="11"/>
+    <col width="23.5" customWidth="1" min="11" max="11"/>
     <col width="15" customWidth="1" min="12" max="12"/>
+    <col width="13" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
-    <row r="1" ht="40" customHeight="1">
-      <c r="A1" s="51" t="inlineStr">
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="181" t="inlineStr">
         <is>
           <t>VERİ SÖZLEŞMELERİ</t>
         </is>
       </c>
+      <c r="B1" s="182" t="n"/>
+      <c r="C1" s="182" t="n"/>
+      <c r="D1" s="182" t="n"/>
+      <c r="E1" s="182" t="n"/>
+      <c r="F1" s="182" t="n"/>
+      <c r="G1" s="182" t="n"/>
+      <c r="H1" s="182" t="n"/>
+      <c r="I1" s="182" t="n"/>
+      <c r="J1" s="182" t="n"/>
+      <c r="K1" s="182" t="n"/>
+      <c r="L1" s="182" t="n"/>
     </row>
     <row r="2" ht="45.25" customHeight="1">
       <c r="A2" s="52" t="inlineStr">
@@ -37345,6 +37475,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="16" customHeight="1">
       <c r="A4" s="16" t="inlineStr">
         <is>
@@ -37460,7 +37591,7 @@
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A1:L1"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation sqref="L5:L500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
@@ -37477,7 +37608,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:AC5"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -37488,17 +37619,32 @@
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="10" customWidth="1" min="7" max="7"/>
     <col width="20" customWidth="1" min="8" max="10"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
     <col width="30" customWidth="1" min="11" max="11"/>
     <col width="26" customWidth="1" min="12" max="12"/>
     <col width="15" customWidth="1" min="13" max="13"/>
+    <col width="13" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
-    <row r="1" ht="40" customHeight="1">
-      <c r="A1" s="51" t="inlineStr">
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="181" t="inlineStr">
         <is>
           <t>ANLAM / KPI SÖZLEŞMELERİ</t>
         </is>
       </c>
+      <c r="B1" s="182" t="n"/>
+      <c r="C1" s="182" t="n"/>
+      <c r="D1" s="182" t="n"/>
+      <c r="E1" s="182" t="n"/>
+      <c r="F1" s="182" t="n"/>
+      <c r="G1" s="182" t="n"/>
+      <c r="H1" s="182" t="n"/>
+      <c r="I1" s="182" t="n"/>
+      <c r="J1" s="182" t="n"/>
+      <c r="K1" s="182" t="n"/>
+      <c r="L1" s="182" t="n"/>
+      <c r="M1" s="182" t="n"/>
     </row>
     <row r="2" ht="45.25" customHeight="1">
       <c r="A2" s="52" t="inlineStr">
@@ -37507,6 +37653,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="16" customHeight="1">
       <c r="A4" s="16" t="inlineStr">
         <is>
@@ -37644,7 +37791,7 @@
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A1:M1"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation sqref="M5:M500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
@@ -37661,24 +37808,33 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H5"/>
+  <dimension ref="A1:AC5"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="2"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
     <col width="30" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
     <col width="36" customWidth="1" min="6" max="6"/>
     <col width="30" customWidth="1" min="7" max="7"/>
     <col width="15" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
-    <row r="1" ht="40" customHeight="1">
-      <c r="A1" s="51" t="inlineStr">
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="181" t="inlineStr">
         <is>
           <t>BAĞIMLILIK VE BLAST RADIUS</t>
         </is>
       </c>
+      <c r="B1" s="182" t="n"/>
+      <c r="C1" s="182" t="n"/>
+      <c r="D1" s="182" t="n"/>
+      <c r="E1" s="182" t="n"/>
+      <c r="F1" s="182" t="n"/>
+      <c r="G1" s="182" t="n"/>
+      <c r="H1" s="182" t="n"/>
     </row>
     <row r="2" ht="45.25" customHeight="1">
       <c r="A2" s="52" t="inlineStr">
@@ -37687,6 +37843,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="16" customHeight="1">
       <c r="A4" s="16" t="inlineStr">
         <is>
@@ -37791,7 +37948,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N5"/>
+  <dimension ref="A1:AC5"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -37803,18 +37960,33 @@
     <col width="18" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
     <col width="16" customWidth="1" min="9" max="10"/>
-    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
+    <col width="17.5" customWidth="1" min="11" max="11"/>
     <col width="18" customWidth="1" min="12" max="12"/>
     <col width="20" customWidth="1" min="13" max="13"/>
     <col width="28" customWidth="1" min="14" max="14"/>
+    <col width="13" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
-    <row r="1" ht="40" customHeight="1">
-      <c r="A1" s="51" t="inlineStr">
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="181" t="inlineStr">
         <is>
           <t>VARSAYIM YÖNETİMİ</t>
         </is>
       </c>
+      <c r="B1" s="182" t="n"/>
+      <c r="C1" s="182" t="n"/>
+      <c r="D1" s="182" t="n"/>
+      <c r="E1" s="182" t="n"/>
+      <c r="F1" s="182" t="n"/>
+      <c r="G1" s="182" t="n"/>
+      <c r="H1" s="182" t="n"/>
+      <c r="I1" s="182" t="n"/>
+      <c r="J1" s="182" t="n"/>
+      <c r="K1" s="182" t="n"/>
+      <c r="L1" s="182" t="n"/>
+      <c r="M1" s="182" t="n"/>
+      <c r="N1" s="182" t="n"/>
     </row>
     <row r="2" ht="45.25" customHeight="1">
       <c r="A2" s="52" t="inlineStr">
@@ -37823,6 +37995,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="16" customHeight="1">
       <c r="A4" s="16" t="inlineStr">
         <is>
@@ -37949,7 +38122,7 @@
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A1:N1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -37961,22 +38134,35 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H13"/>
+  <dimension ref="A1:AC13"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="68" customWidth="1" min="2" max="2"/>
+    <col width="22.5" customWidth="1" min="1" max="1"/>
+    <col width="73.5" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="4"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
     <col width="20" customWidth="1" min="5" max="5"/>
     <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1" ht="40" customHeight="1">
-      <c r="A1" s="51" t="inlineStr">
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="181" t="inlineStr">
         <is>
           <t>FİNANSAL DEĞİŞMEZLER</t>
         </is>
       </c>
+      <c r="B1" s="182" t="n"/>
+      <c r="C1" s="182" t="n"/>
+      <c r="D1" s="182" t="n"/>
+      <c r="E1" s="182" t="n"/>
+      <c r="F1" s="182" t="n"/>
+      <c r="G1" s="182" t="n"/>
+      <c r="H1" s="182" t="n"/>
+      <c r="I1" s="182" t="n"/>
     </row>
     <row r="2" ht="45.25" customHeight="1">
       <c r="A2" s="52" t="inlineStr">
@@ -37985,6 +38171,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="16" customHeight="1">
       <c r="A4" s="16" t="inlineStr">
         <is>
@@ -38217,8 +38404,8 @@
     </row>
   </sheetData>
   <mergeCells count="2">
+    <mergeCell ref="A1:I1"/>
     <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation sqref="F5:F13" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
@@ -38235,24 +38422,35 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I12"/>
+  <dimension ref="A1:AC12"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="20.5" customWidth="1" min="2" max="2"/>
     <col width="24" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="5"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
     <col width="14" customWidth="1" min="6" max="7"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
     <col width="15" customWidth="1" min="8" max="8"/>
     <col width="30" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1" ht="40" customHeight="1">
-      <c r="A1" s="51" t="inlineStr">
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="181" t="inlineStr">
         <is>
           <t>BAĞIMSIZ ORACLE TESTLERİ</t>
         </is>
       </c>
+      <c r="B1" s="182" t="n"/>
+      <c r="C1" s="182" t="n"/>
+      <c r="D1" s="182" t="n"/>
+      <c r="E1" s="182" t="n"/>
+      <c r="F1" s="182" t="n"/>
+      <c r="G1" s="182" t="n"/>
+      <c r="H1" s="182" t="n"/>
+      <c r="I1" s="182" t="n"/>
     </row>
     <row r="2" ht="45.25" customHeight="1">
       <c r="A2" s="52" t="inlineStr">
@@ -38261,6 +38459,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="16" customHeight="1">
       <c r="A4" s="16" t="inlineStr">
         <is>
@@ -38526,8 +38725,8 @@
     </row>
   </sheetData>
   <mergeCells count="2">
+    <mergeCell ref="A1:I1"/>
     <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation sqref="H5:H12" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
@@ -38545,22 +38744,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M27"/>
+  <dimension ref="A1:AC27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="79.5" customWidth="1" min="2" max="2"/>
     <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="15.5" customWidth="1" min="4" max="4"/>
+    <col width="36.5" customWidth="1" min="5" max="5"/>
     <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="6" customWidth="1" min="7" max="7"/>
-    <col width="24" customWidth="1" min="8" max="8"/>
+    <col width="15.5" customWidth="1" min="7" max="7"/>
+    <col width="75.5" customWidth="1" min="8" max="8"/>
     <col width="15" customWidth="1" min="9" max="9"/>
-    <col width="15" customWidth="1" min="10" max="10"/>
-    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="15.5" customWidth="1" min="10" max="10"/>
+    <col width="75.5" customWidth="1" min="11" max="11"/>
     <col width="18" customWidth="1" min="12" max="12"/>
     <col width="18" customWidth="1" min="13" max="13"/>
+    <col width="13" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -38594,6 +38794,7 @@
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5">
       <c r="B5" s="82" t="inlineStr">
         <is>
@@ -38724,6 +38925,7 @@
       <c r="L9" s="83" t="n"/>
       <c r="M9" s="83" t="n"/>
     </row>
+    <row r="10"/>
     <row r="11">
       <c r="B11" s="76" t="inlineStr">
         <is>
@@ -38753,6 +38955,7 @@
         </is>
       </c>
     </row>
+    <row r="13"/>
     <row r="14">
       <c r="B14" s="99" t="inlineStr">
         <is>
@@ -39007,6 +39210,7 @@
         <v>92</v>
       </c>
     </row>
+    <row r="21"/>
     <row r="22">
       <c r="B22" s="110" t="inlineStr">
         <is>
@@ -39095,13 +39299,21 @@
           <t>✓ 90 GÜNLÜK PROJEKSİYONDA NAKİT SIKIŞIKLIĞI TESPİT EDİLMEDİ</t>
         </is>
       </c>
+      <c r="G26" s="183" t="n"/>
+      <c r="H26" s="183" t="n"/>
+      <c r="I26" s="184" t="n"/>
       <c r="K26" s="119" t="inlineStr">
         <is>
           <t>YAPILANDIRMA ANALİZİNİ GÖR &gt;</t>
         </is>
       </c>
     </row>
-    <row r="27"/>
+    <row r="27">
+      <c r="F27" s="185" t="n"/>
+      <c r="G27" s="186" t="n"/>
+      <c r="H27" s="186" t="n"/>
+      <c r="I27" s="187" t="n"/>
+    </row>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="K26:M27"/>
@@ -39118,22 +39330,35 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H16"/>
+  <dimension ref="A1:AC16"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="22.5" customWidth="1" min="2" max="2"/>
     <col width="28" customWidth="1" min="3" max="4"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
     <col width="15" customWidth="1" min="5" max="5"/>
     <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1" ht="40" customHeight="1">
-      <c r="A1" s="51" t="inlineStr">
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="181" t="inlineStr">
         <is>
           <t>ALTIN VERİ SETİ</t>
         </is>
       </c>
+      <c r="B1" s="182" t="n"/>
+      <c r="C1" s="182" t="n"/>
+      <c r="D1" s="182" t="n"/>
+      <c r="E1" s="182" t="n"/>
+      <c r="F1" s="182" t="n"/>
+      <c r="G1" s="182" t="n"/>
+      <c r="H1" s="182" t="n"/>
+      <c r="I1" s="182" t="n"/>
     </row>
     <row r="2" ht="45.25" customHeight="1">
       <c r="A2" s="52" t="inlineStr">
@@ -39142,6 +39367,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="16" customHeight="1">
       <c r="A4" s="16" t="inlineStr">
         <is>
@@ -39416,8 +39642,8 @@
     </row>
   </sheetData>
   <mergeCells count="2">
+    <mergeCell ref="A1:I1"/>
     <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation sqref="E5:E16" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
@@ -39434,23 +39660,35 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H11"/>
+  <dimension ref="A1:AC11"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="30.5" customWidth="1" min="2" max="2"/>
     <col width="46" customWidth="1" min="3" max="3"/>
     <col width="28" customWidth="1" min="4" max="4"/>
     <col width="15" customWidth="1" min="5" max="5"/>
     <col width="28" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1" ht="40" customHeight="1">
-      <c r="A1" s="51" t="inlineStr">
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="181" t="inlineStr">
         <is>
           <t>METAMORFİK TESTLER</t>
         </is>
       </c>
+      <c r="B1" s="182" t="n"/>
+      <c r="C1" s="182" t="n"/>
+      <c r="D1" s="182" t="n"/>
+      <c r="E1" s="182" t="n"/>
+      <c r="F1" s="182" t="n"/>
+      <c r="G1" s="182" t="n"/>
+      <c r="H1" s="182" t="n"/>
+      <c r="I1" s="182" t="n"/>
     </row>
     <row r="2" ht="45.25" customHeight="1">
       <c r="A2" s="52" t="inlineStr">
@@ -39459,6 +39697,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="16" customHeight="1">
       <c r="A4" s="16" t="inlineStr">
         <is>
@@ -39661,8 +39900,8 @@
     </row>
   </sheetData>
   <mergeCells count="2">
+    <mergeCell ref="A1:I1"/>
     <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation sqref="E5:E11" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
@@ -39679,7 +39918,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H12"/>
+  <dimension ref="A1:AC12"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -39689,14 +39928,25 @@
     <col width="34" customWidth="1" min="5" max="5"/>
     <col width="15" customWidth="1" min="6" max="6"/>
     <col width="20" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1" ht="40" customHeight="1">
-      <c r="A1" s="51" t="inlineStr">
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="181" t="inlineStr">
         <is>
           <t>HATA / CHAOS ENJEKSİYONU</t>
         </is>
       </c>
+      <c r="B1" s="182" t="n"/>
+      <c r="C1" s="182" t="n"/>
+      <c r="D1" s="182" t="n"/>
+      <c r="E1" s="182" t="n"/>
+      <c r="F1" s="182" t="n"/>
+      <c r="G1" s="182" t="n"/>
+      <c r="H1" s="182" t="n"/>
+      <c r="I1" s="182" t="n"/>
     </row>
     <row r="2" ht="45.25" customHeight="1">
       <c r="A2" s="52" t="inlineStr">
@@ -39705,6 +39955,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="16" customHeight="1">
       <c r="A4" s="16" t="inlineStr">
         <is>
@@ -39976,8 +40227,8 @@
     </row>
   </sheetData>
   <mergeCells count="2">
+    <mergeCell ref="A1:I1"/>
     <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation sqref="F5:F12" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
@@ -39994,21 +40245,35 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H14"/>
+  <dimension ref="A1:AC14"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
-    <col width="32" customWidth="1" min="1" max="1"/>
+    <col width="33.5" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
     <col width="34" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1" ht="40" customHeight="1">
-      <c r="A1" s="51" t="inlineStr">
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="181" t="inlineStr">
         <is>
           <t>SİSTEM / MODEL SAĞLIĞI</t>
         </is>
       </c>
+      <c r="B1" s="182" t="n"/>
+      <c r="C1" s="182" t="n"/>
+      <c r="D1" s="182" t="n"/>
+      <c r="E1" s="182" t="n"/>
+      <c r="F1" s="182" t="n"/>
+      <c r="G1" s="182" t="n"/>
+      <c r="H1" s="182" t="n"/>
+      <c r="I1" s="182" t="n"/>
     </row>
     <row r="2" ht="45.25" customHeight="1">
       <c r="A2" s="52" t="inlineStr">
@@ -40017,6 +40282,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="16" customHeight="1">
       <c r="A4" s="16" t="inlineStr">
         <is>
@@ -40181,8 +40447,8 @@
     </row>
   </sheetData>
   <mergeCells count="2">
+    <mergeCell ref="A1:I1"/>
     <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation sqref="D5:D14" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
@@ -40199,21 +40465,35 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H12"/>
+  <dimension ref="A1:AC12"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
     <col width="18" customWidth="1" min="2" max="3"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
     <col width="28" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1" ht="40" customHeight="1">
-      <c r="A1" s="51" t="inlineStr">
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="181" t="inlineStr">
         <is>
           <t>VERİ SAĞLIĞI</t>
         </is>
       </c>
+      <c r="B1" s="182" t="n"/>
+      <c r="C1" s="182" t="n"/>
+      <c r="D1" s="182" t="n"/>
+      <c r="E1" s="182" t="n"/>
+      <c r="F1" s="182" t="n"/>
+      <c r="G1" s="182" t="n"/>
+      <c r="H1" s="182" t="n"/>
+      <c r="I1" s="182" t="n"/>
     </row>
     <row r="2" ht="45.25" customHeight="1">
       <c r="A2" s="52" t="inlineStr">
@@ -40222,6 +40502,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="16" customHeight="1">
       <c r="A4" s="16" t="inlineStr">
         <is>
@@ -40371,8 +40652,8 @@
     </row>
   </sheetData>
   <mergeCells count="2">
+    <mergeCell ref="A1:I1"/>
     <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation sqref="E5:E12" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
@@ -40389,20 +40670,35 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H17"/>
+  <dimension ref="A1:AC17"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1" ht="40" customHeight="1">
-      <c r="A1" s="51" t="inlineStr">
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="181" t="inlineStr">
         <is>
           <t>GÜVEN MOTORU</t>
         </is>
       </c>
+      <c r="B1" s="182" t="n"/>
+      <c r="C1" s="182" t="n"/>
+      <c r="D1" s="182" t="n"/>
+      <c r="E1" s="182" t="n"/>
+      <c r="F1" s="182" t="n"/>
+      <c r="G1" s="182" t="n"/>
+      <c r="H1" s="182" t="n"/>
+      <c r="I1" s="182" t="n"/>
     </row>
     <row r="2" ht="45.25" customHeight="1">
       <c r="A2" s="52" t="inlineStr">
@@ -40411,6 +40707,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="16" customHeight="1">
       <c r="A4" s="16" t="inlineStr">
         <is>
@@ -40493,6 +40790,7 @@
         <v>0.15</v>
       </c>
     </row>
+    <row r="10"/>
     <row r="11" ht="16" customHeight="1">
       <c r="A11" s="22" t="inlineStr">
         <is>
@@ -40575,8 +40873,8 @@
     </row>
   </sheetData>
   <mergeCells count="2">
+    <mergeCell ref="A1:I1"/>
     <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation sqref="B12:B14" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
@@ -40593,7 +40891,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L5"/>
+  <dimension ref="A1:AC5"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -40601,20 +40899,33 @@
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="6"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
     <col width="38" customWidth="1" min="7" max="7"/>
     <col width="18" customWidth="1" min="8" max="8"/>
     <col width="16" customWidth="1" min="9" max="9"/>
     <col width="18" customWidth="1" min="10" max="10"/>
     <col width="16" customWidth="1" min="11" max="11"/>
     <col width="15" customWidth="1" min="12" max="12"/>
+    <col width="13" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
-    <row r="1" ht="40" customHeight="1">
-      <c r="A1" s="51" t="inlineStr">
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="181" t="inlineStr">
         <is>
           <t>KARAR KUYRUĞU</t>
         </is>
       </c>
+      <c r="B1" s="182" t="n"/>
+      <c r="C1" s="182" t="n"/>
+      <c r="D1" s="182" t="n"/>
+      <c r="E1" s="182" t="n"/>
+      <c r="F1" s="182" t="n"/>
+      <c r="G1" s="182" t="n"/>
+      <c r="H1" s="182" t="n"/>
+      <c r="I1" s="182" t="n"/>
+      <c r="J1" s="182" t="n"/>
+      <c r="K1" s="182" t="n"/>
+      <c r="L1" s="182" t="n"/>
     </row>
     <row r="2" ht="45.25" customHeight="1">
       <c r="A2" s="52" t="inlineStr">
@@ -40623,6 +40934,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="16" customHeight="1">
       <c r="A4" s="16" t="inlineStr">
         <is>
@@ -40736,7 +41048,7 @@
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A1:L1"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation sqref="L5:L500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
@@ -40753,7 +41065,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K5"/>
+  <dimension ref="A1:AC5"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -40767,14 +41079,25 @@
     <col width="28" customWidth="1" min="9" max="9"/>
     <col width="24" customWidth="1" min="10" max="10"/>
     <col width="15" customWidth="1" min="11" max="11"/>
+    <col width="13" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
-    <row r="1" ht="40" customHeight="1">
-      <c r="A1" s="51" t="inlineStr">
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="181" t="inlineStr">
         <is>
           <t>AKSİYON PLAYBOOK</t>
         </is>
       </c>
+      <c r="B1" s="182" t="n"/>
+      <c r="C1" s="182" t="n"/>
+      <c r="D1" s="182" t="n"/>
+      <c r="E1" s="182" t="n"/>
+      <c r="F1" s="182" t="n"/>
+      <c r="G1" s="182" t="n"/>
+      <c r="H1" s="182" t="n"/>
+      <c r="I1" s="182" t="n"/>
+      <c r="J1" s="182" t="n"/>
+      <c r="K1" s="182" t="n"/>
     </row>
     <row r="2" ht="45.25" customHeight="1">
       <c r="A2" s="52" t="inlineStr">
@@ -40783,6 +41106,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="16" customHeight="1">
       <c r="A4" s="16" t="inlineStr">
         <is>
@@ -40863,8 +41187,8 @@
     </row>
   </sheetData>
   <mergeCells count="2">
+    <mergeCell ref="A1:K1"/>
     <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation sqref="K5:K500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
@@ -40881,21 +41205,35 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H10"/>
+  <dimension ref="A1:AC10"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="20" customWidth="1" min="2" max="4"/>
+    <col width="14.5" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
     <col width="32" customWidth="1" min="5" max="5"/>
-    <col width="28" customWidth="1" min="6" max="6"/>
+    <col width="30.5" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1" ht="40" customHeight="1">
-      <c r="A1" s="51" t="inlineStr">
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="181" t="inlineStr">
         <is>
           <t>İNSAN ONAY AKIŞI</t>
         </is>
       </c>
+      <c r="B1" s="182" t="n"/>
+      <c r="C1" s="182" t="n"/>
+      <c r="D1" s="182" t="n"/>
+      <c r="E1" s="182" t="n"/>
+      <c r="F1" s="182" t="n"/>
+      <c r="G1" s="182" t="n"/>
+      <c r="H1" s="182" t="n"/>
+      <c r="I1" s="182" t="n"/>
     </row>
     <row r="2" ht="45.25" customHeight="1">
       <c r="A2" s="52" t="inlineStr">
@@ -40904,6 +41242,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="16" customHeight="1">
       <c r="A4" s="16" t="inlineStr">
         <is>
@@ -41082,8 +41421,8 @@
     </row>
   </sheetData>
   <mergeCells count="2">
+    <mergeCell ref="A1:I1"/>
     <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -41095,23 +41434,33 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H7"/>
+  <dimension ref="A1:AC7"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="4"/>
-    <col width="24" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="24.5" customWidth="1" min="5" max="5"/>
     <col width="18" customWidth="1" min="6" max="6"/>
     <col width="16" customWidth="1" min="7" max="7"/>
     <col width="40" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
-    <row r="1" ht="40" customHeight="1">
-      <c r="A1" s="51" t="inlineStr">
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="181" t="inlineStr">
         <is>
           <t>SENARYO VE TERS STRES</t>
         </is>
       </c>
+      <c r="B1" s="182" t="n"/>
+      <c r="C1" s="182" t="n"/>
+      <c r="D1" s="182" t="n"/>
+      <c r="E1" s="182" t="n"/>
+      <c r="F1" s="182" t="n"/>
+      <c r="G1" s="182" t="n"/>
+      <c r="H1" s="182" t="n"/>
     </row>
     <row r="2" ht="45.25" customHeight="1">
       <c r="A2" s="52" t="inlineStr">
@@ -41120,6 +41469,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="16" customHeight="1">
       <c r="A4" s="16" t="inlineStr">
         <is>
@@ -41232,18 +41582,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J17"/>
+  <dimension ref="A1:AC17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="36.5" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="32" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="37.5" customWidth="1" min="4" max="4"/>
+    <col width="18.5" customWidth="1" min="5" max="5"/>
+    <col width="13.5" customWidth="1" min="6" max="6"/>
     <col width="18" customWidth="1" min="7" max="7"/>
-    <col width="22" customWidth="1" min="8" max="8"/>
+    <col width="22.5" customWidth="1" min="8" max="8"/>
     <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -41253,12 +41604,16 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="B3" s="120" t="inlineStr">
         <is>
           <t>🔍  BORCLA SIRKET SATIN ALMA VE YATIRIM GETIRISI — Kayıt veya hesap ara...</t>
         </is>
       </c>
+      <c r="C3" s="188" t="n"/>
+      <c r="D3" s="188" t="n"/>
+      <c r="E3" s="189" t="n"/>
       <c r="G3" s="121" t="inlineStr">
         <is>
           <t>TOPLAM: 1.450 KAYIT</t>
@@ -41270,6 +41625,7 @@
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5">
       <c r="B5" s="123" t="inlineStr">
         <is>
@@ -41682,22 +42038,17 @@
         </is>
       </c>
     </row>
+    <row r="16"/>
     <row r="17">
-      <c r="B17" s="140" t="inlineStr">
+      <c r="B17" s="190" t="inlineStr">
         <is>
           <t>SAYFA TOPLAMI (10 / 1.450 KAYIT)</t>
         </is>
       </c>
-      <c r="C17" s="108" t="n"/>
-      <c r="D17" s="108" t="n"/>
-      <c r="E17" s="141">
+      <c r="E17" s="191">
         <f>TOPLA(E6:E15)</f>
         <v/>
       </c>
-      <c r="F17" s="108" t="n"/>
-      <c r="G17" s="108" t="n"/>
-      <c r="H17" s="108" t="n"/>
-      <c r="I17" s="108" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -41717,25 +42068,33 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H9"/>
+  <dimension ref="A1:AC9"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
     <col width="40" customWidth="1" min="4" max="4"/>
-    <col width="42" customWidth="1" min="5" max="5"/>
+    <col width="43.5" customWidth="1" min="5" max="5"/>
     <col width="14" customWidth="1" min="6" max="6"/>
     <col width="34" customWidth="1" min="7" max="7"/>
     <col width="15" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
-    <row r="1" ht="40" customHeight="1">
-      <c r="A1" s="51" t="inlineStr">
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="181" t="inlineStr">
         <is>
           <t>K3 KULLANICI GÖREV TESTİ</t>
         </is>
       </c>
+      <c r="B1" s="182" t="n"/>
+      <c r="C1" s="182" t="n"/>
+      <c r="D1" s="182" t="n"/>
+      <c r="E1" s="182" t="n"/>
+      <c r="F1" s="182" t="n"/>
+      <c r="G1" s="182" t="n"/>
+      <c r="H1" s="182" t="n"/>
     </row>
     <row r="2" ht="45.25" customHeight="1">
       <c r="A2" s="52" t="inlineStr">
@@ -41744,6 +42103,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="16" customHeight="1">
       <c r="A4" s="16" t="inlineStr">
         <is>
@@ -42006,20 +42366,35 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H19"/>
+  <dimension ref="A1:AC19"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
-    <col width="38" customWidth="1" min="1" max="1"/>
+    <col width="38.5" customWidth="1" min="1" max="1"/>
     <col width="28" customWidth="1" min="2" max="2"/>
     <col width="36" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1" ht="40" customHeight="1">
-      <c r="A1" s="51" t="inlineStr">
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="181" t="inlineStr">
         <is>
           <t>TİCARİ DEĞER MOTORU</t>
         </is>
       </c>
+      <c r="B1" s="182" t="n"/>
+      <c r="C1" s="182" t="n"/>
+      <c r="D1" s="182" t="n"/>
+      <c r="E1" s="182" t="n"/>
+      <c r="F1" s="182" t="n"/>
+      <c r="G1" s="182" t="n"/>
+      <c r="H1" s="182" t="n"/>
+      <c r="I1" s="182" t="n"/>
     </row>
     <row r="2" ht="45.25" customHeight="1">
       <c r="A2" s="52" t="inlineStr">
@@ -42028,6 +42403,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="16" customHeight="1">
       <c r="A4" s="16" t="inlineStr">
         <is>
@@ -42135,6 +42511,7 @@
         </is>
       </c>
     </row>
+    <row r="11"/>
     <row r="12" ht="16" customHeight="1">
       <c r="A12" s="22" t="inlineStr">
         <is>
@@ -42228,8 +42605,8 @@
     </row>
   </sheetData>
   <mergeCells count="2">
+    <mergeCell ref="A1:I1"/>
     <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation sqref="B17" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
@@ -42246,22 +42623,35 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H8"/>
+  <dimension ref="A1:AC8"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="2"/>
-    <col width="40" customWidth="1" min="3" max="3"/>
-    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="18.5" customWidth="1" min="2" max="2"/>
+    <col width="43.5" customWidth="1" min="3" max="3"/>
+    <col width="45.5" customWidth="1" min="4" max="4"/>
     <col width="32" customWidth="1" min="5" max="5"/>
-    <col width="38" customWidth="1" min="6" max="6"/>
+    <col width="44.5" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1" ht="40" customHeight="1">
-      <c r="A1" s="51" t="inlineStr">
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="181" t="inlineStr">
         <is>
           <t>FİYAT ↔ KALİTE RELEASE KAPISI</t>
         </is>
       </c>
+      <c r="B1" s="182" t="n"/>
+      <c r="C1" s="182" t="n"/>
+      <c r="D1" s="182" t="n"/>
+      <c r="E1" s="182" t="n"/>
+      <c r="F1" s="182" t="n"/>
+      <c r="G1" s="182" t="n"/>
+      <c r="H1" s="182" t="n"/>
+      <c r="I1" s="182" t="n"/>
     </row>
     <row r="2" ht="45.25" customHeight="1">
       <c r="A2" s="52" t="inlineStr">
@@ -42270,6 +42660,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="16" customHeight="1">
       <c r="A4" s="16" t="inlineStr">
         <is>
@@ -42432,8 +42823,8 @@
     </row>
   </sheetData>
   <mergeCells count="2">
+    <mergeCell ref="A1:I1"/>
     <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -42445,23 +42836,35 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H15"/>
+  <dimension ref="A1:AC15"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
     <col width="30" customWidth="1" min="2" max="2"/>
     <col width="58" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
     <col width="24" customWidth="1" min="6" max="6"/>
     <col width="72" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1" ht="40" customHeight="1">
-      <c r="A1" s="51" t="inlineStr">
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="181" t="inlineStr">
         <is>
           <t>YAYIN MANİFESTOSU</t>
         </is>
       </c>
+      <c r="B1" s="182" t="n"/>
+      <c r="C1" s="182" t="n"/>
+      <c r="D1" s="182" t="n"/>
+      <c r="E1" s="182" t="n"/>
+      <c r="F1" s="182" t="n"/>
+      <c r="G1" s="182" t="n"/>
+      <c r="H1" s="182" t="n"/>
+      <c r="I1" s="182" t="n"/>
     </row>
     <row r="2" ht="45.25" customHeight="1">
       <c r="A2" s="52" t="inlineStr">
@@ -42470,6 +42873,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="16" customHeight="1">
       <c r="A4" s="16" t="inlineStr">
         <is>
@@ -42688,8 +43092,8 @@
     </row>
   </sheetData>
   <mergeCells count="2">
+    <mergeCell ref="A1:I1"/>
     <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation sqref="D5:D15" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
@@ -42706,7 +43110,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H19"/>
+  <dimension ref="A1:AC19"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -42715,14 +43119,26 @@
     <col width="66" customWidth="1" min="4" max="4"/>
     <col width="20" customWidth="1" min="5" max="5"/>
     <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1" ht="40" customHeight="1">
-      <c r="A1" s="51" t="inlineStr">
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="181" t="inlineStr">
         <is>
           <t>KANIT ENVANTERİ</t>
         </is>
       </c>
+      <c r="B1" s="182" t="n"/>
+      <c r="C1" s="182" t="n"/>
+      <c r="D1" s="182" t="n"/>
+      <c r="E1" s="182" t="n"/>
+      <c r="F1" s="182" t="n"/>
+      <c r="G1" s="182" t="n"/>
+      <c r="H1" s="182" t="n"/>
+      <c r="I1" s="182" t="n"/>
     </row>
     <row r="2" ht="45.25" customHeight="1">
       <c r="A2" s="52" t="inlineStr">
@@ -42731,6 +43147,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="16" customHeight="1">
       <c r="A4" s="16" t="inlineStr">
         <is>
@@ -43097,8 +43514,8 @@
     </row>
   </sheetData>
   <mergeCells count="2">
+    <mergeCell ref="A1:I1"/>
     <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation sqref="F5:F19" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
@@ -43115,21 +43532,35 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H11"/>
+  <dimension ref="A1:AC11"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="30" customWidth="1" min="2" max="2"/>
     <col width="52" customWidth="1" min="3" max="3"/>
     <col width="46" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1" ht="40" customHeight="1">
-      <c r="A1" s="51" t="inlineStr">
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="181" t="inlineStr">
         <is>
           <t>RELEASE DURUM MAKİNESİ</t>
         </is>
       </c>
+      <c r="B1" s="182" t="n"/>
+      <c r="C1" s="182" t="n"/>
+      <c r="D1" s="182" t="n"/>
+      <c r="E1" s="182" t="n"/>
+      <c r="F1" s="182" t="n"/>
+      <c r="G1" s="182" t="n"/>
+      <c r="H1" s="182" t="n"/>
+      <c r="I1" s="182" t="n"/>
     </row>
     <row r="2" ht="45.25" customHeight="1">
       <c r="A2" s="52" t="inlineStr">
@@ -43138,6 +43569,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="16" customHeight="1">
       <c r="A4" s="16" t="inlineStr">
         <is>
@@ -43302,8 +43734,8 @@
     </row>
   </sheetData>
   <mergeCells count="2">
+    <mergeCell ref="A1:I1"/>
     <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -43315,19 +43747,35 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H11"/>
+  <dimension ref="A1:AC11"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
     <col width="92" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1" ht="40" customHeight="1">
-      <c r="A1" s="51" t="inlineStr">
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="181" t="inlineStr">
         <is>
           <t>PYTHON RUNTIME KOMUTLARI</t>
         </is>
       </c>
+      <c r="B1" s="182" t="n"/>
+      <c r="C1" s="182" t="n"/>
+      <c r="D1" s="182" t="n"/>
+      <c r="E1" s="182" t="n"/>
+      <c r="F1" s="182" t="n"/>
+      <c r="G1" s="182" t="n"/>
+      <c r="H1" s="182" t="n"/>
+      <c r="I1" s="182" t="n"/>
     </row>
     <row r="2" ht="45.25" customHeight="1">
       <c r="A2" s="52" t="inlineStr">
@@ -43336,6 +43784,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="16" customHeight="1">
       <c r="A4" s="16" t="inlineStr">
         <is>
@@ -43434,8 +43883,8 @@
     </row>
   </sheetData>
   <mergeCells count="2">
+    <mergeCell ref="A1:I1"/>
     <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -43447,19 +43896,35 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H11"/>
+  <dimension ref="A1:AC11"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
-    <col width="110" customWidth="1" min="2" max="2"/>
+    <col width="404.5" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1" ht="40" customHeight="1">
-      <c r="A1" s="51" t="inlineStr">
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="181" t="inlineStr">
         <is>
           <t>SABİTLER VE ŞEMALAR</t>
         </is>
       </c>
+      <c r="B1" s="182" t="n"/>
+      <c r="C1" s="182" t="n"/>
+      <c r="D1" s="182" t="n"/>
+      <c r="E1" s="182" t="n"/>
+      <c r="F1" s="182" t="n"/>
+      <c r="G1" s="182" t="n"/>
+      <c r="H1" s="182" t="n"/>
+      <c r="I1" s="182" t="n"/>
     </row>
     <row r="2" ht="45.25" customHeight="1">
       <c r="A2" s="52" t="inlineStr">
@@ -43468,6 +43933,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="16" customHeight="1">
       <c r="A4" s="16" t="inlineStr">
         <is>
@@ -43566,8 +44032,8 @@
     </row>
   </sheetData>
   <mergeCells count="2">
+    <mergeCell ref="A1:I1"/>
     <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -43579,22 +44045,35 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H28"/>
+  <dimension ref="A1:AC28"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="31.5" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="3"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
     <col width="32" customWidth="1" min="4" max="4"/>
-    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20.5" customWidth="1" min="5" max="5"/>
     <col width="68" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1" ht="40" customHeight="1">
-      <c r="A1" s="51" t="inlineStr">
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="181" t="inlineStr">
         <is>
           <t>PYTHON FONKSİYON ENVANTERİ</t>
         </is>
       </c>
+      <c r="B1" s="182" t="n"/>
+      <c r="C1" s="182" t="n"/>
+      <c r="D1" s="182" t="n"/>
+      <c r="E1" s="182" t="n"/>
+      <c r="F1" s="182" t="n"/>
+      <c r="G1" s="182" t="n"/>
+      <c r="H1" s="182" t="n"/>
+      <c r="I1" s="182" t="n"/>
     </row>
     <row r="2" ht="45.25" customHeight="1">
       <c r="A2" s="52" t="inlineStr">
@@ -43603,6 +44082,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="16" customHeight="1">
       <c r="A4" s="16" t="inlineStr">
         <is>
@@ -44297,8 +44777,8 @@
     </row>
   </sheetData>
   <mergeCells count="2">
+    <mergeCell ref="A1:I1"/>
     <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -44310,19 +44790,35 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H40"/>
+  <dimension ref="A1:AC40"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="120" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1" ht="40" customHeight="1">
-      <c r="A1" s="51" t="inlineStr">
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="181" t="inlineStr">
         <is>
           <t>v15.1 HARDENING RAPORU</t>
         </is>
       </c>
+      <c r="B1" s="182" t="n"/>
+      <c r="C1" s="182" t="n"/>
+      <c r="D1" s="182" t="n"/>
+      <c r="E1" s="182" t="n"/>
+      <c r="F1" s="182" t="n"/>
+      <c r="G1" s="182" t="n"/>
+      <c r="H1" s="182" t="n"/>
+      <c r="I1" s="182" t="n"/>
     </row>
     <row r="2" ht="45.25" customHeight="1">
       <c r="A2" s="52" t="inlineStr">
@@ -44331,6 +44827,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="16" customHeight="1">
       <c r="A4" s="16" t="inlineStr">
         <is>
@@ -44705,8 +45202,8 @@
     </row>
   </sheetData>
   <mergeCells count="2">
+    <mergeCell ref="A1:I1"/>
     <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -44719,7 +45216,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L26"/>
+  <dimension ref="A1:AC26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -44764,25 +45261,26 @@
         </is>
       </c>
     </row>
+    <row r="5"/>
     <row r="6">
       <c r="B6" s="145" t="inlineStr">
         <is>
           <t>SENARYO A: KÖTÜMSER (STRES TESTİ -%20)</t>
         </is>
       </c>
-      <c r="C6" s="83" t="n"/>
-      <c r="D6" s="83" t="n"/>
-      <c r="E6" s="83" t="n"/>
-      <c r="F6" s="83" t="n"/>
+      <c r="C6" s="188" t="n"/>
+      <c r="D6" s="188" t="n"/>
+      <c r="E6" s="188" t="n"/>
+      <c r="F6" s="189" t="n"/>
       <c r="H6" s="146" t="inlineStr">
         <is>
           <t>SENARYO B: BAZ MODEL (HEDEFLENEN)</t>
         </is>
       </c>
-      <c r="I6" s="83" t="n"/>
-      <c r="J6" s="83" t="n"/>
-      <c r="K6" s="83" t="n"/>
-      <c r="L6" s="83" t="n"/>
+      <c r="I6" s="188" t="n"/>
+      <c r="J6" s="188" t="n"/>
+      <c r="K6" s="188" t="n"/>
+      <c r="L6" s="189" t="n"/>
     </row>
     <row r="7">
       <c r="B7" s="83" t="n"/>
@@ -44933,32 +45431,33 @@
           <t>STRES SENARYOSUNDA DAHİ İFLAS RİSKİ YOK</t>
         </is>
       </c>
-      <c r="C14" s="83" t="n"/>
-      <c r="D14" s="83" t="n"/>
-      <c r="E14" s="83" t="n"/>
-      <c r="F14" s="83" t="n"/>
+      <c r="C14" s="192" t="n"/>
+      <c r="D14" s="192" t="n"/>
+      <c r="E14" s="192" t="n"/>
+      <c r="F14" s="193" t="n"/>
       <c r="H14" s="153" t="inlineStr">
         <is>
           <t>OPTİMUM İCRA VE PLANLAMA REÇETESİ</t>
         </is>
       </c>
-      <c r="I14" s="83" t="n"/>
-      <c r="J14" s="83" t="n"/>
-      <c r="K14" s="83" t="n"/>
-      <c r="L14" s="83" t="n"/>
+      <c r="I14" s="194" t="n"/>
+      <c r="J14" s="194" t="n"/>
+      <c r="K14" s="194" t="n"/>
+      <c r="L14" s="195" t="n"/>
     </row>
     <row r="15">
-      <c r="B15" s="83" t="n"/>
-      <c r="C15" s="83" t="n"/>
-      <c r="D15" s="83" t="n"/>
-      <c r="E15" s="83" t="n"/>
-      <c r="F15" s="83" t="n"/>
-      <c r="H15" s="83" t="n"/>
-      <c r="I15" s="83" t="n"/>
-      <c r="J15" s="83" t="n"/>
-      <c r="K15" s="83" t="n"/>
-      <c r="L15" s="83" t="n"/>
-    </row>
+      <c r="B15" s="196" t="n"/>
+      <c r="C15" s="197" t="n"/>
+      <c r="D15" s="197" t="n"/>
+      <c r="E15" s="197" t="n"/>
+      <c r="F15" s="198" t="n"/>
+      <c r="H15" s="199" t="n"/>
+      <c r="I15" s="200" t="n"/>
+      <c r="J15" s="200" t="n"/>
+      <c r="K15" s="200" t="n"/>
+      <c r="L15" s="201" t="n"/>
+    </row>
+    <row r="16"/>
     <row r="17">
       <c r="B17" s="63" t="inlineStr">
         <is>
@@ -44966,6 +45465,7 @@
         </is>
       </c>
     </row>
+    <row r="18"/>
     <row r="19">
       <c r="B19" s="110" t="inlineStr">
         <is>
@@ -45039,8 +45539,21 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
+  <dimension ref="A1:AC5"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14"/>
+  <cols>
+    <col width="13" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
+    <col width="13" customWidth="1" min="11" max="11"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="62" t="inlineStr">
@@ -45049,6 +45562,10 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
+    <row r="3"/>
+    <row r="4"/>
+    <row r="5"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -45061,25 +45578,37 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G15"/>
+  <dimension ref="A1:AC15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
-    <col width="24" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="27" customWidth="1" min="4" max="4"/>
-    <col width="29" customWidth="1" min="5" max="5"/>
-    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="30.5" customWidth="1" min="2" max="2"/>
+    <col width="23.5" customWidth="1" min="3" max="3"/>
+    <col width="48.5" customWidth="1" min="4" max="4"/>
+    <col width="43.5" customWidth="1" min="5" max="5"/>
+    <col width="21.5" customWidth="1" min="6" max="6"/>
     <col width="21" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="46" t="inlineStr">
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="181" t="inlineStr">
         <is>
           <t>YÜRÜTME ÇEKİRDEĞİ — ZORUNLU ÜRETİM SIRASI</t>
         </is>
       </c>
-    </row>
+      <c r="B1" s="182" t="n"/>
+      <c r="C1" s="182" t="n"/>
+      <c r="D1" s="182" t="n"/>
+      <c r="E1" s="182" t="n"/>
+      <c r="F1" s="182" t="n"/>
+      <c r="G1" s="182" t="n"/>
+      <c r="H1" s="182" t="n"/>
+      <c r="I1" s="182" t="n"/>
+    </row>
+    <row r="2"/>
     <row r="3" ht="24" customHeight="1">
       <c r="A3" s="160" t="inlineStr">
         <is>
@@ -45539,7 +46068,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A1:I1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -45552,22 +46081,37 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E34"/>
+  <dimension ref="A1:AC34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="52" customWidth="1" min="2" max="2"/>
-    <col width="34" customWidth="1" min="3" max="3"/>
+    <col width="89.5" customWidth="1" min="2" max="2"/>
+    <col width="34.5" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="47" t="inlineStr">
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="181" t="inlineStr">
         <is>
           <t>NİHAİ KONTROL LİSTESİ — KANITSIZ GEÇİŞ YOK</t>
         </is>
       </c>
-    </row>
+      <c r="B1" s="182" t="n"/>
+      <c r="C1" s="182" t="n"/>
+      <c r="D1" s="182" t="n"/>
+      <c r="E1" s="182" t="n"/>
+      <c r="F1" s="182" t="n"/>
+      <c r="G1" s="182" t="n"/>
+      <c r="H1" s="182" t="n"/>
+      <c r="I1" s="182" t="n"/>
+    </row>
+    <row r="2"/>
     <row r="3" ht="24" customHeight="1">
       <c r="A3" s="162" t="inlineStr">
         <is>
@@ -46279,7 +46823,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A1:I1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -46292,24 +46836,37 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F22"/>
+  <dimension ref="A1:AC22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="36" customWidth="1" min="2" max="2"/>
-    <col width="48" customWidth="1" min="3" max="3"/>
-    <col width="34" customWidth="1" min="4" max="4"/>
-    <col width="30" customWidth="1" min="5" max="5"/>
+    <col width="30.5" customWidth="1" min="1" max="1"/>
+    <col width="71.5" customWidth="1" min="2" max="2"/>
+    <col width="160.5" customWidth="1" min="3" max="3"/>
+    <col width="70.5" customWidth="1" min="4" max="4"/>
+    <col width="50.5" customWidth="1" min="5" max="5"/>
     <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="48" t="inlineStr">
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="181" t="inlineStr">
         <is>
           <t>GÖRSEL TASARIM VE PREMIUM EXCEL STANDARDI</t>
         </is>
       </c>
-    </row>
+      <c r="B1" s="182" t="n"/>
+      <c r="C1" s="182" t="n"/>
+      <c r="D1" s="182" t="n"/>
+      <c r="E1" s="182" t="n"/>
+      <c r="F1" s="182" t="n"/>
+      <c r="G1" s="182" t="n"/>
+      <c r="H1" s="182" t="n"/>
+      <c r="I1" s="182" t="n"/>
+    </row>
+    <row r="2"/>
     <row r="3" ht="24" customHeight="1">
       <c r="A3" s="164" t="inlineStr">
         <is>
@@ -46952,7 +47509,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A1:I1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -46965,24 +47522,37 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F18"/>
+  <dimension ref="A1:AC18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="40" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
-    <col width="30" customWidth="1" min="4" max="4"/>
-    <col width="28" customWidth="1" min="5" max="5"/>
-    <col width="26" customWidth="1" min="6" max="6"/>
+    <col width="22.5" customWidth="1" min="1" max="1"/>
+    <col width="60.5" customWidth="1" min="2" max="2"/>
+    <col width="86.5" customWidth="1" min="3" max="3"/>
+    <col width="40.5" customWidth="1" min="4" max="4"/>
+    <col width="39.5" customWidth="1" min="5" max="5"/>
+    <col width="27.5" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="49" t="inlineStr">
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="181" t="inlineStr">
         <is>
           <t>TÜRKİYE MUHASEBE VE TEKDÜZEN HESAP PLANI STANDARDI</t>
         </is>
       </c>
-    </row>
+      <c r="B1" s="182" t="n"/>
+      <c r="C1" s="182" t="n"/>
+      <c r="D1" s="182" t="n"/>
+      <c r="E1" s="182" t="n"/>
+      <c r="F1" s="182" t="n"/>
+      <c r="G1" s="182" t="n"/>
+      <c r="H1" s="182" t="n"/>
+      <c r="I1" s="182" t="n"/>
+    </row>
+    <row r="2"/>
     <row r="3" ht="24" customHeight="1">
       <c r="A3" s="166" t="inlineStr">
         <is>
@@ -47497,7 +48067,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A1:I1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -47510,23 +48080,37 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F19"/>
+  <dimension ref="A1:AC19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="32" customWidth="1" min="2" max="2"/>
-    <col width="54" customWidth="1" min="3" max="3"/>
-    <col width="34" customWidth="1" min="4" max="4"/>
+    <col width="20.5" customWidth="1" min="1" max="1"/>
+    <col width="41.5" customWidth="1" min="2" max="2"/>
+    <col width="86.5" customWidth="1" min="3" max="3"/>
+    <col width="35.5" customWidth="1" min="4" max="4"/>
+    <col width="33.5" customWidth="1" min="5" max="5"/>
     <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="50" t="inlineStr">
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="181" t="inlineStr">
         <is>
           <t>KARAR, GÜVEN VE SATIŞA HAZIRLIK STANDARDI</t>
         </is>
       </c>
-    </row>
+      <c r="B1" s="182" t="n"/>
+      <c r="C1" s="182" t="n"/>
+      <c r="D1" s="182" t="n"/>
+      <c r="E1" s="182" t="n"/>
+      <c r="F1" s="182" t="n"/>
+      <c r="G1" s="182" t="n"/>
+      <c r="H1" s="182" t="n"/>
+      <c r="I1" s="182" t="n"/>
+    </row>
+    <row r="2"/>
     <row r="3" ht="24" customHeight="1">
       <c r="A3" s="168" t="inlineStr">
         <is>
@@ -48073,7 +48657,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A1:I1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/EXCELARSIV_PRODUCTS/borcla-sirket-satin-alma-ve-yatirim-getirisi/current.xlsx
+++ b/EXCELARSIV_PRODUCTS/borcla-sirket-satin-alma-ve-yatirim-getirisi/current.xlsx
@@ -1868,7 +1868,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC33"/>
+  <dimension ref="A1:I33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -1889,14 +1889,6 @@
           <t>EXCELARŞİV KARAR SİSTEMİ v15.1 — ÜRETİM REFERANSI</t>
         </is>
       </c>
-      <c r="B1" s="182" t="n"/>
-      <c r="C1" s="182" t="n"/>
-      <c r="D1" s="182" t="n"/>
-      <c r="E1" s="182" t="n"/>
-      <c r="F1" s="182" t="n"/>
-      <c r="G1" s="182" t="n"/>
-      <c r="H1" s="182" t="n"/>
-      <c r="I1" s="182" t="n"/>
     </row>
     <row r="2"/>
     <row r="3" ht="24" customHeight="1">
@@ -2274,7 +2266,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC7245"/>
+  <dimension ref="A1:I7245"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2290,19 +2282,11 @@
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
-      <c r="A1" s="202" t="inlineStr">
+      <c r="A1" s="181" t="inlineStr">
         <is>
           <t>HARİCİ PYTHON KAYNAĞI</t>
         </is>
       </c>
-      <c r="B1" s="182" t="n"/>
-      <c r="C1" s="182" t="n"/>
-      <c r="D1" s="182" t="n"/>
-      <c r="E1" s="182" t="n"/>
-      <c r="F1" s="182" t="n"/>
-      <c r="G1" s="182" t="n"/>
-      <c r="H1" s="182" t="n"/>
-      <c r="I1" s="182" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="27" t="inlineStr">
@@ -31338,7 +31322,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC253"/>
+  <dimension ref="A1:I253"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -31359,14 +31343,6 @@
           <t>KAYNAK HARİTASI</t>
         </is>
       </c>
-      <c r="B1" s="182" t="n"/>
-      <c r="C1" s="182" t="n"/>
-      <c r="D1" s="182" t="n"/>
-      <c r="E1" s="182" t="n"/>
-      <c r="F1" s="182" t="n"/>
-      <c r="G1" s="182" t="n"/>
-      <c r="H1" s="182" t="n"/>
-      <c r="I1" s="182" t="n"/>
     </row>
     <row r="2" ht="45.25" customHeight="1">
       <c r="A2" s="52" t="inlineStr">
@@ -35895,7 +35871,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC30"/>
+  <dimension ref="A1:I30"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
     <col width="24.5" customWidth="1" min="1" max="1"/>
@@ -35916,14 +35892,6 @@
           <t>MODÜL MATRİSİ</t>
         </is>
       </c>
-      <c r="B1" s="182" t="n"/>
-      <c r="C1" s="182" t="n"/>
-      <c r="D1" s="182" t="n"/>
-      <c r="E1" s="182" t="n"/>
-      <c r="F1" s="182" t="n"/>
-      <c r="G1" s="182" t="n"/>
-      <c r="H1" s="182" t="n"/>
-      <c r="I1" s="182" t="n"/>
     </row>
     <row r="2" ht="45.25" customHeight="1">
       <c r="A2" s="52" t="inlineStr">
@@ -37222,7 +37190,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC15"/>
+  <dimension ref="A1:I15"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="2"/>
@@ -37243,14 +37211,6 @@
           <t>MODEL YÖNETİŞİM SEVİYESİ</t>
         </is>
       </c>
-      <c r="B1" s="182" t="n"/>
-      <c r="C1" s="182" t="n"/>
-      <c r="D1" s="182" t="n"/>
-      <c r="E1" s="182" t="n"/>
-      <c r="F1" s="182" t="n"/>
-      <c r="G1" s="182" t="n"/>
-      <c r="H1" s="182" t="n"/>
-      <c r="I1" s="182" t="n"/>
     </row>
     <row r="2" ht="45.25" customHeight="1">
       <c r="A2" s="52" t="inlineStr">
@@ -37432,7 +37392,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC5"/>
+  <dimension ref="A1:L5"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -37456,17 +37416,6 @@
           <t>VERİ SÖZLEŞMELERİ</t>
         </is>
       </c>
-      <c r="B1" s="182" t="n"/>
-      <c r="C1" s="182" t="n"/>
-      <c r="D1" s="182" t="n"/>
-      <c r="E1" s="182" t="n"/>
-      <c r="F1" s="182" t="n"/>
-      <c r="G1" s="182" t="n"/>
-      <c r="H1" s="182" t="n"/>
-      <c r="I1" s="182" t="n"/>
-      <c r="J1" s="182" t="n"/>
-      <c r="K1" s="182" t="n"/>
-      <c r="L1" s="182" t="n"/>
     </row>
     <row r="2" ht="45.25" customHeight="1">
       <c r="A2" s="52" t="inlineStr">
@@ -37608,7 +37557,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC5"/>
+  <dimension ref="A1:M5"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -37633,18 +37582,6 @@
           <t>ANLAM / KPI SÖZLEŞMELERİ</t>
         </is>
       </c>
-      <c r="B1" s="182" t="n"/>
-      <c r="C1" s="182" t="n"/>
-      <c r="D1" s="182" t="n"/>
-      <c r="E1" s="182" t="n"/>
-      <c r="F1" s="182" t="n"/>
-      <c r="G1" s="182" t="n"/>
-      <c r="H1" s="182" t="n"/>
-      <c r="I1" s="182" t="n"/>
-      <c r="J1" s="182" t="n"/>
-      <c r="K1" s="182" t="n"/>
-      <c r="L1" s="182" t="n"/>
-      <c r="M1" s="182" t="n"/>
     </row>
     <row r="2" ht="45.25" customHeight="1">
       <c r="A2" s="52" t="inlineStr">
@@ -37808,7 +37745,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC5"/>
+  <dimension ref="A1:H5"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="2"/>
@@ -37828,13 +37765,6 @@
           <t>BAĞIMLILIK VE BLAST RADIUS</t>
         </is>
       </c>
-      <c r="B1" s="182" t="n"/>
-      <c r="C1" s="182" t="n"/>
-      <c r="D1" s="182" t="n"/>
-      <c r="E1" s="182" t="n"/>
-      <c r="F1" s="182" t="n"/>
-      <c r="G1" s="182" t="n"/>
-      <c r="H1" s="182" t="n"/>
     </row>
     <row r="2" ht="45.25" customHeight="1">
       <c r="A2" s="52" t="inlineStr">
@@ -37948,7 +37878,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC5"/>
+  <dimension ref="A1:N5"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -37974,19 +37904,6 @@
           <t>VARSAYIM YÖNETİMİ</t>
         </is>
       </c>
-      <c r="B1" s="182" t="n"/>
-      <c r="C1" s="182" t="n"/>
-      <c r="D1" s="182" t="n"/>
-      <c r="E1" s="182" t="n"/>
-      <c r="F1" s="182" t="n"/>
-      <c r="G1" s="182" t="n"/>
-      <c r="H1" s="182" t="n"/>
-      <c r="I1" s="182" t="n"/>
-      <c r="J1" s="182" t="n"/>
-      <c r="K1" s="182" t="n"/>
-      <c r="L1" s="182" t="n"/>
-      <c r="M1" s="182" t="n"/>
-      <c r="N1" s="182" t="n"/>
     </row>
     <row r="2" ht="45.25" customHeight="1">
       <c r="A2" s="52" t="inlineStr">
@@ -38134,7 +38051,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC13"/>
+  <dimension ref="A1:I13"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
     <col width="22.5" customWidth="1" min="1" max="1"/>
@@ -38155,14 +38072,6 @@
           <t>FİNANSAL DEĞİŞMEZLER</t>
         </is>
       </c>
-      <c r="B1" s="182" t="n"/>
-      <c r="C1" s="182" t="n"/>
-      <c r="D1" s="182" t="n"/>
-      <c r="E1" s="182" t="n"/>
-      <c r="F1" s="182" t="n"/>
-      <c r="G1" s="182" t="n"/>
-      <c r="H1" s="182" t="n"/>
-      <c r="I1" s="182" t="n"/>
     </row>
     <row r="2" ht="45.25" customHeight="1">
       <c r="A2" s="52" t="inlineStr">
@@ -38422,7 +38331,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC12"/>
+  <dimension ref="A1:I12"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -38443,14 +38352,6 @@
           <t>BAĞIMSIZ ORACLE TESTLERİ</t>
         </is>
       </c>
-      <c r="B1" s="182" t="n"/>
-      <c r="C1" s="182" t="n"/>
-      <c r="D1" s="182" t="n"/>
-      <c r="E1" s="182" t="n"/>
-      <c r="F1" s="182" t="n"/>
-      <c r="G1" s="182" t="n"/>
-      <c r="H1" s="182" t="n"/>
-      <c r="I1" s="182" t="n"/>
     </row>
     <row r="2" ht="45.25" customHeight="1">
       <c r="A2" s="52" t="inlineStr">
@@ -38744,7 +38645,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC27"/>
+  <dimension ref="A1:M27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -38875,7 +38776,7 @@
       <c r="I7" s="83" t="n"/>
       <c r="J7" s="83" t="n"/>
       <c r="K7" s="94">
-        <f>EĞER(E7&gt;0; YUVARLA(B7/E7; 2); 0)</f>
+        <f>IF(E7&gt;0, ROUND(B7/E7, 2), 0)</f>
         <v/>
       </c>
       <c r="L7" s="83" t="n"/>
@@ -39180,11 +39081,11 @@
         </is>
       </c>
       <c r="I19" s="175">
-        <f>TOPLA(I15:I18)</f>
+        <f>SUM(I15:I18)</f>
         <v/>
       </c>
       <c r="J19" s="176">
-        <f>TOPLA(J15:J18)</f>
+        <f>SUM(J15:J18)</f>
         <v/>
       </c>
       <c r="K19" s="108" t="inlineStr"/>
@@ -39330,7 +39231,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC16"/>
+  <dimension ref="A1:I16"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -39351,14 +39252,6 @@
           <t>ALTIN VERİ SETİ</t>
         </is>
       </c>
-      <c r="B1" s="182" t="n"/>
-      <c r="C1" s="182" t="n"/>
-      <c r="D1" s="182" t="n"/>
-      <c r="E1" s="182" t="n"/>
-      <c r="F1" s="182" t="n"/>
-      <c r="G1" s="182" t="n"/>
-      <c r="H1" s="182" t="n"/>
-      <c r="I1" s="182" t="n"/>
     </row>
     <row r="2" ht="45.25" customHeight="1">
       <c r="A2" s="52" t="inlineStr">
@@ -39660,7 +39553,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC11"/>
+  <dimension ref="A1:I11"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -39681,14 +39574,6 @@
           <t>METAMORFİK TESTLER</t>
         </is>
       </c>
-      <c r="B1" s="182" t="n"/>
-      <c r="C1" s="182" t="n"/>
-      <c r="D1" s="182" t="n"/>
-      <c r="E1" s="182" t="n"/>
-      <c r="F1" s="182" t="n"/>
-      <c r="G1" s="182" t="n"/>
-      <c r="H1" s="182" t="n"/>
-      <c r="I1" s="182" t="n"/>
     </row>
     <row r="2" ht="45.25" customHeight="1">
       <c r="A2" s="52" t="inlineStr">
@@ -39918,7 +39803,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC12"/>
+  <dimension ref="A1:I12"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -39939,14 +39824,6 @@
           <t>HATA / CHAOS ENJEKSİYONU</t>
         </is>
       </c>
-      <c r="B1" s="182" t="n"/>
-      <c r="C1" s="182" t="n"/>
-      <c r="D1" s="182" t="n"/>
-      <c r="E1" s="182" t="n"/>
-      <c r="F1" s="182" t="n"/>
-      <c r="G1" s="182" t="n"/>
-      <c r="H1" s="182" t="n"/>
-      <c r="I1" s="182" t="n"/>
     </row>
     <row r="2" ht="45.25" customHeight="1">
       <c r="A2" s="52" t="inlineStr">
@@ -40245,7 +40122,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC14"/>
+  <dimension ref="A1:I14"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
     <col width="33.5" customWidth="1" min="1" max="1"/>
@@ -40266,14 +40143,6 @@
           <t>SİSTEM / MODEL SAĞLIĞI</t>
         </is>
       </c>
-      <c r="B1" s="182" t="n"/>
-      <c r="C1" s="182" t="n"/>
-      <c r="D1" s="182" t="n"/>
-      <c r="E1" s="182" t="n"/>
-      <c r="F1" s="182" t="n"/>
-      <c r="G1" s="182" t="n"/>
-      <c r="H1" s="182" t="n"/>
-      <c r="I1" s="182" t="n"/>
     </row>
     <row r="2" ht="45.25" customHeight="1">
       <c r="A2" s="52" t="inlineStr">
@@ -40465,7 +40334,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC12"/>
+  <dimension ref="A1:I12"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -40486,14 +40355,6 @@
           <t>VERİ SAĞLIĞI</t>
         </is>
       </c>
-      <c r="B1" s="182" t="n"/>
-      <c r="C1" s="182" t="n"/>
-      <c r="D1" s="182" t="n"/>
-      <c r="E1" s="182" t="n"/>
-      <c r="F1" s="182" t="n"/>
-      <c r="G1" s="182" t="n"/>
-      <c r="H1" s="182" t="n"/>
-      <c r="I1" s="182" t="n"/>
     </row>
     <row r="2" ht="45.25" customHeight="1">
       <c r="A2" s="52" t="inlineStr">
@@ -40670,7 +40531,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC17"/>
+  <dimension ref="A1:I17"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -40691,14 +40552,6 @@
           <t>GÜVEN MOTORU</t>
         </is>
       </c>
-      <c r="B1" s="182" t="n"/>
-      <c r="C1" s="182" t="n"/>
-      <c r="D1" s="182" t="n"/>
-      <c r="E1" s="182" t="n"/>
-      <c r="F1" s="182" t="n"/>
-      <c r="G1" s="182" t="n"/>
-      <c r="H1" s="182" t="n"/>
-      <c r="I1" s="182" t="n"/>
     </row>
     <row r="2" ht="45.25" customHeight="1">
       <c r="A2" s="52" t="inlineStr">
@@ -40891,7 +40744,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC5"/>
+  <dimension ref="A1:L5"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -40915,17 +40768,6 @@
           <t>KARAR KUYRUĞU</t>
         </is>
       </c>
-      <c r="B1" s="182" t="n"/>
-      <c r="C1" s="182" t="n"/>
-      <c r="D1" s="182" t="n"/>
-      <c r="E1" s="182" t="n"/>
-      <c r="F1" s="182" t="n"/>
-      <c r="G1" s="182" t="n"/>
-      <c r="H1" s="182" t="n"/>
-      <c r="I1" s="182" t="n"/>
-      <c r="J1" s="182" t="n"/>
-      <c r="K1" s="182" t="n"/>
-      <c r="L1" s="182" t="n"/>
     </row>
     <row r="2" ht="45.25" customHeight="1">
       <c r="A2" s="52" t="inlineStr">
@@ -41065,7 +40907,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC5"/>
+  <dimension ref="A1:K5"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -41088,16 +40930,6 @@
           <t>AKSİYON PLAYBOOK</t>
         </is>
       </c>
-      <c r="B1" s="182" t="n"/>
-      <c r="C1" s="182" t="n"/>
-      <c r="D1" s="182" t="n"/>
-      <c r="E1" s="182" t="n"/>
-      <c r="F1" s="182" t="n"/>
-      <c r="G1" s="182" t="n"/>
-      <c r="H1" s="182" t="n"/>
-      <c r="I1" s="182" t="n"/>
-      <c r="J1" s="182" t="n"/>
-      <c r="K1" s="182" t="n"/>
     </row>
     <row r="2" ht="45.25" customHeight="1">
       <c r="A2" s="52" t="inlineStr">
@@ -41205,7 +41037,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC10"/>
+  <dimension ref="A1:I10"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -41226,14 +41058,6 @@
           <t>İNSAN ONAY AKIŞI</t>
         </is>
       </c>
-      <c r="B1" s="182" t="n"/>
-      <c r="C1" s="182" t="n"/>
-      <c r="D1" s="182" t="n"/>
-      <c r="E1" s="182" t="n"/>
-      <c r="F1" s="182" t="n"/>
-      <c r="G1" s="182" t="n"/>
-      <c r="H1" s="182" t="n"/>
-      <c r="I1" s="182" t="n"/>
     </row>
     <row r="2" ht="45.25" customHeight="1">
       <c r="A2" s="52" t="inlineStr">
@@ -41434,7 +41258,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC7"/>
+  <dimension ref="A1:H7"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -41454,13 +41278,6 @@
           <t>SENARYO VE TERS STRES</t>
         </is>
       </c>
-      <c r="B1" s="182" t="n"/>
-      <c r="C1" s="182" t="n"/>
-      <c r="D1" s="182" t="n"/>
-      <c r="E1" s="182" t="n"/>
-      <c r="F1" s="182" t="n"/>
-      <c r="G1" s="182" t="n"/>
-      <c r="H1" s="182" t="n"/>
     </row>
     <row r="2" ht="45.25" customHeight="1">
       <c r="A2" s="52" t="inlineStr">
@@ -41582,7 +41399,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC17"/>
+  <dimension ref="A1:J17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -42046,7 +41863,7 @@
         </is>
       </c>
       <c r="E17" s="191">
-        <f>TOPLA(E6:E15)</f>
+        <f>SUM(E6:E15)</f>
         <v/>
       </c>
     </row>
@@ -42068,7 +41885,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC9"/>
+  <dimension ref="A1:H9"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -42088,13 +41905,6 @@
           <t>K3 KULLANICI GÖREV TESTİ</t>
         </is>
       </c>
-      <c r="B1" s="182" t="n"/>
-      <c r="C1" s="182" t="n"/>
-      <c r="D1" s="182" t="n"/>
-      <c r="E1" s="182" t="n"/>
-      <c r="F1" s="182" t="n"/>
-      <c r="G1" s="182" t="n"/>
-      <c r="H1" s="182" t="n"/>
     </row>
     <row r="2" ht="45.25" customHeight="1">
       <c r="A2" s="52" t="inlineStr">
@@ -42366,7 +42176,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC19"/>
+  <dimension ref="A1:I19"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
     <col width="38.5" customWidth="1" min="1" max="1"/>
@@ -42387,14 +42197,6 @@
           <t>TİCARİ DEĞER MOTORU</t>
         </is>
       </c>
-      <c r="B1" s="182" t="n"/>
-      <c r="C1" s="182" t="n"/>
-      <c r="D1" s="182" t="n"/>
-      <c r="E1" s="182" t="n"/>
-      <c r="F1" s="182" t="n"/>
-      <c r="G1" s="182" t="n"/>
-      <c r="H1" s="182" t="n"/>
-      <c r="I1" s="182" t="n"/>
     </row>
     <row r="2" ht="45.25" customHeight="1">
       <c r="A2" s="52" t="inlineStr">
@@ -42623,7 +42425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC8"/>
+  <dimension ref="A1:I8"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="2"/>
@@ -42644,14 +42446,6 @@
           <t>FİYAT ↔ KALİTE RELEASE KAPISI</t>
         </is>
       </c>
-      <c r="B1" s="182" t="n"/>
-      <c r="C1" s="182" t="n"/>
-      <c r="D1" s="182" t="n"/>
-      <c r="E1" s="182" t="n"/>
-      <c r="F1" s="182" t="n"/>
-      <c r="G1" s="182" t="n"/>
-      <c r="H1" s="182" t="n"/>
-      <c r="I1" s="182" t="n"/>
     </row>
     <row r="2" ht="45.25" customHeight="1">
       <c r="A2" s="52" t="inlineStr">
@@ -42836,7 +42630,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC15"/>
+  <dimension ref="A1:I15"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -42857,14 +42651,6 @@
           <t>YAYIN MANİFESTOSU</t>
         </is>
       </c>
-      <c r="B1" s="182" t="n"/>
-      <c r="C1" s="182" t="n"/>
-      <c r="D1" s="182" t="n"/>
-      <c r="E1" s="182" t="n"/>
-      <c r="F1" s="182" t="n"/>
-      <c r="G1" s="182" t="n"/>
-      <c r="H1" s="182" t="n"/>
-      <c r="I1" s="182" t="n"/>
     </row>
     <row r="2" ht="45.25" customHeight="1">
       <c r="A2" s="52" t="inlineStr">
@@ -43110,7 +42896,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC19"/>
+  <dimension ref="A1:I19"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -43131,14 +42917,6 @@
           <t>KANIT ENVANTERİ</t>
         </is>
       </c>
-      <c r="B1" s="182" t="n"/>
-      <c r="C1" s="182" t="n"/>
-      <c r="D1" s="182" t="n"/>
-      <c r="E1" s="182" t="n"/>
-      <c r="F1" s="182" t="n"/>
-      <c r="G1" s="182" t="n"/>
-      <c r="H1" s="182" t="n"/>
-      <c r="I1" s="182" t="n"/>
     </row>
     <row r="2" ht="45.25" customHeight="1">
       <c r="A2" s="52" t="inlineStr">
@@ -43532,7 +43310,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC11"/>
+  <dimension ref="A1:I11"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -43553,14 +43331,6 @@
           <t>RELEASE DURUM MAKİNESİ</t>
         </is>
       </c>
-      <c r="B1" s="182" t="n"/>
-      <c r="C1" s="182" t="n"/>
-      <c r="D1" s="182" t="n"/>
-      <c r="E1" s="182" t="n"/>
-      <c r="F1" s="182" t="n"/>
-      <c r="G1" s="182" t="n"/>
-      <c r="H1" s="182" t="n"/>
-      <c r="I1" s="182" t="n"/>
     </row>
     <row r="2" ht="45.25" customHeight="1">
       <c r="A2" s="52" t="inlineStr">
@@ -43747,7 +43517,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC11"/>
+  <dimension ref="A1:I11"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -43768,14 +43538,6 @@
           <t>PYTHON RUNTIME KOMUTLARI</t>
         </is>
       </c>
-      <c r="B1" s="182" t="n"/>
-      <c r="C1" s="182" t="n"/>
-      <c r="D1" s="182" t="n"/>
-      <c r="E1" s="182" t="n"/>
-      <c r="F1" s="182" t="n"/>
-      <c r="G1" s="182" t="n"/>
-      <c r="H1" s="182" t="n"/>
-      <c r="I1" s="182" t="n"/>
     </row>
     <row r="2" ht="45.25" customHeight="1">
       <c r="A2" s="52" t="inlineStr">
@@ -43896,7 +43658,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC11"/>
+  <dimension ref="A1:I11"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -43917,14 +43679,6 @@
           <t>SABİTLER VE ŞEMALAR</t>
         </is>
       </c>
-      <c r="B1" s="182" t="n"/>
-      <c r="C1" s="182" t="n"/>
-      <c r="D1" s="182" t="n"/>
-      <c r="E1" s="182" t="n"/>
-      <c r="F1" s="182" t="n"/>
-      <c r="G1" s="182" t="n"/>
-      <c r="H1" s="182" t="n"/>
-      <c r="I1" s="182" t="n"/>
     </row>
     <row r="2" ht="45.25" customHeight="1">
       <c r="A2" s="52" t="inlineStr">
@@ -44045,7 +43799,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC28"/>
+  <dimension ref="A1:I28"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
     <col width="31.5" customWidth="1" min="1" max="1"/>
@@ -44066,14 +43820,6 @@
           <t>PYTHON FONKSİYON ENVANTERİ</t>
         </is>
       </c>
-      <c r="B1" s="182" t="n"/>
-      <c r="C1" s="182" t="n"/>
-      <c r="D1" s="182" t="n"/>
-      <c r="E1" s="182" t="n"/>
-      <c r="F1" s="182" t="n"/>
-      <c r="G1" s="182" t="n"/>
-      <c r="H1" s="182" t="n"/>
-      <c r="I1" s="182" t="n"/>
     </row>
     <row r="2" ht="45.25" customHeight="1">
       <c r="A2" s="52" t="inlineStr">
@@ -44790,7 +44536,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC40"/>
+  <dimension ref="A1:I40"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -44811,14 +44557,6 @@
           <t>v15.1 HARDENING RAPORU</t>
         </is>
       </c>
-      <c r="B1" s="182" t="n"/>
-      <c r="C1" s="182" t="n"/>
-      <c r="D1" s="182" t="n"/>
-      <c r="E1" s="182" t="n"/>
-      <c r="F1" s="182" t="n"/>
-      <c r="G1" s="182" t="n"/>
-      <c r="H1" s="182" t="n"/>
-      <c r="I1" s="182" t="n"/>
     </row>
     <row r="2" ht="45.25" customHeight="1">
       <c r="A2" s="52" t="inlineStr">
@@ -45216,7 +44954,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC26"/>
+  <dimension ref="A1:L26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -45383,7 +45121,7 @@
       <c r="C11" s="83" t="n"/>
       <c r="D11" s="83" t="n"/>
       <c r="E11" s="180">
-        <f>YUVARLA(PANO!B7*0.8/PANO!E7; 2)</f>
+        <f>ROUND(PANO!B7*0.8/PANO!E7, 2)</f>
         <v/>
       </c>
       <c r="F11" s="83" t="n"/>
@@ -45539,7 +45277,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC5"/>
+  <dimension ref="A1:A1"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -45562,10 +45300,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
-    <row r="3"/>
-    <row r="4"/>
-    <row r="5"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -45578,7 +45312,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC15"/>
+  <dimension ref="A1:I15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -45599,14 +45333,6 @@
           <t>YÜRÜTME ÇEKİRDEĞİ — ZORUNLU ÜRETİM SIRASI</t>
         </is>
       </c>
-      <c r="B1" s="182" t="n"/>
-      <c r="C1" s="182" t="n"/>
-      <c r="D1" s="182" t="n"/>
-      <c r="E1" s="182" t="n"/>
-      <c r="F1" s="182" t="n"/>
-      <c r="G1" s="182" t="n"/>
-      <c r="H1" s="182" t="n"/>
-      <c r="I1" s="182" t="n"/>
     </row>
     <row r="2"/>
     <row r="3" ht="24" customHeight="1">
@@ -46081,7 +45807,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC34"/>
+  <dimension ref="A1:I34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -46102,14 +45828,6 @@
           <t>NİHAİ KONTROL LİSTESİ — KANITSIZ GEÇİŞ YOK</t>
         </is>
       </c>
-      <c r="B1" s="182" t="n"/>
-      <c r="C1" s="182" t="n"/>
-      <c r="D1" s="182" t="n"/>
-      <c r="E1" s="182" t="n"/>
-      <c r="F1" s="182" t="n"/>
-      <c r="G1" s="182" t="n"/>
-      <c r="H1" s="182" t="n"/>
-      <c r="I1" s="182" t="n"/>
     </row>
     <row r="2"/>
     <row r="3" ht="24" customHeight="1">
@@ -46836,7 +46554,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC22"/>
+  <dimension ref="A1:I22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30.5" customWidth="1" min="1" max="1"/>
@@ -46857,14 +46575,6 @@
           <t>GÖRSEL TASARIM VE PREMIUM EXCEL STANDARDI</t>
         </is>
       </c>
-      <c r="B1" s="182" t="n"/>
-      <c r="C1" s="182" t="n"/>
-      <c r="D1" s="182" t="n"/>
-      <c r="E1" s="182" t="n"/>
-      <c r="F1" s="182" t="n"/>
-      <c r="G1" s="182" t="n"/>
-      <c r="H1" s="182" t="n"/>
-      <c r="I1" s="182" t="n"/>
     </row>
     <row r="2"/>
     <row r="3" ht="24" customHeight="1">
@@ -47522,7 +47232,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC18"/>
+  <dimension ref="A1:I18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22.5" customWidth="1" min="1" max="1"/>
@@ -47543,14 +47253,6 @@
           <t>TÜRKİYE MUHASEBE VE TEKDÜZEN HESAP PLANI STANDARDI</t>
         </is>
       </c>
-      <c r="B1" s="182" t="n"/>
-      <c r="C1" s="182" t="n"/>
-      <c r="D1" s="182" t="n"/>
-      <c r="E1" s="182" t="n"/>
-      <c r="F1" s="182" t="n"/>
-      <c r="G1" s="182" t="n"/>
-      <c r="H1" s="182" t="n"/>
-      <c r="I1" s="182" t="n"/>
     </row>
     <row r="2"/>
     <row r="3" ht="24" customHeight="1">
@@ -48080,7 +47782,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC19"/>
+  <dimension ref="A1:I19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20.5" customWidth="1" min="1" max="1"/>
@@ -48101,14 +47803,6 @@
           <t>KARAR, GÜVEN VE SATIŞA HAZIRLIK STANDARDI</t>
         </is>
       </c>
-      <c r="B1" s="182" t="n"/>
-      <c r="C1" s="182" t="n"/>
-      <c r="D1" s="182" t="n"/>
-      <c r="E1" s="182" t="n"/>
-      <c r="F1" s="182" t="n"/>
-      <c r="G1" s="182" t="n"/>
-      <c r="H1" s="182" t="n"/>
-      <c r="I1" s="182" t="n"/>
     </row>
     <row r="2"/>
     <row r="3" ht="24" customHeight="1">

--- a/EXCELARSIV_PRODUCTS/borcla-sirket-satin-alma-ve-yatirim-getirisi/current.xlsx
+++ b/EXCELARSIV_PRODUCTS/borcla-sirket-satin-alma-ve-yatirim-getirisi/current.xlsx
@@ -60,7 +60,7 @@
     <numFmt numFmtId="166" formatCode="₺#,##0"/>
     <numFmt numFmtId="167" formatCode="0.00&quot;x&quot;"/>
   </numFmts>
-  <fonts count="72">
+  <fonts count="108">
     <font>
       <name val="Carlito"/>
       <sz val="11"/>
@@ -475,8 +475,220 @@
       <color rgb="00FFFFFF"/>
       <sz val="13"/>
     </font>
+    <font>
+      <name val="Segoe UI"/>
+      <color rgb="00334155"/>
+      <sz val="8.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="0064748B"/>
+      <sz val="8.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="001E40AF"/>
+      <sz val="7.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="000F172A"/>
+      <sz val="20"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00B91C1C"/>
+      <sz val="7.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00DC2626"/>
+      <sz val="20"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="0015803D"/>
+      <sz val="7.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00475569"/>
+      <sz val="7.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="000F172A"/>
+      <sz val="10.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="0015803D"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00475569"/>
+      <sz val="8.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <color rgb="000F172A"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <color rgb="00475569"/>
+      <sz val="8.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00166534"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="001E40AF"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="0092400E"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00115E59"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="0038BDF8"/>
+      <sz val="9.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00F87171"/>
+      <sz val="9.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="0034D399"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="000F172A"/>
+      <sz val="9.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00059669"/>
+      <sz val="8.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="000284C7"/>
+      <sz val="8.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00D97706"/>
+      <sz val="8.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="008B5CF6"/>
+      <sz val="8.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00059669"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00A7F3D0"/>
+      <sz val="7.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00065F46"/>
+      <sz val="8.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00991B1B"/>
+      <sz val="9.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <color rgb="00475569"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00DC2626"/>
+      <sz val="9.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00059669"/>
+      <sz val="9.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00B91C1C"/>
+      <sz val="8.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="001E40AF"/>
+      <sz val="9.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="002563EB"/>
+      <sz val="9.5"/>
+    </font>
   </fonts>
-  <fills count="40">
+  <fills count="44">
     <fill>
       <patternFill/>
     </fill>
@@ -688,8 +900,32 @@
         <bgColor rgb="001B365D"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00DCFCE7"/>
+        <bgColor rgb="00DCFCE7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F1F5F9"/>
+        <bgColor rgb="00F1F5F9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00CCFBF1"/>
+        <bgColor rgb="00CCFBF1"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F0FDF4"/>
+        <bgColor rgb="00F0FDF4"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="38">
+  <borders count="74">
     <border>
       <left/>
       <right/>
@@ -1079,11 +1315,353 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="001E3A8A"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="00E2E8F0"/>
+      </top>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00E2E8F0"/>
+      </top>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00E2E8F0"/>
+      </right>
+      <top style="thin">
+        <color rgb="00E2E8F0"/>
+      </top>
+      <bottom/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="001E3A8A"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00E2E8F0"/>
+      </right>
+      <top/>
+      <bottom/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="001E3A8A"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="00E2E8F0"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="00E2E8F0"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00E2E8F0"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="00E2E8F0"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="00DC2626"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="00E2E8F0"/>
+      </top>
+      <bottom/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="00DC2626"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="00DC2626"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="00E2E8F0"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="00059669"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="00E2E8F0"/>
+      </top>
+      <bottom/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="00059669"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="00059669"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="00E2E8F0"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="000284C7"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="00E2E8F0"/>
+      </top>
+      <bottom/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="000284C7"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="000284C7"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="00E2E8F0"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00334155"/>
+      </left>
+      <right style="thin">
+        <color rgb="00334155"/>
+      </right>
+      <top style="thin">
+        <color rgb="000F172A"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="000F172A"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00334155"/>
+      </left>
+      <right style="thin">
+        <color rgb="00334155"/>
+      </right>
+      <top style="medium">
+        <color rgb="00334155"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="000F172A"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00E2E8F0"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="00E2E8F0"/>
+      </top>
+      <bottom/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00E2E8F0"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00E2E8F0"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="00E2E8F0"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00065F46"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="00065F46"/>
+      </top>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00065F46"/>
+      </top>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00065F46"/>
+      </right>
+      <top style="thin">
+        <color rgb="00065F46"/>
+      </top>
+      <bottom/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00065F46"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00065F46"/>
+      </right>
+      <top/>
+      <bottom/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00FECACA"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="00FECACA"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00FECACA"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00FECACA"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00FECACA"/>
+      </right>
+      <top/>
+      <bottom/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00FCA5A5"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="00FCA5A5"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00FCA5A5"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00BFDBFE"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="00BFDBFE"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00BFDBFE"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00BFDBFE"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00BFDBFE"/>
+      </right>
+      <top/>
+      <bottom/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="0093C5FD"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="0093C5FD"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="0093C5FD"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4"/>
   </cellStyleXfs>
-  <cellXfs count="203">
+  <cellXfs count="300">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
@@ -1535,6 +2113,235 @@
     <xf numFmtId="0" fontId="71" fillId="39" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="40" fillId="36" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="72" fillId="36" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="58" fillId="28" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="73" fillId="36" borderId="38" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="36" borderId="39" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="74" fillId="29" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="73" fillId="36" borderId="47" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="76" fillId="30" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="73" fillId="36" borderId="50" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="78" fillId="40" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="73" fillId="36" borderId="53" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="79" fillId="41" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="36" borderId="41" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="36" borderId="42" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="36" borderId="43" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="36" borderId="48" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="36" borderId="51" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="36" borderId="54" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="75" fillId="36" borderId="41" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="77" fillId="36" borderId="48" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="75" fillId="36" borderId="51" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="75" fillId="36" borderId="54" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="36" borderId="44" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="36" borderId="45" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="36" borderId="46" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="37" fillId="36" borderId="49" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="36" borderId="52" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="36" borderId="55" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="80" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="81" fillId="40" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="82" fillId="37" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="58" fillId="25" borderId="56" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="58" fillId="25" borderId="56" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="83" fillId="36" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="36" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="40" fillId="36" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="65" fillId="36" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="84" fillId="36" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="85" fillId="40" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="36" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="83" fillId="37" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="37" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="40" fillId="37" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="65" fillId="37" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="84" fillId="37" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="86" fillId="29" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="37" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="87" fillId="34" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="88" fillId="42" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="25" borderId="57" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="89" fillId="25" borderId="57" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="90" fillId="25" borderId="57" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="25" borderId="57" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="91" fillId="25" borderId="57" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="92" fillId="36" borderId="58" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="36" borderId="40" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="98" fillId="35" borderId="61" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="35" borderId="62" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="35" borderId="63" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="93" fillId="36" borderId="59" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="84" fillId="36" borderId="59" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="93" fillId="36" borderId="43" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="99" fillId="35" borderId="64" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="35" borderId="42" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="35" borderId="65" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="94" fillId="36" borderId="59" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="35" borderId="64" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="95" fillId="36" borderId="59" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="40" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="96" fillId="36" borderId="59" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="97" fillId="43" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="100" fillId="36" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="36" borderId="60" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="93" fillId="0" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="101" fillId="30" borderId="66" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="106" fillId="29" borderId="70" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="36" borderId="67" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="36" borderId="68" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="36" borderId="71" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="36" borderId="72" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="102" fillId="36" borderId="67" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="103" fillId="36" borderId="42" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="102" fillId="36" borderId="71" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="107" fillId="36" borderId="42" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="92" fillId="36" borderId="42" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="104" fillId="36" borderId="42" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="104" fillId="36" borderId="42" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="104" fillId="36" borderId="42" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="105" fillId="30" borderId="69" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="70" fillId="29" borderId="73" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="80" fillId="36" borderId="58" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="36" borderId="59" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="92" fillId="36" borderId="59" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="84" fillId="36" borderId="59" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="2"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1890,7 +2697,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="24" customHeight="1">
       <c r="A3" s="156" t="inlineStr">
         <is>
@@ -2155,7 +2961,6 @@
         </is>
       </c>
     </row>
-    <row r="25"/>
     <row r="26" ht="16" customHeight="1">
       <c r="A26" s="159" t="inlineStr">
         <is>
@@ -31351,7 +32156,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4" ht="16" customHeight="1">
       <c r="A4" s="16" t="inlineStr">
         <is>
@@ -35900,7 +36704,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4" ht="16" customHeight="1">
       <c r="A4" s="16" t="inlineStr">
         <is>
@@ -37219,7 +38022,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4" ht="16" customHeight="1">
       <c r="A4" s="16" t="inlineStr">
         <is>
@@ -37327,7 +38129,6 @@
         </is>
       </c>
     </row>
-    <row r="11"/>
     <row r="12" ht="16" customHeight="1">
       <c r="A12" s="22" t="inlineStr">
         <is>
@@ -37424,7 +38225,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4" ht="16" customHeight="1">
       <c r="A4" s="16" t="inlineStr">
         <is>
@@ -37590,7 +38390,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4" ht="16" customHeight="1">
       <c r="A4" s="16" t="inlineStr">
         <is>
@@ -37773,7 +38572,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4" ht="16" customHeight="1">
       <c r="A4" s="16" t="inlineStr">
         <is>
@@ -37912,7 +38710,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4" ht="16" customHeight="1">
       <c r="A4" s="16" t="inlineStr">
         <is>
@@ -38080,7 +38877,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4" ht="16" customHeight="1">
       <c r="A4" s="16" t="inlineStr">
         <is>
@@ -38360,7 +39156,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4" ht="16" customHeight="1">
       <c r="A4" s="16" t="inlineStr">
         <is>
@@ -38648,554 +39443,585 @@
   <dimension ref="A1:M27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="8" customWidth="1" min="1" max="1"/>
-    <col width="79.5" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="15.5" customWidth="1" min="4" max="4"/>
-    <col width="36.5" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="15.5" customWidth="1" min="7" max="7"/>
-    <col width="75.5" customWidth="1" min="8" max="8"/>
-    <col width="15" customWidth="1" min="9" max="9"/>
-    <col width="15.5" customWidth="1" min="10" max="10"/>
-    <col width="75.5" customWidth="1" min="11" max="11"/>
-    <col width="18" customWidth="1" min="12" max="12"/>
-    <col width="18" customWidth="1" min="13" max="13"/>
-    <col width="13" customWidth="1" min="14" max="14"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="17" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="4" max="4"/>
+    <col width="17" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="11" customWidth="1" min="7" max="7"/>
+    <col width="17" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="11" customWidth="1" min="10" max="10"/>
+    <col width="17" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
+    <col width="6" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="62" t="inlineStr">
+    <row r="1" ht="24" customHeight="1">
+      <c r="A1" s="203" t="inlineStr">
         <is>
           <t>☰ PANO</t>
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="B2" s="78" t="inlineStr">
+    <row r="2" ht="28" customHeight="1">
+      <c r="B2" s="204" t="inlineStr">
         <is>
           <t>BORCLA SIRKET SATIN ALMA VE YATIRIM GETIRISI</t>
         </is>
       </c>
-      <c r="L2" s="79" t="inlineStr">
+      <c r="L2" s="205" t="inlineStr">
         <is>
           <t>Dönem: 2026 / Tam ▼</t>
         </is>
       </c>
-      <c r="M2" s="80" t="inlineStr">
+      <c r="M2" s="206" t="inlineStr">
         <is>
           <t>★ DOĞRULANMIŞ</t>
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="B3" s="81" t="inlineStr">
+    <row r="3" ht="18" customHeight="1">
+      <c r="B3" s="207" t="inlineStr">
         <is>
           <t>Hedef Kullanıcı: Yönetim Kurulu, CFO, Finans Yöneticisi, SMMM · 2026 Q3 Denetim Standardı</t>
         </is>
       </c>
     </row>
-    <row r="4"/>
-    <row r="5">
-      <c r="B5" s="82" t="inlineStr">
+    <row r="4" ht="10" customHeight="1"/>
+    <row r="5" ht="20" customHeight="1">
+      <c r="B5" s="208" t="inlineStr">
         <is>
           <t>TOPLAM KREDİ PORTFÖYÜ</t>
         </is>
       </c>
-      <c r="C5" s="83" t="n"/>
-      <c r="D5" s="84" t="inlineStr">
+      <c r="C5" s="209" t="n"/>
+      <c r="D5" s="210" t="inlineStr">
         <is>
           <t>6 BANKA</t>
         </is>
       </c>
-      <c r="E5" s="85" t="inlineStr">
+      <c r="E5" s="211" t="inlineStr">
         <is>
           <t>AYLIK TAKSİT YÜKÜ</t>
         </is>
       </c>
-      <c r="F5" s="83" t="n"/>
-      <c r="G5" s="86" t="inlineStr">
+      <c r="F5" s="209" t="n"/>
+      <c r="G5" s="212" t="inlineStr">
         <is>
           <t>VADE: 7 GÜN</t>
         </is>
       </c>
-      <c r="H5" s="82" t="inlineStr">
+      <c r="H5" s="213" t="inlineStr">
         <is>
           <t>KULLANILABİLİR KREDİ LİMİTİ</t>
         </is>
       </c>
-      <c r="I5" s="83" t="n"/>
-      <c r="J5" s="87" t="inlineStr">
+      <c r="I5" s="209" t="n"/>
+      <c r="J5" s="214" t="inlineStr">
         <is>
           <t>GÜVENLİ</t>
         </is>
       </c>
-      <c r="K5" s="88" t="inlineStr">
+      <c r="K5" s="215" t="inlineStr">
         <is>
           <t>BORÇ SERVİS ORANI (DSCR)</t>
         </is>
       </c>
-      <c r="L5" s="83" t="n"/>
-      <c r="M5" s="84" t="inlineStr">
+      <c r="L5" s="209" t="n"/>
+      <c r="M5" s="216" t="inlineStr">
         <is>
           <t>EŞİK: 1.25x</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="B6" s="89" t="n"/>
-      <c r="C6" s="83" t="n"/>
-      <c r="D6" s="83" t="n"/>
-      <c r="E6" s="90" t="n"/>
-      <c r="F6" s="83" t="n"/>
-      <c r="G6" s="83" t="n"/>
-      <c r="H6" s="89" t="n"/>
-      <c r="I6" s="83" t="n"/>
-      <c r="J6" s="83" t="n"/>
-      <c r="K6" s="91" t="n"/>
-      <c r="L6" s="83" t="n"/>
-      <c r="M6" s="83" t="n"/>
-    </row>
-    <row r="7">
-      <c r="B7" s="171">
+    <row r="6" ht="6" customHeight="1">
+      <c r="B6" s="217" t="n"/>
+      <c r="C6" s="218" t="n"/>
+      <c r="D6" s="219" t="n"/>
+      <c r="E6" s="220" t="n"/>
+      <c r="F6" s="218" t="n"/>
+      <c r="G6" s="219" t="n"/>
+      <c r="H6" s="221" t="n"/>
+      <c r="I6" s="218" t="n"/>
+      <c r="J6" s="219" t="n"/>
+      <c r="K6" s="222" t="n"/>
+      <c r="L6" s="218" t="n"/>
+      <c r="M6" s="219" t="n"/>
+    </row>
+    <row r="7" ht="32" customHeight="1">
+      <c r="B7" s="223">
         <f>GİRDİLER!E17</f>
         <v/>
       </c>
-      <c r="C7" s="83" t="n"/>
-      <c r="D7" s="83" t="n"/>
-      <c r="E7" s="172">
+      <c r="C7" s="218" t="n"/>
+      <c r="D7" s="219" t="n"/>
+      <c r="E7" s="224">
         <f>B7*0.22</f>
         <v/>
       </c>
-      <c r="F7" s="83" t="n"/>
-      <c r="G7" s="83" t="n"/>
-      <c r="H7" s="171">
+      <c r="F7" s="218" t="n"/>
+      <c r="G7" s="219" t="n"/>
+      <c r="H7" s="225">
         <f>B7-E7</f>
         <v/>
       </c>
-      <c r="I7" s="83" t="n"/>
-      <c r="J7" s="83" t="n"/>
-      <c r="K7" s="94">
+      <c r="I7" s="218" t="n"/>
+      <c r="J7" s="219" t="n"/>
+      <c r="K7" s="226">
         <f>IF(E7&gt;0, ROUND(B7/E7, 2), 0)</f>
         <v/>
       </c>
-      <c r="L7" s="83" t="n"/>
-      <c r="M7" s="83" t="n"/>
-    </row>
-    <row r="8">
-      <c r="B8" s="89" t="n"/>
-      <c r="C8" s="83" t="n"/>
-      <c r="D8" s="83" t="n"/>
-      <c r="E8" s="90" t="n"/>
-      <c r="F8" s="83" t="n"/>
-      <c r="G8" s="83" t="n"/>
-      <c r="H8" s="89" t="n"/>
-      <c r="I8" s="83" t="n"/>
-      <c r="J8" s="83" t="n"/>
-      <c r="K8" s="91" t="n"/>
-      <c r="L8" s="83" t="n"/>
-      <c r="M8" s="83" t="n"/>
-    </row>
-    <row r="9">
-      <c r="B9" s="95" t="inlineStr">
+      <c r="L7" s="218" t="n"/>
+      <c r="M7" s="219" t="n"/>
+    </row>
+    <row r="8" ht="6" customHeight="1">
+      <c r="B8" s="217" t="n"/>
+      <c r="C8" s="218" t="n"/>
+      <c r="D8" s="219" t="n"/>
+      <c r="E8" s="220" t="n"/>
+      <c r="F8" s="218" t="n"/>
+      <c r="G8" s="219" t="n"/>
+      <c r="H8" s="221" t="n"/>
+      <c r="I8" s="218" t="n"/>
+      <c r="J8" s="219" t="n"/>
+      <c r="K8" s="222" t="n"/>
+      <c r="L8" s="218" t="n"/>
+      <c r="M8" s="219" t="n"/>
+    </row>
+    <row r="9" ht="18" customHeight="1">
+      <c r="B9" s="227" t="inlineStr">
         <is>
           <t>↑ %14.2 konsolide canlı veri bağlantısı</t>
         </is>
       </c>
-      <c r="C9" s="83" t="n"/>
-      <c r="D9" s="83" t="n"/>
-      <c r="E9" s="96" t="inlineStr">
+      <c r="C9" s="228" t="n"/>
+      <c r="D9" s="229" t="n"/>
+      <c r="E9" s="230" t="inlineStr">
         <is>
           <t>● 8 Kalem nakit karşılığı: bloke</t>
         </is>
       </c>
-      <c r="F9" s="83" t="n"/>
-      <c r="G9" s="83" t="n"/>
-      <c r="H9" s="95" t="inlineStr">
+      <c r="F9" s="228" t="n"/>
+      <c r="G9" s="229" t="n"/>
+      <c r="H9" s="231" t="inlineStr">
         <is>
           <t>██████████░░░░░ %78.0 NET MARJ</t>
         </is>
       </c>
-      <c r="I9" s="83" t="n"/>
-      <c r="J9" s="83" t="n"/>
-      <c r="K9" s="97" t="inlineStr">
+      <c r="I9" s="228" t="n"/>
+      <c r="J9" s="229" t="n"/>
+      <c r="K9" s="232" t="inlineStr">
         <is>
           <t>✓ İDEAL karşılama rasyosu</t>
         </is>
       </c>
-      <c r="L9" s="83" t="n"/>
-      <c r="M9" s="83" t="n"/>
-    </row>
-    <row r="10"/>
-    <row r="11">
-      <c r="B11" s="76" t="inlineStr">
+      <c r="L9" s="228" t="n"/>
+      <c r="M9" s="229" t="n"/>
+    </row>
+    <row r="10" ht="14" customHeight="1"/>
+    <row r="11" ht="24" customHeight="1">
+      <c r="B11" s="233" t="inlineStr">
         <is>
           <t>BORCLA SIRKET SATIN ALMA VE YATIRIM GETIRISI — DÖNEMSEL İCRA VE PROJEKSİYON</t>
         </is>
       </c>
-      <c r="F11" s="98" t="inlineStr">
+      <c r="F11" s="234" t="inlineStr">
         <is>
           <t>+%32 Verim</t>
         </is>
       </c>
-      <c r="H11" s="76" t="inlineStr">
+      <c r="H11" s="233" t="inlineStr">
         <is>
           <t>KONSOLİDE OPERASYON VE KARAR MATRİSİ</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="B12" s="75" t="inlineStr">
+    <row r="12" ht="18" customHeight="1">
+      <c r="B12" s="81" t="inlineStr">
         <is>
           <t>Kümülatif Hacim vs. Operasyonel Maliyet ve Net Kâr Eğilimi</t>
         </is>
       </c>
-      <c r="H12" s="75" t="inlineStr">
+      <c r="H12" s="81" t="inlineStr">
         <is>
           <t>Anlık Hesaplama Sonuçları, Dinamik Formül Çıktıları ve Durum Puanlaması</t>
         </is>
       </c>
     </row>
-    <row r="13"/>
-    <row r="14">
-      <c r="B14" s="99" t="inlineStr">
+    <row r="13" ht="8" customHeight="1"/>
+    <row r="14" ht="24" customHeight="1">
+      <c r="B14" s="235" t="inlineStr">
         <is>
           <t>Dönem</t>
         </is>
       </c>
-      <c r="C14" s="99" t="inlineStr">
+      <c r="C14" s="235" t="inlineStr">
         <is>
           <t>Aktif Hacim</t>
         </is>
       </c>
-      <c r="D14" s="99" t="inlineStr">
+      <c r="D14" s="235" t="inlineStr">
         <is>
           <t>Maliyet/Yük</t>
         </is>
       </c>
-      <c r="E14" s="99" t="inlineStr">
+      <c r="E14" s="235" t="inlineStr">
         <is>
           <t>Hedef</t>
         </is>
       </c>
-      <c r="H14" s="100" t="inlineStr">
+      <c r="H14" s="236" t="inlineStr">
         <is>
           <t>PARAMETRE / KALEM</t>
         </is>
       </c>
-      <c r="I14" s="100" t="inlineStr">
+      <c r="I14" s="237" t="inlineStr">
         <is>
           <t>ANA TUTAR</t>
         </is>
       </c>
-      <c r="J14" s="100" t="inlineStr">
+      <c r="J14" s="237" t="inlineStr">
         <is>
           <t>FARK / MARJ</t>
         </is>
       </c>
-      <c r="K14" s="100" t="inlineStr">
+      <c r="K14" s="237" t="inlineStr">
         <is>
           <t>VADE</t>
         </is>
       </c>
-      <c r="L14" s="100" t="inlineStr">
+      <c r="L14" s="237" t="inlineStr">
         <is>
           <t>KONTROL DURUMU</t>
         </is>
       </c>
-    </row>
-    <row r="15">
-      <c r="B15" s="75" t="inlineStr">
+      <c r="M14" s="237" t="n"/>
+    </row>
+    <row r="15" ht="22" customHeight="1">
+      <c r="B15" s="238" t="inlineStr">
         <is>
           <t>D1</t>
         </is>
       </c>
-      <c r="C15" s="75" t="n">
+      <c r="C15" s="238" t="n">
         <v>65</v>
       </c>
-      <c r="D15" s="75" t="n">
+      <c r="D15" s="238" t="n">
         <v>45</v>
       </c>
-      <c r="E15" s="75" t="n">
+      <c r="E15" s="238" t="n">
         <v>60</v>
       </c>
-      <c r="H15" s="101" t="inlineStr">
+      <c r="H15" s="239" t="inlineStr">
         <is>
           <t>Dönemlik Kümülatif Bakiye</t>
         </is>
       </c>
-      <c r="I15" s="173">
+      <c r="I15" s="240">
         <f>B7*0.45</f>
         <v/>
       </c>
-      <c r="J15" s="174">
+      <c r="J15" s="241">
         <f>B7*0.05</f>
         <v/>
       </c>
-      <c r="K15" s="103" t="inlineStr">
+      <c r="K15" s="242" t="inlineStr">
         <is>
           <t>12 Ay</t>
         </is>
       </c>
-      <c r="L15" s="87" t="inlineStr">
+      <c r="L15" s="243" t="inlineStr">
         <is>
           <t>✓ DÜZENLİ</t>
         </is>
       </c>
-    </row>
-    <row r="16">
-      <c r="B16" s="75" t="inlineStr">
+      <c r="M15" s="244" t="n"/>
+    </row>
+    <row r="16" ht="22" customHeight="1">
+      <c r="B16" s="245" t="inlineStr">
         <is>
           <t>D2</t>
         </is>
       </c>
-      <c r="C16" s="75" t="n">
+      <c r="C16" s="245" t="n">
         <v>78</v>
       </c>
-      <c r="D16" s="75" t="n">
+      <c r="D16" s="245" t="n">
         <v>48</v>
       </c>
-      <c r="E16" s="75" t="n">
+      <c r="E16" s="245" t="n">
         <v>70</v>
       </c>
-      <c r="H16" s="101" t="inlineStr">
+      <c r="H16" s="246" t="inlineStr">
         <is>
           <t>Kritik Eşik Güvenlik Tamponu</t>
         </is>
       </c>
-      <c r="I16" s="173">
+      <c r="I16" s="247">
         <f>B7*0.30</f>
         <v/>
       </c>
-      <c r="J16" s="174">
+      <c r="J16" s="248">
         <f>B7*0.03</f>
         <v/>
       </c>
-      <c r="K16" s="103" t="inlineStr">
+      <c r="K16" s="249" t="inlineStr">
         <is>
           <t>24 Ay</t>
         </is>
       </c>
-      <c r="L16" s="84" t="inlineStr">
+      <c r="L16" s="250" t="inlineStr">
         <is>
           <t>★ AVANTAJ</t>
         </is>
       </c>
-    </row>
-    <row r="17">
-      <c r="B17" s="75" t="inlineStr">
+      <c r="M16" s="251" t="n"/>
+    </row>
+    <row r="17" ht="22" customHeight="1">
+      <c r="B17" s="238" t="inlineStr">
         <is>
           <t>D3</t>
         </is>
       </c>
-      <c r="C17" s="75" t="n">
+      <c r="C17" s="238" t="n">
         <v>85</v>
       </c>
-      <c r="D17" s="75" t="n">
+      <c r="D17" s="238" t="n">
         <v>55</v>
       </c>
-      <c r="E17" s="75" t="n">
+      <c r="E17" s="238" t="n">
         <v>80</v>
       </c>
-      <c r="H17" s="101" t="inlineStr">
+      <c r="H17" s="239" t="inlineStr">
         <is>
           <t>Operasyonel Net Fark</t>
         </is>
       </c>
-      <c r="I17" s="173">
+      <c r="I17" s="240">
         <f>B7*0.15</f>
         <v/>
       </c>
-      <c r="J17" s="174">
+      <c r="J17" s="241">
         <f>B7*0.02</f>
         <v/>
       </c>
-      <c r="K17" s="103" t="inlineStr">
+      <c r="K17" s="242" t="inlineStr">
         <is>
           <t>8 Ay</t>
         </is>
       </c>
-      <c r="L17" s="104" t="inlineStr">
+      <c r="L17" s="252" t="inlineStr">
         <is>
           <t>● YAKLAŞAN</t>
         </is>
       </c>
-    </row>
-    <row r="18">
-      <c r="B18" s="75" t="inlineStr">
+      <c r="M17" s="244" t="n"/>
+    </row>
+    <row r="18" ht="22" customHeight="1">
+      <c r="B18" s="245" t="inlineStr">
         <is>
           <t>D4</t>
         </is>
       </c>
-      <c r="C18" s="75" t="n">
+      <c r="C18" s="245" t="n">
         <v>75</v>
       </c>
-      <c r="D18" s="75" t="n">
+      <c r="D18" s="245" t="n">
         <v>42</v>
       </c>
-      <c r="E18" s="75" t="n">
+      <c r="E18" s="245" t="n">
         <v>75</v>
       </c>
-      <c r="H18" s="101" t="inlineStr">
+      <c r="H18" s="246" t="inlineStr">
         <is>
           <t>Rezerv ve Likit Dağılım</t>
         </is>
       </c>
-      <c r="I18" s="173">
+      <c r="I18" s="247">
         <f>B7*0.10</f>
         <v/>
       </c>
-      <c r="J18" s="174">
+      <c r="J18" s="248">
         <f>B7*0.01</f>
         <v/>
       </c>
-      <c r="K18" s="103" t="inlineStr">
+      <c r="K18" s="249" t="inlineStr">
         <is>
           <t>16 Ay</t>
         </is>
       </c>
-      <c r="L18" s="87" t="inlineStr">
+      <c r="L18" s="253" t="inlineStr">
         <is>
           <t>✓ TAM UYUM</t>
         </is>
       </c>
-    </row>
-    <row r="19">
-      <c r="B19" s="75" t="inlineStr">
+      <c r="M18" s="251" t="n"/>
+    </row>
+    <row r="19" ht="26" customHeight="1">
+      <c r="B19" s="238" t="inlineStr">
         <is>
           <t>D5</t>
         </is>
       </c>
-      <c r="C19" s="75" t="n">
+      <c r="C19" s="238" t="n">
         <v>90</v>
       </c>
-      <c r="D19" s="75" t="n">
+      <c r="D19" s="238" t="n">
         <v>40</v>
       </c>
-      <c r="E19" s="75" t="n">
+      <c r="E19" s="238" t="n">
         <v>85</v>
       </c>
-      <c r="H19" s="105" t="inlineStr">
+      <c r="H19" s="254" t="inlineStr">
         <is>
           <t>KONSOLİDE SİSTEM TOPLAMI</t>
         </is>
       </c>
-      <c r="I19" s="175">
+      <c r="I19" s="255">
         <f>SUM(I15:I18)</f>
         <v/>
       </c>
-      <c r="J19" s="176">
+      <c r="J19" s="256">
         <f>SUM(J15:J18)</f>
         <v/>
       </c>
-      <c r="K19" s="108" t="inlineStr"/>
-      <c r="L19" s="109" t="inlineStr">
+      <c r="K19" s="257" t="inlineStr"/>
+      <c r="L19" s="258" t="inlineStr">
         <is>
           <t>TAM DOĞRULANDI (0 HATA)</t>
         </is>
       </c>
-    </row>
-    <row r="20">
-      <c r="B20" s="75" t="inlineStr">
+      <c r="M19" s="258" t="n"/>
+    </row>
+    <row r="20" ht="22" customHeight="1">
+      <c r="B20" s="245" t="inlineStr">
         <is>
           <t>D6</t>
         </is>
       </c>
-      <c r="C20" s="75" t="n">
+      <c r="C20" s="245" t="n">
         <v>96</v>
       </c>
-      <c r="D20" s="75" t="n">
+      <c r="D20" s="245" t="n">
         <v>32</v>
       </c>
-      <c r="E20" s="75" t="n">
+      <c r="E20" s="245" t="n">
         <v>92</v>
       </c>
     </row>
-    <row r="21"/>
-    <row r="22">
-      <c r="B22" s="110" t="inlineStr">
+    <row r="21" ht="14" customHeight="1"/>
+    <row r="22" ht="24" customHeight="1">
+      <c r="B22" s="259" t="inlineStr">
         <is>
           <t>KONSOLİDE PAY VE AĞIRLIK</t>
         </is>
       </c>
-      <c r="F22" s="110" t="inlineStr">
+      <c r="C22" s="209" t="n"/>
+      <c r="D22" s="209" t="n"/>
+      <c r="E22" s="260" t="n"/>
+      <c r="F22" s="259" t="inlineStr">
         <is>
           <t>LİKİDİTE RİSKİ &amp; ERKEN UYARI SİNYALLERİ</t>
         </is>
       </c>
-      <c r="K22" s="111" t="inlineStr">
+      <c r="G22" s="209" t="n"/>
+      <c r="H22" s="209" t="n"/>
+      <c r="I22" s="260" t="n"/>
+      <c r="K22" s="261" t="inlineStr">
         <is>
           <t>KARAR MOTORU</t>
         </is>
       </c>
-      <c r="L22" s="112" t="n"/>
-      <c r="M22" s="112" t="n"/>
-    </row>
-    <row r="23">
-      <c r="B23" s="60" t="inlineStr">
+      <c r="L22" s="262" t="n"/>
+      <c r="M22" s="263" t="n"/>
+    </row>
+    <row r="23" ht="20" customHeight="1">
+      <c r="B23" s="264" t="inlineStr">
         <is>
           <t>■ Ana Segment (%42)</t>
         </is>
       </c>
-      <c r="F23" s="75" t="inlineStr">
+      <c r="C23" s="218" t="n"/>
+      <c r="D23" s="218" t="n"/>
+      <c r="E23" s="219" t="n"/>
+      <c r="F23" s="265" t="inlineStr">
         <is>
           <t>Nakit Açığı Riski (30 Gün)</t>
         </is>
       </c>
-      <c r="I23" s="113" t="inlineStr">
+      <c r="G23" s="218" t="n"/>
+      <c r="H23" s="218" t="n"/>
+      <c r="I23" s="266" t="inlineStr">
         <is>
           <t>0.00 TL (Sıfır Risk)</t>
         </is>
       </c>
-      <c r="K23" s="114" t="inlineStr">
-        <is>
-          <t>REVERSED REFINANSING FIRSATI</t>
-        </is>
-      </c>
-      <c r="L23" s="112" t="n"/>
-      <c r="M23" s="112" t="n"/>
-    </row>
-    <row r="24">
-      <c r="B24" s="61" t="inlineStr">
+      <c r="K23" s="267" t="inlineStr">
+        <is>
+          <t>LİKİDİTE OPTİMİZASYON FIRSATI</t>
+        </is>
+      </c>
+      <c r="L23" s="268" t="n"/>
+      <c r="M23" s="269" t="n"/>
+    </row>
+    <row r="24" ht="20" customHeight="1">
+      <c r="B24" s="270" t="inlineStr">
         <is>
           <t>■ İkincil Grup (%30)</t>
         </is>
       </c>
-      <c r="F24" s="75" t="inlineStr">
+      <c r="C24" s="218" t="n"/>
+      <c r="D24" s="218" t="n"/>
+      <c r="E24" s="219" t="n"/>
+      <c r="F24" s="265" t="inlineStr">
         <is>
           <t>Tahsilat Gecikme Toleransı</t>
         </is>
       </c>
-      <c r="I24" s="113" t="inlineStr">
+      <c r="G24" s="218" t="n"/>
+      <c r="H24" s="218" t="n"/>
+      <c r="I24" s="266" t="inlineStr">
         <is>
           <t>48 Gün Güvenli Eşik</t>
         </is>
       </c>
-      <c r="K24" s="115" t="inlineStr">
-        <is>
-          <t>Kredi maliyetini düşürmek için uzun vadeli yapılandırma önerilmektedir.</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="B25" s="116" t="inlineStr">
+      <c r="K24" s="271" t="inlineStr">
+        <is>
+          <t>Atıl kalan nakit rezervinin gecelik repoda</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="20" customHeight="1">
+      <c r="B25" s="272" t="inlineStr">
         <is>
           <t>■ Destek Birimi (%15)</t>
         </is>
       </c>
-      <c r="F25" s="60" t="inlineStr">
+      <c r="C25" s="218" t="n"/>
+      <c r="D25" s="218" t="n"/>
+      <c r="E25" s="219" t="n"/>
+      <c r="F25" s="243" t="inlineStr">
         <is>
           <t>██████████████████████████████████████ Güvenli Bölge (%100)</t>
         </is>
       </c>
-    </row>
-    <row r="26">
-      <c r="B26" s="117" t="inlineStr">
+      <c r="G25" s="273" t="n"/>
+      <c r="H25" s="273" t="n"/>
+      <c r="I25" s="273" t="n"/>
+    </row>
+    <row r="26" ht="20" customHeight="1">
+      <c r="B26" s="274" t="inlineStr">
         <is>
           <t>■ Rezervler (%13)</t>
         </is>
       </c>
-      <c r="F26" s="118" t="inlineStr">
+      <c r="C26" s="218" t="n"/>
+      <c r="D26" s="218" t="n"/>
+      <c r="E26" s="219" t="n"/>
+      <c r="F26" s="275" t="inlineStr">
         <is>
           <t>✓ 90 GÜNLÜK PROJEKSİYONDA NAKİT SIKIŞIKLIĞI TESPİT EDİLMEDİ</t>
         </is>
@@ -39203,23 +40029,29 @@
       <c r="G26" s="183" t="n"/>
       <c r="H26" s="183" t="n"/>
       <c r="I26" s="184" t="n"/>
-      <c r="K26" s="119" t="inlineStr">
-        <is>
-          <t>YAPILANDIRMA ANALİZİNİ GÖR &gt;</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
+      <c r="K26" s="276" t="inlineStr">
+        <is>
+          <t>FONLAMA SENARYOSUNU İNCELE ›</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="26" customHeight="1">
+      <c r="B27" s="277" t="n"/>
+      <c r="C27" s="228" t="n"/>
+      <c r="D27" s="228" t="n"/>
+      <c r="E27" s="229" t="n"/>
       <c r="F27" s="185" t="n"/>
       <c r="G27" s="186" t="n"/>
       <c r="H27" s="186" t="n"/>
       <c r="I27" s="187" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="3">
-    <mergeCell ref="K26:M27"/>
+  <mergeCells count="5">
     <mergeCell ref="K24:M25"/>
     <mergeCell ref="F26:I27"/>
+    <mergeCell ref="B2:K2"/>
+    <mergeCell ref="K26:M27"/>
+    <mergeCell ref="B3:K3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -39260,7 +40092,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4" ht="16" customHeight="1">
       <c r="A4" s="16" t="inlineStr">
         <is>
@@ -39582,7 +40413,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4" ht="16" customHeight="1">
       <c r="A4" s="16" t="inlineStr">
         <is>
@@ -39832,7 +40662,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4" ht="16" customHeight="1">
       <c r="A4" s="16" t="inlineStr">
         <is>
@@ -40151,7 +40980,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4" ht="16" customHeight="1">
       <c r="A4" s="16" t="inlineStr">
         <is>
@@ -40363,7 +41191,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4" ht="16" customHeight="1">
       <c r="A4" s="16" t="inlineStr">
         <is>
@@ -40560,7 +41387,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4" ht="16" customHeight="1">
       <c r="A4" s="16" t="inlineStr">
         <is>
@@ -40643,7 +41469,6 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="10"/>
     <row r="11" ht="16" customHeight="1">
       <c r="A11" s="22" t="inlineStr">
         <is>
@@ -40776,7 +41601,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4" ht="16" customHeight="1">
       <c r="A4" s="16" t="inlineStr">
         <is>
@@ -40938,7 +41762,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4" ht="16" customHeight="1">
       <c r="A4" s="16" t="inlineStr">
         <is>
@@ -41066,7 +41889,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4" ht="16" customHeight="1">
       <c r="A4" s="16" t="inlineStr">
         <is>
@@ -41286,7 +42108,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4" ht="16" customHeight="1">
       <c r="A4" s="16" t="inlineStr">
         <is>
@@ -41421,7 +42242,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="B3" s="120" t="inlineStr">
         <is>
@@ -41442,7 +42262,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5">
       <c r="B5" s="123" t="inlineStr">
         <is>
@@ -41855,7 +42674,6 @@
         </is>
       </c>
     </row>
-    <row r="16"/>
     <row r="17">
       <c r="B17" s="190" t="inlineStr">
         <is>
@@ -41913,7 +42731,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4" ht="16" customHeight="1">
       <c r="A4" s="16" t="inlineStr">
         <is>
@@ -42205,7 +43022,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4" ht="16" customHeight="1">
       <c r="A4" s="16" t="inlineStr">
         <is>
@@ -42313,7 +43129,6 @@
         </is>
       </c>
     </row>
-    <row r="11"/>
     <row r="12" ht="16" customHeight="1">
       <c r="A12" s="22" t="inlineStr">
         <is>
@@ -42454,7 +43269,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4" ht="16" customHeight="1">
       <c r="A4" s="16" t="inlineStr">
         <is>
@@ -42659,7 +43473,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4" ht="16" customHeight="1">
       <c r="A4" s="16" t="inlineStr">
         <is>
@@ -42925,7 +43738,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4" ht="16" customHeight="1">
       <c r="A4" s="16" t="inlineStr">
         <is>
@@ -43339,7 +44151,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4" ht="16" customHeight="1">
       <c r="A4" s="16" t="inlineStr">
         <is>
@@ -43546,7 +44357,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4" ht="16" customHeight="1">
       <c r="A4" s="16" t="inlineStr">
         <is>
@@ -43687,7 +44497,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4" ht="16" customHeight="1">
       <c r="A4" s="16" t="inlineStr">
         <is>
@@ -43828,7 +44637,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4" ht="16" customHeight="1">
       <c r="A4" s="16" t="inlineStr">
         <is>
@@ -44565,7 +45373,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4" ht="16" customHeight="1">
       <c r="A4" s="16" t="inlineStr">
         <is>
@@ -44954,54 +45761,55 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L26"/>
+  <dimension ref="A1:L27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
     <col width="24" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="22" customWidth="1" min="5" max="5"/>
-    <col width="6" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
     <col width="6" customWidth="1" min="7" max="7"/>
     <col width="24" customWidth="1" min="8" max="8"/>
-    <col width="15" customWidth="1" min="9" max="9"/>
-    <col width="15" customWidth="1" min="10" max="10"/>
-    <col width="22" customWidth="1" min="11" max="11"/>
-    <col width="6" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="16" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="6" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="62" t="inlineStr">
+    <row r="1" ht="24" customHeight="1">
+      <c r="A1" s="203" t="inlineStr">
         <is>
           <t>☰ PANO</t>
         </is>
       </c>
     </row>
-    <row r="2">
+    <row r="2" ht="28" customHeight="1">
       <c r="B2" s="142" t="inlineStr">
         <is>
           <t>BORCLA SIRKET SATIN ALMA VE YATIRIM GETIRISI — NİHAİ KARAR VE DEĞERLEME</t>
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="B3" s="143" t="inlineStr">
+    <row r="3" ht="18" customHeight="1">
+      <c r="B3" s="278" t="inlineStr">
         <is>
           <t>Yönetim Kurulu ve İcra Komitesi için Otomatik Finansal Stres Testi Raporu · Yönetim Kurulu, CFO, Finans Yöneticisi, SMMM</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="B4" s="144" t="inlineStr">
+    <row r="4" ht="20" customHeight="1">
+      <c r="B4" s="279" t="inlineStr">
         <is>
           <t>DÖNEM: 2026 Q3 · DENETİM PROTOKOLÜ: ISO/VUK/IFRS UYUMLU · DURUM: ONAYLANDI</t>
         </is>
       </c>
     </row>
-    <row r="5"/>
-    <row r="6">
-      <c r="B6" s="145" t="inlineStr">
+    <row r="5" ht="12" customHeight="1"/>
+    <row r="6" ht="26" customHeight="1">
+      <c r="B6" s="280" t="inlineStr">
         <is>
           <t>SENARYO A: KÖTÜMSER (STRES TESTİ -%20)</t>
         </is>
@@ -45010,7 +45818,7 @@
       <c r="D6" s="188" t="n"/>
       <c r="E6" s="188" t="n"/>
       <c r="F6" s="189" t="n"/>
-      <c r="H6" s="146" t="inlineStr">
+      <c r="H6" s="281" t="inlineStr">
         <is>
           <t>SENARYO B: BAZ MODEL (HEDEFLENEN)</t>
         </is>
@@ -45020,151 +45828,151 @@
       <c r="K6" s="188" t="n"/>
       <c r="L6" s="189" t="n"/>
     </row>
-    <row r="7">
-      <c r="B7" s="83" t="n"/>
-      <c r="C7" s="83" t="n"/>
-      <c r="D7" s="83" t="n"/>
-      <c r="E7" s="83" t="n"/>
-      <c r="F7" s="83" t="n"/>
-      <c r="H7" s="83" t="n"/>
-      <c r="I7" s="83" t="n"/>
-      <c r="J7" s="83" t="n"/>
-      <c r="K7" s="83" t="n"/>
-      <c r="L7" s="83" t="n"/>
-    </row>
-    <row r="8">
-      <c r="B8" s="147" t="inlineStr">
+    <row r="7" ht="22" customHeight="1">
+      <c r="B7" s="282" t="n"/>
+      <c r="C7" s="218" t="n"/>
+      <c r="D7" s="218" t="n"/>
+      <c r="E7" s="218" t="n"/>
+      <c r="F7" s="283" t="n"/>
+      <c r="H7" s="284" t="n"/>
+      <c r="I7" s="218" t="n"/>
+      <c r="J7" s="218" t="n"/>
+      <c r="K7" s="218" t="n"/>
+      <c r="L7" s="285" t="n"/>
+    </row>
+    <row r="8" ht="22" customHeight="1">
+      <c r="B8" s="286" t="inlineStr">
         <is>
           <t>Ciro / Hacim Düşüşü:</t>
         </is>
       </c>
-      <c r="C8" s="83" t="n"/>
-      <c r="D8" s="83" t="n"/>
-      <c r="E8" s="148" t="inlineStr">
+      <c r="C8" s="218" t="n"/>
+      <c r="D8" s="218" t="n"/>
+      <c r="E8" s="287" t="inlineStr">
         <is>
           <t>-%20.0 (Kriz Eşiği)</t>
         </is>
       </c>
-      <c r="F8" s="83" t="n"/>
-      <c r="H8" s="147" t="inlineStr">
+      <c r="F8" s="283" t="n"/>
+      <c r="H8" s="288" t="inlineStr">
         <is>
           <t>Ciro / Hacim Gerçekleşmesi:</t>
         </is>
       </c>
-      <c r="I8" s="83" t="n"/>
-      <c r="J8" s="83" t="n"/>
-      <c r="K8" s="149" t="inlineStr">
+      <c r="I8" s="218" t="n"/>
+      <c r="J8" s="218" t="n"/>
+      <c r="K8" s="289" t="inlineStr">
         <is>
           <t>%100.0 (Tam Bütçe)</t>
         </is>
       </c>
-      <c r="L8" s="83" t="n"/>
-    </row>
-    <row r="9">
-      <c r="B9" s="147" t="inlineStr">
+      <c r="L8" s="285" t="n"/>
+    </row>
+    <row r="9" ht="22" customHeight="1">
+      <c r="B9" s="286" t="inlineStr">
         <is>
           <t>Beklenen Net Kâr / Getiri:</t>
         </is>
       </c>
-      <c r="C9" s="83" t="n"/>
-      <c r="D9" s="83" t="n"/>
-      <c r="E9" s="178">
+      <c r="C9" s="218" t="n"/>
+      <c r="D9" s="218" t="n"/>
+      <c r="E9" s="290">
         <f>PANO!B7*0.8*0.22</f>
         <v/>
       </c>
-      <c r="F9" s="83" t="n"/>
-      <c r="H9" s="147" t="inlineStr">
+      <c r="F9" s="283" t="n"/>
+      <c r="H9" s="288" t="inlineStr">
         <is>
           <t>Beklenen Net Kâr / Getiri:</t>
         </is>
       </c>
-      <c r="I9" s="83" t="n"/>
-      <c r="J9" s="83" t="n"/>
-      <c r="K9" s="178">
+      <c r="I9" s="218" t="n"/>
+      <c r="J9" s="218" t="n"/>
+      <c r="K9" s="290">
         <f>PANO!H7</f>
         <v/>
       </c>
-      <c r="L9" s="83" t="n"/>
-    </row>
-    <row r="10">
-      <c r="B10" s="147" t="inlineStr">
+      <c r="L9" s="285" t="n"/>
+    </row>
+    <row r="10" ht="22" customHeight="1">
+      <c r="B10" s="286" t="inlineStr">
         <is>
           <t>Minimum Nakit Tamponu:</t>
         </is>
       </c>
-      <c r="C10" s="83" t="n"/>
-      <c r="D10" s="83" t="n"/>
-      <c r="E10" s="179">
+      <c r="C10" s="218" t="n"/>
+      <c r="D10" s="218" t="n"/>
+      <c r="E10" s="291">
         <f>PANO!E7*0.75</f>
         <v/>
       </c>
-      <c r="F10" s="83" t="n"/>
-      <c r="H10" s="147" t="inlineStr">
+      <c r="F10" s="283" t="n"/>
+      <c r="H10" s="288" t="inlineStr">
         <is>
           <t>Serbest Nakit Akımı:</t>
         </is>
       </c>
-      <c r="I10" s="83" t="n"/>
-      <c r="J10" s="83" t="n"/>
-      <c r="K10" s="179">
+      <c r="I10" s="218" t="n"/>
+      <c r="J10" s="218" t="n"/>
+      <c r="K10" s="291">
         <f>PANO!H7*0.75</f>
         <v/>
       </c>
-      <c r="L10" s="83" t="n"/>
-    </row>
-    <row r="11">
-      <c r="B11" s="147" t="inlineStr">
+      <c r="L10" s="285" t="n"/>
+    </row>
+    <row r="11" ht="22" customHeight="1">
+      <c r="B11" s="286" t="inlineStr">
         <is>
           <t>Likidite Karşılama Oranı:</t>
         </is>
       </c>
-      <c r="C11" s="83" t="n"/>
-      <c r="D11" s="83" t="n"/>
-      <c r="E11" s="180">
+      <c r="C11" s="218" t="n"/>
+      <c r="D11" s="218" t="n"/>
+      <c r="E11" s="292">
         <f>ROUND(PANO!B7*0.8/PANO!E7, 2)</f>
         <v/>
       </c>
-      <c r="F11" s="83" t="n"/>
-      <c r="H11" s="147" t="inlineStr">
+      <c r="F11" s="283" t="n"/>
+      <c r="H11" s="288" t="inlineStr">
         <is>
           <t>Yatırım Geri Dönüşü (ROI):</t>
         </is>
       </c>
-      <c r="I11" s="83" t="n"/>
-      <c r="J11" s="83" t="n"/>
-      <c r="K11" s="151" t="inlineStr">
+      <c r="I11" s="218" t="n"/>
+      <c r="J11" s="218" t="n"/>
+      <c r="K11" s="293" t="inlineStr">
         <is>
           <t>%38.4 Yıllık</t>
         </is>
       </c>
-      <c r="L11" s="83" t="n"/>
-    </row>
-    <row r="12">
-      <c r="B12" s="83" t="n"/>
-      <c r="C12" s="83" t="n"/>
-      <c r="D12" s="83" t="n"/>
-      <c r="E12" s="83" t="n"/>
-      <c r="F12" s="83" t="n"/>
-      <c r="H12" s="83" t="n"/>
-      <c r="I12" s="83" t="n"/>
-      <c r="J12" s="83" t="n"/>
-      <c r="K12" s="83" t="n"/>
-      <c r="L12" s="83" t="n"/>
-    </row>
-    <row r="13">
-      <c r="B13" s="83" t="n"/>
-      <c r="C13" s="83" t="n"/>
-      <c r="D13" s="83" t="n"/>
-      <c r="E13" s="83" t="n"/>
-      <c r="F13" s="83" t="n"/>
-      <c r="H13" s="83" t="n"/>
-      <c r="I13" s="83" t="n"/>
-      <c r="J13" s="83" t="n"/>
-      <c r="K13" s="83" t="n"/>
-      <c r="L13" s="83" t="n"/>
-    </row>
-    <row r="14">
-      <c r="B14" s="152" t="inlineStr">
+      <c r="L11" s="285" t="n"/>
+    </row>
+    <row r="12" ht="22" customHeight="1">
+      <c r="B12" s="282" t="n"/>
+      <c r="C12" s="218" t="n"/>
+      <c r="D12" s="218" t="n"/>
+      <c r="E12" s="218" t="n"/>
+      <c r="F12" s="283" t="n"/>
+      <c r="H12" s="284" t="n"/>
+      <c r="I12" s="218" t="n"/>
+      <c r="J12" s="218" t="n"/>
+      <c r="K12" s="218" t="n"/>
+      <c r="L12" s="285" t="n"/>
+    </row>
+    <row r="13" ht="22" customHeight="1">
+      <c r="B13" s="282" t="n"/>
+      <c r="C13" s="218" t="n"/>
+      <c r="D13" s="218" t="n"/>
+      <c r="E13" s="218" t="n"/>
+      <c r="F13" s="283" t="n"/>
+      <c r="H13" s="284" t="n"/>
+      <c r="I13" s="218" t="n"/>
+      <c r="J13" s="218" t="n"/>
+      <c r="K13" s="218" t="n"/>
+      <c r="L13" s="285" t="n"/>
+    </row>
+    <row r="14" ht="28" customHeight="1">
+      <c r="B14" s="294" t="inlineStr">
         <is>
           <t>STRES SENARYOSUNDA DAHİ İFLAS RİSKİ YOK</t>
         </is>
@@ -45173,7 +45981,7 @@
       <c r="D14" s="192" t="n"/>
       <c r="E14" s="192" t="n"/>
       <c r="F14" s="193" t="n"/>
-      <c r="H14" s="153" t="inlineStr">
+      <c r="H14" s="295" t="inlineStr">
         <is>
           <t>OPTİMUM İCRA VE PLANLAMA REÇETESİ</t>
         </is>
@@ -45183,7 +45991,7 @@
       <c r="K14" s="194" t="n"/>
       <c r="L14" s="195" t="n"/>
     </row>
-    <row r="15">
+    <row r="15" ht="14" customHeight="1">
       <c r="B15" s="196" t="n"/>
       <c r="C15" s="197" t="n"/>
       <c r="D15" s="197" t="n"/>
@@ -45195,70 +46003,185 @@
       <c r="K15" s="200" t="n"/>
       <c r="L15" s="201" t="n"/>
     </row>
-    <row r="16"/>
-    <row r="17">
-      <c r="B17" s="63" t="inlineStr">
+    <row r="16" ht="10" customHeight="1"/>
+    <row r="17" ht="26" customHeight="1">
+      <c r="B17" s="296" t="inlineStr">
         <is>
           <t>YÖNETİM KARAR MATRİSİ VE UYGULAMA REÇETESİ</t>
         </is>
       </c>
-    </row>
-    <row r="18"/>
-    <row r="19">
-      <c r="B19" s="110" t="inlineStr">
+      <c r="C17" s="209" t="n"/>
+      <c r="D17" s="209" t="n"/>
+      <c r="E17" s="209" t="n"/>
+      <c r="F17" s="209" t="n"/>
+      <c r="G17" s="209" t="n"/>
+      <c r="H17" s="209" t="n"/>
+      <c r="I17" s="209" t="n"/>
+      <c r="J17" s="209" t="n"/>
+      <c r="K17" s="209" t="n"/>
+      <c r="L17" s="260" t="n"/>
+    </row>
+    <row r="18" ht="22" customHeight="1">
+      <c r="B18" s="297" t="n"/>
+      <c r="C18" s="218" t="n"/>
+      <c r="D18" s="218" t="n"/>
+      <c r="E18" s="218" t="n"/>
+      <c r="F18" s="218" t="n"/>
+      <c r="G18" s="218" t="n"/>
+      <c r="H18" s="218" t="n"/>
+      <c r="I18" s="218" t="n"/>
+      <c r="J18" s="218" t="n"/>
+      <c r="K18" s="218" t="n"/>
+      <c r="L18" s="219" t="n"/>
+    </row>
+    <row r="19" ht="22" customHeight="1">
+      <c r="B19" s="298" t="inlineStr">
         <is>
           <t>●  Öncelik 1: Acil Likidite ve Borç Servis Planlaması</t>
         </is>
       </c>
-    </row>
-    <row r="20">
-      <c r="B20" s="154" t="inlineStr">
+      <c r="C19" s="218" t="n"/>
+      <c r="D19" s="218" t="n"/>
+      <c r="E19" s="218" t="n"/>
+      <c r="F19" s="218" t="n"/>
+      <c r="G19" s="218" t="n"/>
+      <c r="H19" s="218" t="n"/>
+      <c r="I19" s="218" t="n"/>
+      <c r="J19" s="218" t="n"/>
+      <c r="K19" s="218" t="n"/>
+      <c r="L19" s="219" t="n"/>
+    </row>
+    <row r="20" ht="22" customHeight="1">
+      <c r="B20" s="299" t="inlineStr">
         <is>
           <t xml:space="preserve">   Sistemde hesaplanan vade günlerine sadık kalınarak nakit blokajı 3 gün önceden hazır edilmelidir.</t>
         </is>
       </c>
-    </row>
-    <row r="21">
-      <c r="B21" s="110" t="inlineStr">
+      <c r="C20" s="218" t="n"/>
+      <c r="D20" s="218" t="n"/>
+      <c r="E20" s="218" t="n"/>
+      <c r="F20" s="218" t="n"/>
+      <c r="G20" s="218" t="n"/>
+      <c r="H20" s="218" t="n"/>
+      <c r="I20" s="218" t="n"/>
+      <c r="J20" s="218" t="n"/>
+      <c r="K20" s="218" t="n"/>
+      <c r="L20" s="219" t="n"/>
+    </row>
+    <row r="21" ht="22" customHeight="1">
+      <c r="B21" s="298" t="inlineStr">
         <is>
           <t>●  Öncelik 2: Formül Doğrulama ve Çapraz Sağlama</t>
         </is>
       </c>
-    </row>
-    <row r="22">
-      <c r="B22" s="154" t="inlineStr">
+      <c r="C21" s="218" t="n"/>
+      <c r="D21" s="218" t="n"/>
+      <c r="E21" s="218" t="n"/>
+      <c r="F21" s="218" t="n"/>
+      <c r="G21" s="218" t="n"/>
+      <c r="H21" s="218" t="n"/>
+      <c r="I21" s="218" t="n"/>
+      <c r="J21" s="218" t="n"/>
+      <c r="K21" s="218" t="n"/>
+      <c r="L21" s="219" t="n"/>
+    </row>
+    <row r="22" ht="22" customHeight="1">
+      <c r="B22" s="299" t="inlineStr">
         <is>
           <t xml:space="preserve">   Tüm hücreler kilitli formül korumasında olup girdi sayfalarında sıfır döngüsel başvuru (circular ref) garantilidir.</t>
         </is>
       </c>
-    </row>
-    <row r="23">
-      <c r="B23" s="110" t="inlineStr">
+      <c r="C22" s="218" t="n"/>
+      <c r="D22" s="218" t="n"/>
+      <c r="E22" s="218" t="n"/>
+      <c r="F22" s="218" t="n"/>
+      <c r="G22" s="218" t="n"/>
+      <c r="H22" s="218" t="n"/>
+      <c r="I22" s="218" t="n"/>
+      <c r="J22" s="218" t="n"/>
+      <c r="K22" s="218" t="n"/>
+      <c r="L22" s="219" t="n"/>
+    </row>
+    <row r="23" ht="22" customHeight="1">
+      <c r="B23" s="298" t="inlineStr">
         <is>
           <t>●  Öncelik 3: Resmi Mevzuat ve Vergi Kalkanı Entegrasyonu</t>
         </is>
       </c>
-    </row>
-    <row r="24">
-      <c r="B24" s="154" t="inlineStr">
+      <c r="C23" s="218" t="n"/>
+      <c r="D23" s="218" t="n"/>
+      <c r="E23" s="218" t="n"/>
+      <c r="F23" s="218" t="n"/>
+      <c r="G23" s="218" t="n"/>
+      <c r="H23" s="218" t="n"/>
+      <c r="I23" s="218" t="n"/>
+      <c r="J23" s="218" t="n"/>
+      <c r="K23" s="218" t="n"/>
+      <c r="L23" s="219" t="n"/>
+    </row>
+    <row r="24" ht="22" customHeight="1">
+      <c r="B24" s="299" t="inlineStr">
         <is>
           <t xml:space="preserve">   2026 güncel vergi dilimleri, amortisman ve SGK teşvik parametreleri tam otomatik yansıtılmaktadır.</t>
         </is>
       </c>
-    </row>
-    <row r="25">
-      <c r="B25" s="110" t="inlineStr">
+      <c r="C24" s="218" t="n"/>
+      <c r="D24" s="218" t="n"/>
+      <c r="E24" s="218" t="n"/>
+      <c r="F24" s="218" t="n"/>
+      <c r="G24" s="218" t="n"/>
+      <c r="H24" s="218" t="n"/>
+      <c r="I24" s="218" t="n"/>
+      <c r="J24" s="218" t="n"/>
+      <c r="K24" s="218" t="n"/>
+      <c r="L24" s="219" t="n"/>
+    </row>
+    <row r="25" ht="22" customHeight="1">
+      <c r="B25" s="298" t="inlineStr">
         <is>
           <t>●  Öncelik 4: Yönetici İmzası ve Rapor Paylaşımı</t>
         </is>
       </c>
-    </row>
-    <row r="26">
-      <c r="B26" s="154" t="inlineStr">
+      <c r="C25" s="218" t="n"/>
+      <c r="D25" s="218" t="n"/>
+      <c r="E25" s="218" t="n"/>
+      <c r="F25" s="218" t="n"/>
+      <c r="G25" s="218" t="n"/>
+      <c r="H25" s="218" t="n"/>
+      <c r="I25" s="218" t="n"/>
+      <c r="J25" s="218" t="n"/>
+      <c r="K25" s="218" t="n"/>
+      <c r="L25" s="219" t="n"/>
+    </row>
+    <row r="26" ht="22" customHeight="1">
+      <c r="B26" s="299" t="inlineStr">
         <is>
           <t xml:space="preserve">   Tek tuşla PDF ve A4 çıktı formatına tam uyumlu sayfa yapısı kurgulanmıştır.</t>
         </is>
       </c>
+      <c r="C26" s="218" t="n"/>
+      <c r="D26" s="218" t="n"/>
+      <c r="E26" s="218" t="n"/>
+      <c r="F26" s="218" t="n"/>
+      <c r="G26" s="218" t="n"/>
+      <c r="H26" s="218" t="n"/>
+      <c r="I26" s="218" t="n"/>
+      <c r="J26" s="218" t="n"/>
+      <c r="K26" s="218" t="n"/>
+      <c r="L26" s="219" t="n"/>
+    </row>
+    <row r="27" ht="22" customHeight="1">
+      <c r="B27" s="277" t="n"/>
+      <c r="C27" s="228" t="n"/>
+      <c r="D27" s="228" t="n"/>
+      <c r="E27" s="228" t="n"/>
+      <c r="F27" s="228" t="n"/>
+      <c r="G27" s="228" t="n"/>
+      <c r="H27" s="228" t="n"/>
+      <c r="I27" s="228" t="n"/>
+      <c r="J27" s="228" t="n"/>
+      <c r="K27" s="228" t="n"/>
+      <c r="L27" s="229" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -45334,7 +46257,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="24" customHeight="1">
       <c r="A3" s="160" t="inlineStr">
         <is>
@@ -45829,7 +46751,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="24" customHeight="1">
       <c r="A3" s="162" t="inlineStr">
         <is>
@@ -46576,7 +47497,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="24" customHeight="1">
       <c r="A3" s="164" t="inlineStr">
         <is>
@@ -47254,7 +48174,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="24" customHeight="1">
       <c r="A3" s="166" t="inlineStr">
         <is>
@@ -47804,7 +48723,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="24" customHeight="1">
       <c r="A3" s="168" t="inlineStr">
         <is>
